--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887F97AB-8116-4C60-987A-2741881F3AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16CEBCB-2FD8-48B0-9892-C3F676C46123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="618" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1331,12 +1331,6 @@
     <t>第二聯：海關聯</t>
   </si>
   <si>
-    <t>金門料羅貨櫃(物)運送單(兼出進站通行單)</t>
-  </si>
-  <si>
-    <t>第三聯：進站聯</t>
-  </si>
-  <si>
     <r>
       <t>本放行單當放行單用時，限</t>
     </r>
@@ -1450,6 +1444,81 @@
     <t>EXPRESS PACKAGE</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>第三聯：進站聯</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>金門料羅    貨櫃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>物</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>運送單</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>兼出進站通行單</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1464,7 +1533,7 @@
     <numFmt numFmtId="181" formatCode="0.000"/>
     <numFmt numFmtId="182" formatCode="yyyy&quot;.&quot;m&quot;.&quot;d&quot;&quot;"/>
   </numFmts>
-  <fonts count="78">
+  <fonts count="81">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1964,13 +2033,6 @@
       <name val="宋体"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="7"/>
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
@@ -1999,6 +2061,28 @@
       <color rgb="FF000000"/>
       <name val="細明體"/>
       <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
       <charset val="136"/>
     </font>
   </fonts>
@@ -2554,7 +2638,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="482">
+  <cellXfs count="474">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -3741,7 +3825,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3822,16 +3906,10 @@
     <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3897,9 +3975,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3948,32 +4023,17 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6605,7 +6665,7 @@
     </row>
     <row r="5" spans="1:27">
       <c r="A5" s="231" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B5" s="232"/>
       <c r="C5" s="233"/>
@@ -7058,7 +7118,7 @@
         <v>200405</v>
       </c>
       <c r="Q16" s="220" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="R16" s="116">
         <v>24951752</v>
@@ -7067,7 +7127,7 @@
         <v>244</v>
       </c>
       <c r="T16" s="221" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="U16" s="184" t="s">
         <v>187</v>
@@ -10192,7 +10252,7 @@
       <c r="K3" s="403"/>
       <c r="L3" s="403"/>
     </row>
-    <row r="4" spans="1:12" ht="33" customHeight="1">
+    <row r="4" spans="1:12" ht="42" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>20</v>
       </c>
@@ -10327,7 +10387,7 @@
       </c>
       <c r="I9" s="423"/>
       <c r="J9" s="407" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="L9" s="44"/>
     </row>
@@ -10428,17 +10488,17 @@
   <cols>
     <col min="1" max="1" width="4.28515625" style="23" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" style="23" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" style="23" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" style="23" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" style="23" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" style="23" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" style="23" customWidth="1"/>
+    <col min="3" max="3" width="3.85546875" style="23" customWidth="1"/>
+    <col min="4" max="4" width="7" style="23" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="15" style="23" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" style="23" customWidth="1"/>
     <col min="8" max="8" width="7.85546875" style="23" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" style="23" customWidth="1"/>
+    <col min="9" max="9" width="3.85546875" style="23" customWidth="1"/>
     <col min="10" max="10" width="9" style="23" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" style="23" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" style="23" customWidth="1"/>
     <col min="12" max="12" width="7.7109375" style="23" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" style="23" customWidth="1"/>
+    <col min="13" max="13" width="5" style="23" customWidth="1"/>
     <col min="14" max="14" width="10.7109375" style="46" customWidth="1"/>
     <col min="15" max="251" width="9.140625" style="23"/>
     <col min="252" max="252" width="4.28515625" style="23" customWidth="1"/>
@@ -11389,23 +11449,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1">
-      <c r="A1" s="456" t="s">
+      <c r="A1" s="470" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="456"/>
+      <c r="B1" s="470"/>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1" thickBot="1">
-      <c r="D2" s="432" t="s">
-        <v>271</v>
-      </c>
-      <c r="E2" s="432"/>
-      <c r="F2" s="432"/>
-      <c r="G2" s="432"/>
-      <c r="H2" s="432"/>
-      <c r="I2" s="432"/>
-      <c r="J2" s="432"/>
-    </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1" thickTop="1">
+      <c r="D2" s="472" t="s">
+        <v>278</v>
+      </c>
+      <c r="E2" s="473"/>
+      <c r="F2" s="473"/>
+      <c r="G2" s="473"/>
+      <c r="H2" s="473"/>
+      <c r="I2" s="473"/>
+      <c r="J2" s="473"/>
+    </row>
+    <row r="3" spans="1:16" ht="12" customHeight="1" thickTop="1">
       <c r="A3" s="40">
         <v>2</v>
       </c>
@@ -11413,7 +11473,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15" customHeight="1" thickBot="1">
+    <row r="4" spans="1:16" ht="12" customHeight="1" thickBot="1">
       <c r="A4" s="41" t="s">
         <v>183</v>
       </c>
@@ -11421,16 +11481,16 @@
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="30" customHeight="1" thickTop="1" thickBot="1">
+    <row r="5" spans="1:16" ht="30.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="A5" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="B5" s="465" t="str">
+      <c r="B5" s="462" t="str">
         <f>'准單(紅紙)-2份'!C6</f>
         <v>大佑輪</v>
       </c>
-      <c r="C5" s="466"/>
-      <c r="D5" s="467"/>
+      <c r="C5" s="463"/>
+      <c r="D5" s="464"/>
       <c r="E5" s="27" t="s">
         <v>156</v>
       </c>
@@ -11448,12 +11508,12 @@
       <c r="I5" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="J5" s="457" t="str">
+      <c r="J5" s="454" t="str">
         <f>進口艙單印1份!O16</f>
         <v>JET-F WORLDWIDE EXPRESS CO., LTD.</v>
       </c>
-      <c r="K5" s="468"/>
-      <c r="L5" s="458"/>
+      <c r="K5" s="465"/>
+      <c r="L5" s="455"/>
       <c r="M5" s="29" t="s">
         <v>159</v>
       </c>
@@ -11500,189 +11560,189 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A7" s="469" t="s">
+    <row r="7" spans="1:16" ht="12" customHeight="1" thickBot="1">
+      <c r="A7" s="466" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="470"/>
-      <c r="C7" s="470"/>
-      <c r="D7" s="470"/>
-      <c r="E7" s="470"/>
-      <c r="F7" s="471"/>
-      <c r="G7" s="469" t="s">
+      <c r="B7" s="467"/>
+      <c r="C7" s="467"/>
+      <c r="D7" s="467"/>
+      <c r="E7" s="467"/>
+      <c r="F7" s="468"/>
+      <c r="G7" s="466" t="s">
         <v>168</v>
       </c>
-      <c r="H7" s="470"/>
-      <c r="I7" s="470"/>
-      <c r="J7" s="470"/>
-      <c r="K7" s="470"/>
-      <c r="L7" s="470"/>
-      <c r="M7" s="470"/>
-      <c r="N7" s="471"/>
-    </row>
-    <row r="8" spans="1:16" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A8" s="435" t="s">
+      <c r="H7" s="467"/>
+      <c r="I7" s="467"/>
+      <c r="J7" s="467"/>
+      <c r="K7" s="467"/>
+      <c r="L7" s="467"/>
+      <c r="M7" s="467"/>
+      <c r="N7" s="468"/>
+    </row>
+    <row r="8" spans="1:16" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A8" s="433" t="s">
         <v>169</v>
       </c>
-      <c r="B8" s="472"/>
-      <c r="C8" s="436"/>
-      <c r="D8" s="435" t="s">
+      <c r="B8" s="469"/>
+      <c r="C8" s="434"/>
+      <c r="D8" s="433" t="s">
         <v>170</v>
       </c>
-      <c r="E8" s="472"/>
-      <c r="F8" s="436"/>
-      <c r="G8" s="435" t="s">
+      <c r="E8" s="469"/>
+      <c r="F8" s="434"/>
+      <c r="G8" s="433" t="s">
         <v>171</v>
       </c>
-      <c r="H8" s="436"/>
-      <c r="I8" s="435" t="s">
+      <c r="H8" s="434"/>
+      <c r="I8" s="433" t="s">
         <v>172</v>
       </c>
-      <c r="J8" s="436"/>
-      <c r="K8" s="435" t="s">
+      <c r="J8" s="434"/>
+      <c r="K8" s="433" t="s">
         <v>173</v>
       </c>
-      <c r="L8" s="436"/>
-      <c r="M8" s="435" t="s">
+      <c r="L8" s="434"/>
+      <c r="M8" s="433" t="s">
         <v>174</v>
       </c>
-      <c r="N8" s="436"/>
+      <c r="N8" s="434"/>
     </row>
     <row r="9" spans="1:16" ht="24" customHeight="1">
-      <c r="A9" s="437" t="str">
+      <c r="A9" s="435" t="str">
         <f>進口艙單印1份!E16</f>
         <v>TCNU9125529</v>
       </c>
-      <c r="B9" s="438"/>
-      <c r="C9" s="439"/>
-      <c r="D9" s="459">
+      <c r="B9" s="436"/>
+      <c r="C9" s="437"/>
+      <c r="D9" s="456">
         <f>進口艙單印1份!P16</f>
         <v>200405</v>
       </c>
-      <c r="E9" s="460"/>
-      <c r="F9" s="461"/>
-      <c r="G9" s="449"/>
-      <c r="H9" s="450"/>
-      <c r="I9" s="449"/>
-      <c r="J9" s="450"/>
-      <c r="K9" s="449"/>
-      <c r="L9" s="450"/>
-      <c r="M9" s="449"/>
-      <c r="N9" s="450"/>
+      <c r="E9" s="457"/>
+      <c r="F9" s="458"/>
+      <c r="G9" s="447"/>
+      <c r="H9" s="448"/>
+      <c r="I9" s="447"/>
+      <c r="J9" s="448"/>
+      <c r="K9" s="447"/>
+      <c r="L9" s="448"/>
+      <c r="M9" s="447"/>
+      <c r="N9" s="448"/>
       <c r="P9" s="37"/>
     </row>
-    <row r="10" spans="1:16" ht="36" customHeight="1" thickBot="1">
-      <c r="A10" s="440"/>
-      <c r="B10" s="441"/>
-      <c r="C10" s="442"/>
-      <c r="D10" s="462" t="str">
+    <row r="10" spans="1:16" ht="33.75" customHeight="1" thickBot="1">
+      <c r="A10" s="438"/>
+      <c r="B10" s="439"/>
+      <c r="C10" s="440"/>
+      <c r="D10" s="459" t="str">
         <f>'貨櫃清單-1份'!J9</f>
         <v>ESN500</v>
       </c>
-      <c r="E10" s="463"/>
-      <c r="F10" s="464"/>
-      <c r="G10" s="451"/>
-      <c r="H10" s="452"/>
-      <c r="I10" s="451"/>
-      <c r="J10" s="452"/>
-      <c r="K10" s="451"/>
-      <c r="L10" s="452"/>
-      <c r="M10" s="451"/>
-      <c r="N10" s="452"/>
+      <c r="E10" s="460"/>
+      <c r="F10" s="461"/>
+      <c r="G10" s="449"/>
+      <c r="H10" s="450"/>
+      <c r="I10" s="449"/>
+      <c r="J10" s="450"/>
+      <c r="K10" s="449"/>
+      <c r="L10" s="450"/>
+      <c r="M10" s="449"/>
+      <c r="N10" s="450"/>
       <c r="P10" s="37"/>
     </row>
-    <row r="11" spans="1:16" ht="30" customHeight="1" thickBot="1">
-      <c r="A11" s="443"/>
-      <c r="B11" s="444"/>
-      <c r="C11" s="445"/>
-      <c r="D11" s="435" t="s">
+    <row r="11" spans="1:16" ht="42" customHeight="1" thickBot="1">
+      <c r="A11" s="441"/>
+      <c r="B11" s="442"/>
+      <c r="C11" s="443"/>
+      <c r="D11" s="433" t="s">
         <v>175</v>
       </c>
-      <c r="E11" s="436"/>
+      <c r="E11" s="434"/>
       <c r="F11" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="G11" s="435" t="s">
+      <c r="G11" s="433" t="s">
         <v>177</v>
       </c>
-      <c r="H11" s="436"/>
-      <c r="I11" s="435" t="s">
+      <c r="H11" s="434"/>
+      <c r="I11" s="433" t="s">
         <v>178</v>
       </c>
-      <c r="J11" s="436"/>
-      <c r="K11" s="435" t="s">
+      <c r="J11" s="434"/>
+      <c r="K11" s="433" t="s">
         <v>179</v>
       </c>
-      <c r="L11" s="436"/>
-      <c r="M11" s="435" t="s">
+      <c r="L11" s="434"/>
+      <c r="M11" s="433" t="s">
         <v>180</v>
       </c>
-      <c r="N11" s="436"/>
-    </row>
-    <row r="12" spans="1:16" ht="51.75" customHeight="1" thickBot="1">
+      <c r="N11" s="434"/>
+    </row>
+    <row r="12" spans="1:16" ht="49.5" customHeight="1" thickBot="1">
       <c r="A12" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="435"/>
-      <c r="C12" s="436"/>
-      <c r="D12" s="457"/>
-      <c r="E12" s="458"/>
+      <c r="B12" s="433"/>
+      <c r="C12" s="434"/>
+      <c r="D12" s="454"/>
+      <c r="E12" s="455"/>
       <c r="F12" s="28"/>
-      <c r="G12" s="457"/>
-      <c r="H12" s="458"/>
-      <c r="I12" s="457"/>
-      <c r="J12" s="458"/>
-      <c r="K12" s="457"/>
-      <c r="L12" s="458"/>
-      <c r="M12" s="457"/>
-      <c r="N12" s="458"/>
-    </row>
-    <row r="13" spans="1:16" ht="10.5" customHeight="1">
-      <c r="A13" s="433" t="s">
-        <v>273</v>
-      </c>
-      <c r="B13" s="433"/>
-      <c r="C13" s="433"/>
-      <c r="D13" s="433"/>
-      <c r="E13" s="433"/>
-      <c r="F13" s="433"/>
+      <c r="G12" s="454"/>
+      <c r="H12" s="455"/>
+      <c r="I12" s="454"/>
+      <c r="J12" s="455"/>
+      <c r="K12" s="454"/>
+      <c r="L12" s="455"/>
+      <c r="M12" s="454"/>
+      <c r="N12" s="455"/>
+    </row>
+    <row r="13" spans="1:16" ht="23.25" customHeight="1">
+      <c r="A13" s="431" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" s="431"/>
+      <c r="C13" s="431"/>
+      <c r="D13" s="431"/>
+      <c r="E13" s="431"/>
+      <c r="F13" s="431"/>
     </row>
     <row r="14" spans="1:16" ht="9" customHeight="1">
-      <c r="A14" s="434" t="s">
-        <v>274</v>
-      </c>
-      <c r="B14" s="434"/>
-      <c r="C14" s="434"/>
-      <c r="D14" s="434"/>
-      <c r="E14" s="434"/>
-      <c r="F14" s="434"/>
-      <c r="G14" s="434"/>
-      <c r="H14" s="434"/>
-      <c r="I14" s="434"/>
-      <c r="J14" s="434"/>
-      <c r="K14" s="434"/>
-      <c r="L14" s="434"/>
-      <c r="M14" s="434"/>
-      <c r="N14" s="434"/>
+      <c r="A14" s="432" t="s">
+        <v>272</v>
+      </c>
+      <c r="B14" s="432"/>
+      <c r="C14" s="432"/>
+      <c r="D14" s="432"/>
+      <c r="E14" s="432"/>
+      <c r="F14" s="432"/>
+      <c r="G14" s="432"/>
+      <c r="H14" s="432"/>
+      <c r="I14" s="432"/>
+      <c r="J14" s="432"/>
+      <c r="K14" s="432"/>
+      <c r="L14" s="432"/>
+      <c r="M14" s="432"/>
+      <c r="N14" s="432"/>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1">
-      <c r="A15" s="456" t="s">
+      <c r="A15" s="470" t="s">
         <v>270</v>
       </c>
-      <c r="B15" s="456"/>
+      <c r="B15" s="470"/>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1" thickBot="1">
-      <c r="D16" s="432" t="s">
-        <v>271</v>
-      </c>
-      <c r="E16" s="432"/>
-      <c r="F16" s="432"/>
-      <c r="G16" s="432"/>
-      <c r="H16" s="432"/>
-      <c r="I16" s="432"/>
-      <c r="J16" s="432"/>
-    </row>
-    <row r="17" spans="1:14" ht="15" customHeight="1" thickTop="1">
+      <c r="D16" s="472" t="s">
+        <v>278</v>
+      </c>
+      <c r="E16" s="473"/>
+      <c r="F16" s="473"/>
+      <c r="G16" s="473"/>
+      <c r="H16" s="473"/>
+      <c r="I16" s="473"/>
+      <c r="J16" s="473"/>
+    </row>
+    <row r="17" spans="1:14" ht="12" customHeight="1" thickTop="1">
       <c r="A17" s="40">
         <v>2</v>
       </c>
@@ -11690,7 +11750,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1" thickBot="1">
+    <row r="18" spans="1:14" ht="12" customHeight="1" thickBot="1">
       <c r="A18" s="41" t="s">
         <v>183</v>
       </c>
@@ -11698,16 +11758,16 @@
         <v>154</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="30" customHeight="1" thickTop="1" thickBot="1">
+    <row r="19" spans="1:14" ht="30.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="A19" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="465" t="str">
+      <c r="B19" s="462" t="str">
         <f>B5</f>
         <v>大佑輪</v>
       </c>
-      <c r="C19" s="466"/>
-      <c r="D19" s="467"/>
+      <c r="C19" s="463"/>
+      <c r="D19" s="464"/>
       <c r="E19" s="27" t="s">
         <v>156</v>
       </c>
@@ -11725,12 +11785,12 @@
       <c r="I19" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="J19" s="457" t="str">
+      <c r="J19" s="454" t="str">
         <f>J5</f>
         <v>JET-F WORLDWIDE EXPRESS CO., LTD.</v>
       </c>
-      <c r="K19" s="468"/>
-      <c r="L19" s="458"/>
+      <c r="K19" s="465"/>
+      <c r="L19" s="455"/>
       <c r="M19" s="29" t="s">
         <v>159</v>
       </c>
@@ -11779,187 +11839,187 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A21" s="469" t="s">
+    <row r="21" spans="1:14" ht="12" customHeight="1" thickBot="1">
+      <c r="A21" s="466" t="s">
         <v>167</v>
       </c>
-      <c r="B21" s="470"/>
-      <c r="C21" s="470"/>
-      <c r="D21" s="470"/>
-      <c r="E21" s="470"/>
-      <c r="F21" s="471"/>
-      <c r="G21" s="469" t="s">
+      <c r="B21" s="467"/>
+      <c r="C21" s="467"/>
+      <c r="D21" s="467"/>
+      <c r="E21" s="467"/>
+      <c r="F21" s="468"/>
+      <c r="G21" s="466" t="s">
         <v>168</v>
       </c>
-      <c r="H21" s="470"/>
-      <c r="I21" s="470"/>
-      <c r="J21" s="470"/>
-      <c r="K21" s="470"/>
-      <c r="L21" s="470"/>
-      <c r="M21" s="470"/>
-      <c r="N21" s="471"/>
-    </row>
-    <row r="22" spans="1:14" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A22" s="435" t="s">
+      <c r="H21" s="467"/>
+      <c r="I21" s="467"/>
+      <c r="J21" s="467"/>
+      <c r="K21" s="467"/>
+      <c r="L21" s="467"/>
+      <c r="M21" s="467"/>
+      <c r="N21" s="468"/>
+    </row>
+    <row r="22" spans="1:14" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A22" s="433" t="s">
         <v>169</v>
       </c>
-      <c r="B22" s="472"/>
-      <c r="C22" s="436"/>
-      <c r="D22" s="435" t="s">
+      <c r="B22" s="469"/>
+      <c r="C22" s="434"/>
+      <c r="D22" s="433" t="s">
         <v>170</v>
       </c>
-      <c r="E22" s="472"/>
-      <c r="F22" s="436"/>
-      <c r="G22" s="435" t="s">
+      <c r="E22" s="469"/>
+      <c r="F22" s="434"/>
+      <c r="G22" s="433" t="s">
         <v>171</v>
       </c>
-      <c r="H22" s="436"/>
-      <c r="I22" s="435" t="s">
+      <c r="H22" s="434"/>
+      <c r="I22" s="433" t="s">
         <v>172</v>
       </c>
-      <c r="J22" s="436"/>
-      <c r="K22" s="435" t="s">
+      <c r="J22" s="434"/>
+      <c r="K22" s="433" t="s">
         <v>173</v>
       </c>
-      <c r="L22" s="436"/>
-      <c r="M22" s="435" t="s">
+      <c r="L22" s="434"/>
+      <c r="M22" s="433" t="s">
         <v>174</v>
       </c>
-      <c r="N22" s="436"/>
+      <c r="N22" s="434"/>
     </row>
     <row r="23" spans="1:14" ht="24" customHeight="1">
-      <c r="A23" s="473" t="str">
+      <c r="A23" s="435" t="str">
         <f>A9</f>
         <v>TCNU9125529</v>
       </c>
-      <c r="B23" s="474"/>
-      <c r="C23" s="475"/>
-      <c r="D23" s="446">
+      <c r="B23" s="436"/>
+      <c r="C23" s="437"/>
+      <c r="D23" s="444">
         <f>D9</f>
         <v>200405</v>
       </c>
-      <c r="E23" s="447"/>
-      <c r="F23" s="448"/>
-      <c r="G23" s="449"/>
-      <c r="H23" s="450"/>
-      <c r="I23" s="449"/>
-      <c r="J23" s="450"/>
-      <c r="K23" s="449"/>
-      <c r="L23" s="450"/>
-      <c r="M23" s="449"/>
-      <c r="N23" s="450"/>
-    </row>
-    <row r="24" spans="1:14" ht="36" customHeight="1" thickBot="1">
-      <c r="A24" s="476"/>
-      <c r="B24" s="477"/>
-      <c r="C24" s="478"/>
-      <c r="D24" s="453" t="str">
+      <c r="E23" s="445"/>
+      <c r="F23" s="446"/>
+      <c r="G23" s="447"/>
+      <c r="H23" s="448"/>
+      <c r="I23" s="447"/>
+      <c r="J23" s="448"/>
+      <c r="K23" s="447"/>
+      <c r="L23" s="448"/>
+      <c r="M23" s="447"/>
+      <c r="N23" s="448"/>
+    </row>
+    <row r="24" spans="1:14" ht="33.75" customHeight="1" thickBot="1">
+      <c r="A24" s="438"/>
+      <c r="B24" s="439"/>
+      <c r="C24" s="440"/>
+      <c r="D24" s="451" t="str">
         <f>D10</f>
         <v>ESN500</v>
       </c>
-      <c r="E24" s="454"/>
-      <c r="F24" s="455"/>
-      <c r="G24" s="451"/>
-      <c r="H24" s="452"/>
-      <c r="I24" s="451"/>
-      <c r="J24" s="452"/>
-      <c r="K24" s="451"/>
-      <c r="L24" s="452"/>
-      <c r="M24" s="451"/>
-      <c r="N24" s="452"/>
-    </row>
-    <row r="25" spans="1:14" ht="30" customHeight="1" thickBot="1">
-      <c r="A25" s="479"/>
-      <c r="B25" s="480"/>
-      <c r="C25" s="481"/>
-      <c r="D25" s="435" t="s">
+      <c r="E24" s="452"/>
+      <c r="F24" s="453"/>
+      <c r="G24" s="449"/>
+      <c r="H24" s="450"/>
+      <c r="I24" s="449"/>
+      <c r="J24" s="450"/>
+      <c r="K24" s="449"/>
+      <c r="L24" s="450"/>
+      <c r="M24" s="449"/>
+      <c r="N24" s="450"/>
+    </row>
+    <row r="25" spans="1:14" ht="42" customHeight="1" thickBot="1">
+      <c r="A25" s="441"/>
+      <c r="B25" s="442"/>
+      <c r="C25" s="443"/>
+      <c r="D25" s="433" t="s">
         <v>175</v>
       </c>
-      <c r="E25" s="436"/>
+      <c r="E25" s="434"/>
       <c r="F25" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="G25" s="435" t="s">
+      <c r="G25" s="433" t="s">
         <v>177</v>
       </c>
-      <c r="H25" s="436"/>
-      <c r="I25" s="435" t="s">
+      <c r="H25" s="434"/>
+      <c r="I25" s="433" t="s">
         <v>178</v>
       </c>
-      <c r="J25" s="436"/>
-      <c r="K25" s="435" t="s">
+      <c r="J25" s="434"/>
+      <c r="K25" s="433" t="s">
         <v>179</v>
       </c>
-      <c r="L25" s="436"/>
-      <c r="M25" s="435" t="s">
+      <c r="L25" s="434"/>
+      <c r="M25" s="433" t="s">
         <v>180</v>
       </c>
-      <c r="N25" s="436"/>
-    </row>
-    <row r="26" spans="1:14" ht="51.75" customHeight="1" thickBot="1">
+      <c r="N25" s="434"/>
+    </row>
+    <row r="26" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A26" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="B26" s="435"/>
-      <c r="C26" s="436"/>
-      <c r="D26" s="435"/>
-      <c r="E26" s="436"/>
+      <c r="B26" s="433"/>
+      <c r="C26" s="434"/>
+      <c r="D26" s="433"/>
+      <c r="E26" s="434"/>
       <c r="F26" s="27"/>
-      <c r="G26" s="435"/>
-      <c r="H26" s="436"/>
-      <c r="I26" s="435"/>
-      <c r="J26" s="436"/>
-      <c r="K26" s="435"/>
-      <c r="L26" s="436"/>
-      <c r="M26" s="435"/>
-      <c r="N26" s="436"/>
-    </row>
-    <row r="27" spans="1:14" ht="10.5" customHeight="1">
-      <c r="A27" s="433" t="s">
-        <v>273</v>
-      </c>
-      <c r="B27" s="433"/>
-      <c r="C27" s="433"/>
-      <c r="D27" s="433"/>
-      <c r="E27" s="433"/>
-      <c r="F27" s="433"/>
-    </row>
-    <row r="28" spans="1:14" s="169" customFormat="1" ht="9.75" customHeight="1">
-      <c r="A28" s="434" t="s">
-        <v>274</v>
-      </c>
-      <c r="B28" s="434"/>
-      <c r="C28" s="434"/>
-      <c r="D28" s="434"/>
-      <c r="E28" s="434"/>
-      <c r="F28" s="434"/>
-      <c r="G28" s="434"/>
-      <c r="H28" s="434"/>
-      <c r="I28" s="434"/>
-      <c r="J28" s="434"/>
-      <c r="K28" s="434"/>
-      <c r="L28" s="434"/>
-      <c r="M28" s="434"/>
-      <c r="N28" s="434"/>
+      <c r="G26" s="433"/>
+      <c r="H26" s="434"/>
+      <c r="I26" s="433"/>
+      <c r="J26" s="434"/>
+      <c r="K26" s="433"/>
+      <c r="L26" s="434"/>
+      <c r="M26" s="433"/>
+      <c r="N26" s="434"/>
+    </row>
+    <row r="27" spans="1:14" ht="23.25" customHeight="1">
+      <c r="A27" s="431" t="s">
+        <v>271</v>
+      </c>
+      <c r="B27" s="431"/>
+      <c r="C27" s="431"/>
+      <c r="D27" s="431"/>
+      <c r="E27" s="431"/>
+      <c r="F27" s="431"/>
+    </row>
+    <row r="28" spans="1:14" s="169" customFormat="1" ht="9" customHeight="1">
+      <c r="A28" s="432" t="s">
+        <v>272</v>
+      </c>
+      <c r="B28" s="432"/>
+      <c r="C28" s="432"/>
+      <c r="D28" s="432"/>
+      <c r="E28" s="432"/>
+      <c r="F28" s="432"/>
+      <c r="G28" s="432"/>
+      <c r="H28" s="432"/>
+      <c r="I28" s="432"/>
+      <c r="J28" s="432"/>
+      <c r="K28" s="432"/>
+      <c r="L28" s="432"/>
+      <c r="M28" s="432"/>
+      <c r="N28" s="432"/>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
-      <c r="A29" s="431" t="s">
-        <v>272</v>
-      </c>
-      <c r="B29" s="431"/>
+      <c r="A29" s="471" t="s">
+        <v>277</v>
+      </c>
+      <c r="B29" s="470"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1" thickBot="1">
-      <c r="D30" s="432" t="s">
-        <v>271</v>
-      </c>
-      <c r="E30" s="432"/>
-      <c r="F30" s="432"/>
-      <c r="G30" s="432"/>
-      <c r="H30" s="432"/>
-      <c r="I30" s="432"/>
-      <c r="J30" s="432"/>
-    </row>
-    <row r="31" spans="1:14" ht="15" customHeight="1" thickTop="1">
+      <c r="D30" s="472" t="s">
+        <v>278</v>
+      </c>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
+      <c r="G30" s="473"/>
+      <c r="H30" s="473"/>
+      <c r="I30" s="473"/>
+      <c r="J30" s="473"/>
+    </row>
+    <row r="31" spans="1:14" ht="12" customHeight="1" thickTop="1">
       <c r="A31" s="40">
         <v>2</v>
       </c>
@@ -11967,7 +12027,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15" customHeight="1" thickBot="1">
+    <row r="32" spans="1:14" ht="12" customHeight="1" thickBot="1">
       <c r="A32" s="41" t="s">
         <v>183</v>
       </c>
@@ -11975,16 +12035,16 @@
         <v>154</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="30" customHeight="1" thickTop="1" thickBot="1">
+    <row r="33" spans="1:14" ht="30.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="A33" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="B33" s="465" t="str">
+      <c r="B33" s="462" t="str">
         <f>B5</f>
         <v>大佑輪</v>
       </c>
-      <c r="C33" s="466"/>
-      <c r="D33" s="467"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="464"/>
       <c r="E33" s="27" t="s">
         <v>156</v>
       </c>
@@ -12002,12 +12062,12 @@
       <c r="I33" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="J33" s="457" t="str">
+      <c r="J33" s="454" t="str">
         <f>J5</f>
         <v>JET-F WORLDWIDE EXPRESS CO., LTD.</v>
       </c>
-      <c r="K33" s="468"/>
-      <c r="L33" s="458"/>
+      <c r="K33" s="465"/>
+      <c r="L33" s="455"/>
       <c r="M33" s="29" t="s">
         <v>159</v>
       </c>
@@ -12056,150 +12116,150 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A35" s="469" t="s">
+    <row r="35" spans="1:14" ht="12" customHeight="1" thickBot="1">
+      <c r="A35" s="466" t="s">
         <v>167</v>
       </c>
-      <c r="B35" s="470"/>
-      <c r="C35" s="470"/>
-      <c r="D35" s="470"/>
-      <c r="E35" s="470"/>
-      <c r="F35" s="471"/>
-      <c r="G35" s="469" t="s">
+      <c r="B35" s="467"/>
+      <c r="C35" s="467"/>
+      <c r="D35" s="467"/>
+      <c r="E35" s="467"/>
+      <c r="F35" s="468"/>
+      <c r="G35" s="466" t="s">
         <v>168</v>
       </c>
-      <c r="H35" s="470"/>
-      <c r="I35" s="470"/>
-      <c r="J35" s="470"/>
-      <c r="K35" s="470"/>
-      <c r="L35" s="470"/>
-      <c r="M35" s="470"/>
-      <c r="N35" s="471"/>
-    </row>
-    <row r="36" spans="1:14" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A36" s="435" t="s">
+      <c r="H35" s="467"/>
+      <c r="I35" s="467"/>
+      <c r="J35" s="467"/>
+      <c r="K35" s="467"/>
+      <c r="L35" s="467"/>
+      <c r="M35" s="467"/>
+      <c r="N35" s="468"/>
+    </row>
+    <row r="36" spans="1:14" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A36" s="433" t="s">
         <v>169</v>
       </c>
-      <c r="B36" s="472"/>
-      <c r="C36" s="436"/>
-      <c r="D36" s="435" t="s">
+      <c r="B36" s="469"/>
+      <c r="C36" s="434"/>
+      <c r="D36" s="433" t="s">
         <v>170</v>
       </c>
-      <c r="E36" s="472"/>
-      <c r="F36" s="436"/>
-      <c r="G36" s="435" t="s">
+      <c r="E36" s="469"/>
+      <c r="F36" s="434"/>
+      <c r="G36" s="433" t="s">
         <v>171</v>
       </c>
-      <c r="H36" s="436"/>
-      <c r="I36" s="435" t="s">
+      <c r="H36" s="434"/>
+      <c r="I36" s="433" t="s">
         <v>172</v>
       </c>
-      <c r="J36" s="436"/>
-      <c r="K36" s="435" t="s">
+      <c r="J36" s="434"/>
+      <c r="K36" s="433" t="s">
         <v>173</v>
       </c>
-      <c r="L36" s="436"/>
-      <c r="M36" s="435" t="s">
+      <c r="L36" s="434"/>
+      <c r="M36" s="433" t="s">
         <v>174</v>
       </c>
-      <c r="N36" s="436"/>
+      <c r="N36" s="434"/>
     </row>
     <row r="37" spans="1:14" ht="18" customHeight="1">
-      <c r="A37" s="437" t="str">
+      <c r="A37" s="435" t="str">
         <f>A9</f>
         <v>TCNU9125529</v>
       </c>
-      <c r="B37" s="438"/>
-      <c r="C37" s="439"/>
-      <c r="D37" s="446">
+      <c r="B37" s="436"/>
+      <c r="C37" s="437"/>
+      <c r="D37" s="444">
         <f>D9</f>
         <v>200405</v>
       </c>
-      <c r="E37" s="447"/>
-      <c r="F37" s="448"/>
-      <c r="G37" s="449"/>
-      <c r="H37" s="450"/>
-      <c r="I37" s="449"/>
-      <c r="J37" s="450"/>
-      <c r="K37" s="449"/>
-      <c r="L37" s="450"/>
-      <c r="M37" s="449"/>
-      <c r="N37" s="450"/>
-    </row>
-    <row r="38" spans="1:14" ht="36" customHeight="1" thickBot="1">
-      <c r="A38" s="440"/>
-      <c r="B38" s="441"/>
-      <c r="C38" s="442"/>
-      <c r="D38" s="453" t="str">
+      <c r="E37" s="445"/>
+      <c r="F37" s="446"/>
+      <c r="G37" s="447"/>
+      <c r="H37" s="448"/>
+      <c r="I37" s="447"/>
+      <c r="J37" s="448"/>
+      <c r="K37" s="447"/>
+      <c r="L37" s="448"/>
+      <c r="M37" s="447"/>
+      <c r="N37" s="448"/>
+    </row>
+    <row r="38" spans="1:14" ht="33.75" customHeight="1" thickBot="1">
+      <c r="A38" s="438"/>
+      <c r="B38" s="439"/>
+      <c r="C38" s="440"/>
+      <c r="D38" s="451" t="str">
         <f>D10</f>
         <v>ESN500</v>
       </c>
-      <c r="E38" s="454"/>
-      <c r="F38" s="455"/>
-      <c r="G38" s="451"/>
-      <c r="H38" s="452"/>
-      <c r="I38" s="451"/>
-      <c r="J38" s="452"/>
-      <c r="K38" s="451"/>
-      <c r="L38" s="452"/>
-      <c r="M38" s="451"/>
-      <c r="N38" s="452"/>
-    </row>
-    <row r="39" spans="1:14" ht="30" customHeight="1" thickBot="1">
-      <c r="A39" s="443"/>
-      <c r="B39" s="444"/>
-      <c r="C39" s="445"/>
-      <c r="D39" s="435" t="s">
+      <c r="E38" s="452"/>
+      <c r="F38" s="453"/>
+      <c r="G38" s="449"/>
+      <c r="H38" s="450"/>
+      <c r="I38" s="449"/>
+      <c r="J38" s="450"/>
+      <c r="K38" s="449"/>
+      <c r="L38" s="450"/>
+      <c r="M38" s="449"/>
+      <c r="N38" s="450"/>
+    </row>
+    <row r="39" spans="1:14" ht="42" customHeight="1" thickBot="1">
+      <c r="A39" s="441"/>
+      <c r="B39" s="442"/>
+      <c r="C39" s="443"/>
+      <c r="D39" s="433" t="s">
         <v>175</v>
       </c>
-      <c r="E39" s="436"/>
+      <c r="E39" s="434"/>
       <c r="F39" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="G39" s="435" t="s">
+      <c r="G39" s="433" t="s">
         <v>177</v>
       </c>
-      <c r="H39" s="436"/>
-      <c r="I39" s="435" t="s">
+      <c r="H39" s="434"/>
+      <c r="I39" s="433" t="s">
         <v>178</v>
       </c>
-      <c r="J39" s="436"/>
-      <c r="K39" s="435" t="s">
+      <c r="J39" s="434"/>
+      <c r="K39" s="433" t="s">
         <v>179</v>
       </c>
-      <c r="L39" s="436"/>
-      <c r="M39" s="435" t="s">
+      <c r="L39" s="434"/>
+      <c r="M39" s="433" t="s">
         <v>180</v>
       </c>
-      <c r="N39" s="436"/>
-    </row>
-    <row r="40" spans="1:14" ht="51.75" customHeight="1" thickBot="1">
+      <c r="N39" s="434"/>
+    </row>
+    <row r="40" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A40" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="B40" s="435"/>
-      <c r="C40" s="436"/>
-      <c r="D40" s="435"/>
-      <c r="E40" s="436"/>
+      <c r="B40" s="433"/>
+      <c r="C40" s="434"/>
+      <c r="D40" s="433"/>
+      <c r="E40" s="434"/>
       <c r="F40" s="27"/>
-      <c r="G40" s="435"/>
-      <c r="H40" s="436"/>
-      <c r="I40" s="435"/>
-      <c r="J40" s="436"/>
-      <c r="K40" s="435"/>
-      <c r="L40" s="436"/>
-      <c r="M40" s="435"/>
-      <c r="N40" s="436"/>
-    </row>
-    <row r="41" spans="1:14" ht="10.5" customHeight="1">
-      <c r="A41" s="433" t="s">
-        <v>273</v>
-      </c>
-      <c r="B41" s="433"/>
-      <c r="C41" s="433"/>
-      <c r="D41" s="433"/>
-      <c r="E41" s="433"/>
-      <c r="F41" s="433"/>
+      <c r="G40" s="433"/>
+      <c r="H40" s="434"/>
+      <c r="I40" s="433"/>
+      <c r="J40" s="434"/>
+      <c r="K40" s="433"/>
+      <c r="L40" s="434"/>
+      <c r="M40" s="433"/>
+      <c r="N40" s="434"/>
+    </row>
+    <row r="41" spans="1:14" ht="23.25" customHeight="1">
+      <c r="A41" s="431" t="s">
+        <v>271</v>
+      </c>
+      <c r="B41" s="431"/>
+      <c r="C41" s="431"/>
+      <c r="D41" s="431"/>
+      <c r="E41" s="431"/>
+      <c r="F41" s="431"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
@@ -12303,7 +12363,7 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.27559055118110237" right="0.74803149606299213" top="0.39370078740157483" bottom="0.19685039370078741" header="0.39370078740157483" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/template.xlsx
+++ b/template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABA64EC-9448-43FB-B597-C4636ACE447A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B6DD13-875B-48F6-8C98-DEEB1682275F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="618" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="618" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="建船資料檔" sheetId="78" r:id="rId1"/>
@@ -1516,7 +1516,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>ESN501</t>
+    <t>ESN888</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3279,6 +3279,207 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="46" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="46" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="54" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="54" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="46" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3294,30 +3495,6 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3333,185 +3510,206 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="176" fontId="46" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="46" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="46" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="20" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="46" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="54" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="54" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3528,36 +3726,18 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3565,183 +3745,60 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="20" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3765,62 +3822,65 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="61" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3834,12 +3894,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -3852,59 +3906,23 @@
     <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="61" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3912,6 +3930,87 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3921,15 +4020,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3941,99 +4034,6 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6511,32 +6511,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="30.75" customHeight="1">
-      <c r="A1" s="267" t="s">
+      <c r="A1" s="262" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="268"/>
-      <c r="C1" s="269"/>
-      <c r="D1" s="273" t="s">
+      <c r="B1" s="263"/>
+      <c r="C1" s="264"/>
+      <c r="D1" s="251" t="s">
         <v>193</v>
       </c>
-      <c r="E1" s="273"/>
-      <c r="F1" s="273" t="s">
+      <c r="E1" s="251"/>
+      <c r="F1" s="251" t="s">
         <v>194</v>
       </c>
-      <c r="G1" s="273"/>
-      <c r="H1" s="253" t="s">
+      <c r="G1" s="251"/>
+      <c r="H1" s="234" t="s">
         <v>195</v>
       </c>
-      <c r="I1" s="254"/>
-      <c r="J1" s="273" t="s">
+      <c r="I1" s="235"/>
+      <c r="J1" s="251" t="s">
         <v>196</v>
       </c>
-      <c r="K1" s="273"/>
-      <c r="L1" s="253" t="s">
+      <c r="K1" s="251"/>
+      <c r="L1" s="234" t="s">
         <v>197</v>
       </c>
-      <c r="M1" s="279"/>
-      <c r="N1" s="254"/>
+      <c r="M1" s="252"/>
+      <c r="N1" s="235"/>
       <c r="O1" s="186"/>
       <c r="P1" s="186"/>
       <c r="Q1" s="131"/>
@@ -6546,30 +6546,30 @@
       <c r="U1" s="180"/>
     </row>
     <row r="2" spans="1:27" ht="17.25" customHeight="1">
-      <c r="A2" s="270"/>
-      <c r="B2" s="271"/>
-      <c r="C2" s="272"/>
-      <c r="D2" s="249" t="s">
+      <c r="A2" s="265"/>
+      <c r="B2" s="266"/>
+      <c r="C2" s="267"/>
+      <c r="D2" s="231" t="s">
         <v>198</v>
       </c>
-      <c r="E2" s="250"/>
-      <c r="F2" s="280" t="s">
+      <c r="E2" s="233"/>
+      <c r="F2" s="253" t="s">
         <v>199</v>
       </c>
-      <c r="G2" s="281"/>
-      <c r="H2" s="247" t="s">
+      <c r="G2" s="254"/>
+      <c r="H2" s="228" t="s">
         <v>200</v>
       </c>
-      <c r="I2" s="248"/>
-      <c r="J2" s="247" t="s">
+      <c r="I2" s="230"/>
+      <c r="J2" s="228" t="s">
         <v>201</v>
       </c>
-      <c r="K2" s="248"/>
-      <c r="L2" s="247" t="s">
+      <c r="K2" s="230"/>
+      <c r="L2" s="228" t="s">
         <v>202</v>
       </c>
-      <c r="M2" s="275"/>
-      <c r="N2" s="248"/>
+      <c r="M2" s="229"/>
+      <c r="N2" s="230"/>
       <c r="O2" s="130"/>
       <c r="P2" s="129"/>
       <c r="Q2" s="128"/>
@@ -6582,32 +6582,32 @@
       <c r="A3" s="74"/>
       <c r="B3" s="75"/>
       <c r="C3" s="76"/>
-      <c r="D3" s="231" t="str">
+      <c r="D3" s="273" t="str">
         <f>建船資料檔!B6</f>
         <v>輯薪輪</v>
       </c>
-      <c r="E3" s="232"/>
-      <c r="F3" s="233">
+      <c r="E3" s="274"/>
+      <c r="F3" s="268">
         <f>建船資料檔!B7</f>
         <v>260727</v>
       </c>
-      <c r="G3" s="234"/>
-      <c r="H3" s="235" t="str">
+      <c r="G3" s="269"/>
+      <c r="H3" s="294" t="str">
         <f>建船資料檔!B8</f>
         <v xml:space="preserve">BP3379 </v>
       </c>
-      <c r="I3" s="236"/>
-      <c r="J3" s="225" t="str">
+      <c r="I3" s="295"/>
+      <c r="J3" s="292" t="str">
         <f>建船資料檔!B9</f>
         <v>姜大炎</v>
       </c>
-      <c r="K3" s="226"/>
-      <c r="L3" s="222" t="str">
+      <c r="K3" s="293"/>
+      <c r="L3" s="289" t="str">
         <f>建船資料檔!B10</f>
         <v>15PAHD</v>
       </c>
-      <c r="M3" s="223"/>
-      <c r="N3" s="224"/>
+      <c r="M3" s="290"/>
+      <c r="N3" s="291"/>
       <c r="O3" s="186"/>
       <c r="P3" s="186"/>
       <c r="Q3" s="186"/>
@@ -6623,32 +6623,32 @@
       <c r="AA3" s="78"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="276" t="s">
+      <c r="A4" s="270" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="277"/>
-      <c r="C4" s="278"/>
-      <c r="D4" s="253" t="s">
+      <c r="B4" s="271"/>
+      <c r="C4" s="272"/>
+      <c r="D4" s="234" t="s">
         <v>203</v>
       </c>
-      <c r="E4" s="254"/>
-      <c r="F4" s="253" t="s">
+      <c r="E4" s="235"/>
+      <c r="F4" s="234" t="s">
         <v>204</v>
       </c>
-      <c r="G4" s="254"/>
-      <c r="H4" s="253" t="s">
+      <c r="G4" s="235"/>
+      <c r="H4" s="234" t="s">
         <v>205</v>
       </c>
-      <c r="I4" s="254"/>
-      <c r="J4" s="253" t="s">
+      <c r="I4" s="235"/>
+      <c r="J4" s="234" t="s">
         <v>206</v>
       </c>
-      <c r="K4" s="254"/>
-      <c r="L4" s="253" t="s">
+      <c r="K4" s="235"/>
+      <c r="L4" s="234" t="s">
         <v>207</v>
       </c>
-      <c r="M4" s="279"/>
-      <c r="N4" s="254"/>
+      <c r="M4" s="252"/>
+      <c r="N4" s="235"/>
       <c r="O4" s="148"/>
       <c r="P4" s="154"/>
       <c r="Q4" s="179"/>
@@ -6664,32 +6664,32 @@
       <c r="AA4" s="78"/>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="249" t="s">
+      <c r="A5" s="231" t="s">
         <v>273</v>
       </c>
-      <c r="B5" s="274"/>
-      <c r="C5" s="250"/>
-      <c r="D5" s="247" t="s">
+      <c r="B5" s="232"/>
+      <c r="C5" s="233"/>
+      <c r="D5" s="228" t="s">
         <v>208</v>
       </c>
-      <c r="E5" s="248"/>
-      <c r="F5" s="247" t="s">
+      <c r="E5" s="230"/>
+      <c r="F5" s="228" t="s">
         <v>209</v>
       </c>
-      <c r="G5" s="248"/>
-      <c r="H5" s="247" t="s">
+      <c r="G5" s="230"/>
+      <c r="H5" s="228" t="s">
         <v>210</v>
       </c>
-      <c r="I5" s="248"/>
-      <c r="J5" s="247" t="s">
+      <c r="I5" s="230"/>
+      <c r="J5" s="228" t="s">
         <v>211</v>
       </c>
-      <c r="K5" s="248"/>
-      <c r="L5" s="247" t="s">
+      <c r="K5" s="230"/>
+      <c r="L5" s="228" t="s">
         <v>212</v>
       </c>
-      <c r="M5" s="275"/>
-      <c r="N5" s="248"/>
+      <c r="M5" s="229"/>
+      <c r="N5" s="230"/>
       <c r="O5" s="148"/>
       <c r="P5" s="154"/>
       <c r="Q5" s="147"/>
@@ -6705,34 +6705,34 @@
       <c r="AA5" s="78"/>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="247" t="s">
+      <c r="A6" s="228" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="275"/>
-      <c r="C6" s="248"/>
-      <c r="D6" s="233" t="s">
+      <c r="B6" s="229"/>
+      <c r="C6" s="230"/>
+      <c r="D6" s="268" t="s">
         <v>188</v>
       </c>
-      <c r="E6" s="234"/>
-      <c r="F6" s="231" t="str">
+      <c r="E6" s="269"/>
+      <c r="F6" s="273" t="str">
         <f>建船資料檔!B11</f>
         <v>1486/445</v>
       </c>
-      <c r="G6" s="232"/>
-      <c r="H6" s="233" t="s">
+      <c r="G6" s="274"/>
+      <c r="H6" s="268" t="s">
         <v>213</v>
       </c>
-      <c r="I6" s="234"/>
-      <c r="J6" s="240" t="str">
+      <c r="I6" s="269"/>
+      <c r="J6" s="241" t="str">
         <f>建船資料檔!B12</f>
         <v>115/7/27</v>
       </c>
       <c r="K6" s="242"/>
-      <c r="L6" s="240" t="str">
+      <c r="L6" s="241" t="str">
         <f>J6</f>
         <v>115/7/27</v>
       </c>
-      <c r="M6" s="241"/>
+      <c r="M6" s="299"/>
       <c r="N6" s="242"/>
       <c r="O6" s="189"/>
       <c r="P6" s="189"/>
@@ -6744,36 +6744,36 @@
       <c r="V6" s="186"/>
       <c r="W6" s="177"/>
       <c r="X6" s="77"/>
-      <c r="Y6" s="293"/>
-      <c r="Z6" s="293"/>
+      <c r="Y6" s="222"/>
+      <c r="Z6" s="222"/>
       <c r="AA6" s="78"/>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="249" t="s">
+      <c r="A7" s="231" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="274"/>
-      <c r="C7" s="250"/>
-      <c r="D7" s="253" t="s">
+      <c r="B7" s="232"/>
+      <c r="C7" s="233"/>
+      <c r="D7" s="234" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="254"/>
-      <c r="F7" s="253" t="s">
+      <c r="E7" s="235"/>
+      <c r="F7" s="234" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="254"/>
-      <c r="H7" s="253" t="s">
+      <c r="G7" s="235"/>
+      <c r="H7" s="234" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="254"/>
-      <c r="J7" s="253" t="s">
+      <c r="I7" s="235"/>
+      <c r="J7" s="234" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="254"/>
-      <c r="L7" s="253" t="s">
+      <c r="K7" s="235"/>
+      <c r="L7" s="234" t="s">
         <v>43</v>
       </c>
-      <c r="M7" s="254"/>
+      <c r="M7" s="235"/>
       <c r="N7" s="190" t="s">
         <v>44</v>
       </c>
@@ -6792,29 +6792,29 @@
       <c r="AA7" s="78"/>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="247" t="s">
+      <c r="A8" s="228" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="275"/>
-      <c r="C8" s="248"/>
-      <c r="D8" s="247" t="s">
+      <c r="B8" s="229"/>
+      <c r="C8" s="230"/>
+      <c r="D8" s="228" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="248"/>
-      <c r="F8" s="247" t="s">
+      <c r="E8" s="230"/>
+      <c r="F8" s="228" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="248"/>
-      <c r="H8" s="249"/>
-      <c r="I8" s="250"/>
-      <c r="J8" s="247" t="s">
+      <c r="G8" s="230"/>
+      <c r="H8" s="231"/>
+      <c r="I8" s="233"/>
+      <c r="J8" s="228" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="248"/>
-      <c r="L8" s="249" t="s">
+      <c r="K8" s="230"/>
+      <c r="L8" s="231" t="s">
         <v>49</v>
       </c>
-      <c r="M8" s="250"/>
+      <c r="M8" s="233"/>
       <c r="N8" s="197" t="s">
         <v>50</v>
       </c>
@@ -6828,29 +6828,29 @@
       <c r="V8" s="186"/>
       <c r="W8" s="177"/>
       <c r="X8" s="77"/>
-      <c r="Y8" s="293"/>
-      <c r="Z8" s="293"/>
+      <c r="Y8" s="222"/>
+      <c r="Z8" s="222"/>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="237" t="s">
+      <c r="A9" s="296" t="s">
         <v>152</v>
       </c>
-      <c r="B9" s="238"/>
-      <c r="C9" s="239"/>
-      <c r="D9" s="231" t="s">
+      <c r="B9" s="297"/>
+      <c r="C9" s="298"/>
+      <c r="D9" s="273" t="s">
         <v>225</v>
       </c>
-      <c r="E9" s="232"/>
-      <c r="F9" s="240"/>
+      <c r="E9" s="274"/>
+      <c r="F9" s="241"/>
       <c r="G9" s="242"/>
-      <c r="H9" s="263"/>
-      <c r="I9" s="234"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="234"/>
-      <c r="L9" s="233" t="s">
+      <c r="H9" s="285"/>
+      <c r="I9" s="269"/>
+      <c r="J9" s="268"/>
+      <c r="K9" s="269"/>
+      <c r="L9" s="268" t="s">
         <v>51</v>
       </c>
-      <c r="M9" s="234"/>
+      <c r="M9" s="269"/>
       <c r="N9" s="198"/>
       <c r="O9" s="189"/>
       <c r="P9" s="189"/>
@@ -6868,29 +6868,29 @@
       <c r="B10" s="170" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="245" t="s">
+      <c r="C10" s="260" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="246"/>
+      <c r="D10" s="261"/>
       <c r="E10" s="203" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="243" t="s">
+      <c r="F10" s="226" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="244"/>
+      <c r="G10" s="227"/>
       <c r="H10" s="170" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="245" t="s">
+      <c r="I10" s="260" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="246"/>
-      <c r="K10" s="255" t="s">
+      <c r="J10" s="261"/>
+      <c r="K10" s="277" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="256"/>
-      <c r="M10" s="257"/>
+      <c r="L10" s="278"/>
+      <c r="M10" s="279"/>
       <c r="N10" s="171" t="s">
         <v>59</v>
       </c>
@@ -6909,29 +6909,29 @@
       <c r="B11" s="173" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="227" t="s">
+      <c r="C11" s="236" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="228"/>
+      <c r="D11" s="237"/>
       <c r="E11" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="229" t="s">
+      <c r="F11" s="283" t="s">
         <v>64</v>
       </c>
-      <c r="G11" s="230"/>
+      <c r="G11" s="284"/>
       <c r="H11" s="173" t="s">
         <v>65</v>
       </c>
-      <c r="I11" s="227" t="s">
+      <c r="I11" s="236" t="s">
         <v>66</v>
       </c>
-      <c r="J11" s="228"/>
-      <c r="K11" s="264" t="s">
+      <c r="J11" s="237"/>
+      <c r="K11" s="286" t="s">
         <v>67</v>
       </c>
-      <c r="L11" s="265"/>
-      <c r="M11" s="266"/>
+      <c r="L11" s="287"/>
+      <c r="M11" s="288"/>
       <c r="N11" s="174" t="s">
         <v>68</v>
       </c>
@@ -6949,29 +6949,29 @@
       <c r="B12" s="172" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="227" t="s">
+      <c r="C12" s="236" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="228"/>
+      <c r="D12" s="237"/>
       <c r="E12" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="243" t="s">
+      <c r="F12" s="226" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="244"/>
+      <c r="G12" s="227"/>
       <c r="H12" s="173" t="s">
         <v>74</v>
       </c>
-      <c r="I12" s="258" t="s">
+      <c r="I12" s="255" t="s">
         <v>75</v>
       </c>
-      <c r="J12" s="259"/>
-      <c r="K12" s="260" t="s">
+      <c r="J12" s="256"/>
+      <c r="K12" s="280" t="s">
         <v>76</v>
       </c>
-      <c r="L12" s="261"/>
-      <c r="M12" s="262"/>
+      <c r="L12" s="281"/>
+      <c r="M12" s="282"/>
       <c r="N12" s="175" t="s">
         <v>226</v>
       </c>
@@ -6989,25 +6989,25 @@
       <c r="B13" s="173" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="227" t="s">
+      <c r="C13" s="236" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="228"/>
+      <c r="D13" s="237"/>
       <c r="E13" s="204"/>
-      <c r="F13" s="229" t="s">
+      <c r="F13" s="283" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="230"/>
+      <c r="G13" s="284"/>
       <c r="H13" s="173" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="258" t="s">
+      <c r="I13" s="255" t="s">
         <v>81</v>
       </c>
-      <c r="J13" s="259"/>
-      <c r="K13" s="282"/>
-      <c r="L13" s="283"/>
-      <c r="M13" s="284"/>
+      <c r="J13" s="256"/>
+      <c r="K13" s="257"/>
+      <c r="L13" s="258"/>
+      <c r="M13" s="259"/>
       <c r="N13" s="173" t="s">
         <v>82</v>
       </c>
@@ -7019,22 +7019,22 @@
       <c r="B14" s="173" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="227" t="s">
+      <c r="C14" s="236" t="s">
         <v>84</v>
       </c>
-      <c r="D14" s="228"/>
+      <c r="D14" s="237"/>
       <c r="E14" s="84"/>
-      <c r="F14" s="243" t="s">
+      <c r="F14" s="226" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="244"/>
+      <c r="G14" s="227"/>
       <c r="H14" s="173" t="s">
         <v>86</v>
       </c>
-      <c r="I14" s="258" t="s">
+      <c r="I14" s="255" t="s">
         <v>87</v>
       </c>
-      <c r="J14" s="259"/>
+      <c r="J14" s="256"/>
       <c r="K14" s="88"/>
       <c r="L14" s="89"/>
       <c r="M14" s="87"/>
@@ -7050,15 +7050,15 @@
       <c r="B15" s="199" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="295" t="s">
+      <c r="C15" s="224" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="296"/>
+      <c r="D15" s="225"/>
       <c r="E15" s="90"/>
-      <c r="F15" s="243" t="s">
+      <c r="F15" s="226" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="244"/>
+      <c r="G15" s="227"/>
       <c r="H15" s="90"/>
       <c r="I15" s="200"/>
       <c r="J15" s="202"/>
@@ -7089,11 +7089,11 @@
       <c r="E16" s="210" t="s">
         <v>263</v>
       </c>
-      <c r="F16" s="251" t="str">
+      <c r="F16" s="275" t="str">
         <f>T16&amp;"  "&amp;E16&amp;"/"&amp;U16&amp;"/"&amp;V16&amp;"/"&amp;P16</f>
         <v>EXPRESS PACKAGE  TCNU9125529/45G1/2/200405</v>
       </c>
-      <c r="G16" s="252"/>
+      <c r="G16" s="276"/>
       <c r="H16" s="127" t="s">
         <v>265</v>
       </c>
@@ -7103,11 +7103,11 @@
       <c r="J16" s="96" t="s">
         <v>235</v>
       </c>
-      <c r="K16" s="297" t="s">
+      <c r="K16" s="238" t="s">
         <v>266</v>
       </c>
-      <c r="L16" s="298"/>
-      <c r="M16" s="299"/>
+      <c r="L16" s="239"/>
+      <c r="M16" s="240"/>
       <c r="N16" s="149" t="s">
         <v>95</v>
       </c>
@@ -7149,49 +7149,117 @@
         <v>94</v>
       </c>
       <c r="E17" s="213"/>
-      <c r="F17" s="286"/>
-      <c r="G17" s="287"/>
+      <c r="F17" s="244"/>
+      <c r="G17" s="245"/>
       <c r="H17" s="212"/>
-      <c r="I17" s="288">
+      <c r="I17" s="246">
         <f>SUM(I16:J16)</f>
         <v>7137</v>
       </c>
-      <c r="J17" s="289"/>
-      <c r="K17" s="290"/>
-      <c r="L17" s="291"/>
-      <c r="M17" s="292"/>
+      <c r="J17" s="247"/>
+      <c r="K17" s="248"/>
+      <c r="L17" s="249"/>
+      <c r="M17" s="250"/>
       <c r="N17" s="211"/>
       <c r="T17" s="73"/>
       <c r="U17" s="184"/>
       <c r="V17" s="184"/>
     </row>
     <row r="18" spans="1:22">
-      <c r="A18" s="294" t="s">
+      <c r="A18" s="223" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="294"/>
-      <c r="H18" s="294"/>
-      <c r="I18" s="294"/>
-      <c r="J18" s="294"/>
-      <c r="K18" s="294"/>
+      <c r="B18" s="223"/>
+      <c r="H18" s="223"/>
+      <c r="I18" s="223"/>
+      <c r="J18" s="223"/>
+      <c r="K18" s="223"/>
     </row>
     <row r="19" spans="1:22">
-      <c r="A19" s="285" t="s">
+      <c r="A19" s="243" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="285"/>
-      <c r="H19" s="285" t="s">
+      <c r="B19" s="243"/>
+      <c r="H19" s="243" t="s">
         <v>99</v>
       </c>
-      <c r="I19" s="285"/>
-      <c r="J19" s="285"/>
-      <c r="K19" s="285"/>
+      <c r="I19" s="243"/>
+      <c r="J19" s="243"/>
+      <c r="K19" s="243"/>
     </row>
     <row r="21" spans="1:22">
       <c r="G21" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="84">
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:M17"/>
     <mergeCell ref="Y6:Z6"/>
     <mergeCell ref="Y8:Z8"/>
     <mergeCell ref="A18:B18"/>
@@ -7208,74 +7276,6 @@
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="K16:M16"/>
     <mergeCell ref="J6:K6"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="E3" s="106" t="str">
         <f>'貨櫃清單-1份'!J9</f>
-        <v>ESN501</v>
+        <v>ESN888</v>
       </c>
       <c r="F3" s="119" t="s">
         <v>249</v>
@@ -8235,28 +8235,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="C1" s="332" t="s">
+      <c r="C1" s="346" t="s">
         <v>100</v>
       </c>
-      <c r="D1" s="332"/>
-      <c r="E1" s="332"/>
-      <c r="F1" s="332"/>
-      <c r="G1" s="332"/>
-      <c r="H1" s="332"/>
+      <c r="D1" s="346"/>
+      <c r="E1" s="346"/>
+      <c r="F1" s="346"/>
+      <c r="G1" s="346"/>
+      <c r="H1" s="346"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="C2" s="332"/>
-      <c r="D2" s="332"/>
-      <c r="E2" s="332"/>
-      <c r="F2" s="332"/>
-      <c r="G2" s="332"/>
-      <c r="H2" s="332"/>
+      <c r="C2" s="346"/>
+      <c r="D2" s="346"/>
+      <c r="E2" s="346"/>
+      <c r="F2" s="346"/>
+      <c r="G2" s="346"/>
+      <c r="H2" s="346"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="333" t="s">
+      <c r="A3" s="347" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="334"/>
+      <c r="B3" s="348"/>
       <c r="H3" s="124" t="s">
         <v>251</v>
       </c>
@@ -8266,320 +8266,320 @@
       <c r="J3" s="142"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1">
-      <c r="A4" s="305" t="s">
+      <c r="A4" s="324" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="307"/>
-      <c r="C4" s="335" t="s">
+      <c r="B4" s="325"/>
+      <c r="C4" s="349" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="336"/>
-      <c r="E4" s="336"/>
-      <c r="F4" s="337"/>
+      <c r="D4" s="350"/>
+      <c r="E4" s="350"/>
+      <c r="F4" s="351"/>
       <c r="G4" s="191">
         <v>1312450</v>
       </c>
-      <c r="H4" s="317" t="s">
+      <c r="H4" s="302" t="s">
         <v>104</v>
       </c>
-      <c r="I4" s="341" t="str">
+      <c r="I4" s="300" t="str">
         <f>建船資料檔!B13</f>
         <v>115/7/27</v>
       </c>
       <c r="J4" s="161"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="308"/>
-      <c r="B5" s="310"/>
-      <c r="C5" s="338"/>
-      <c r="D5" s="339"/>
-      <c r="E5" s="339"/>
-      <c r="F5" s="340"/>
+      <c r="A5" s="328"/>
+      <c r="B5" s="329"/>
+      <c r="C5" s="352"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="353"/>
+      <c r="F5" s="354"/>
       <c r="G5" s="215"/>
-      <c r="H5" s="319"/>
-      <c r="I5" s="331"/>
+      <c r="H5" s="304"/>
+      <c r="I5" s="301"/>
       <c r="J5" s="161"/>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1">
-      <c r="A6" s="349" t="s">
+      <c r="A6" s="312" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="350"/>
-      <c r="C6" s="355" t="s">
+      <c r="B6" s="313"/>
+      <c r="C6" s="318" t="s">
         <v>264</v>
       </c>
-      <c r="D6" s="356"/>
-      <c r="E6" s="305" t="s">
+      <c r="D6" s="319"/>
+      <c r="E6" s="324" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="307"/>
-      <c r="G6" s="361" t="str">
+      <c r="F6" s="325"/>
+      <c r="G6" s="330" t="str">
         <f>進口艙單印1份!L3</f>
         <v>15PAHD</v>
       </c>
-      <c r="H6" s="317" t="s">
+      <c r="H6" s="302" t="s">
         <v>107</v>
       </c>
-      <c r="I6" s="317" t="s">
+      <c r="I6" s="302" t="s">
         <v>108</v>
       </c>
       <c r="J6" s="162"/>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1">
-      <c r="A7" s="351"/>
-      <c r="B7" s="352"/>
-      <c r="C7" s="357"/>
-      <c r="D7" s="358"/>
-      <c r="E7" s="313"/>
-      <c r="F7" s="314"/>
-      <c r="G7" s="362"/>
-      <c r="H7" s="318"/>
-      <c r="I7" s="318"/>
+      <c r="A7" s="314"/>
+      <c r="B7" s="315"/>
+      <c r="C7" s="320"/>
+      <c r="D7" s="321"/>
+      <c r="E7" s="326"/>
+      <c r="F7" s="327"/>
+      <c r="G7" s="331"/>
+      <c r="H7" s="303"/>
+      <c r="I7" s="303"/>
       <c r="J7" s="162"/>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1">
-      <c r="A8" s="351"/>
-      <c r="B8" s="352"/>
-      <c r="C8" s="357"/>
-      <c r="D8" s="358"/>
-      <c r="E8" s="313"/>
-      <c r="F8" s="314"/>
-      <c r="G8" s="362"/>
-      <c r="H8" s="318"/>
-      <c r="I8" s="318"/>
+      <c r="A8" s="314"/>
+      <c r="B8" s="315"/>
+      <c r="C8" s="320"/>
+      <c r="D8" s="321"/>
+      <c r="E8" s="326"/>
+      <c r="F8" s="327"/>
+      <c r="G8" s="331"/>
+      <c r="H8" s="303"/>
+      <c r="I8" s="303"/>
       <c r="J8" s="162"/>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1">
-      <c r="A9" s="353"/>
-      <c r="B9" s="354"/>
-      <c r="C9" s="359"/>
-      <c r="D9" s="360"/>
-      <c r="E9" s="308"/>
-      <c r="F9" s="310"/>
-      <c r="G9" s="363"/>
-      <c r="H9" s="319"/>
-      <c r="I9" s="319"/>
+      <c r="A9" s="316"/>
+      <c r="B9" s="317"/>
+      <c r="C9" s="322"/>
+      <c r="D9" s="323"/>
+      <c r="E9" s="328"/>
+      <c r="F9" s="329"/>
+      <c r="G9" s="332"/>
+      <c r="H9" s="304"/>
+      <c r="I9" s="304"/>
       <c r="J9" s="162"/>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1">
-      <c r="A10" s="349" t="s">
+      <c r="A10" s="312" t="s">
         <v>110</v>
       </c>
-      <c r="B10" s="350"/>
-      <c r="C10" s="376" t="s">
+      <c r="B10" s="313"/>
+      <c r="C10" s="345" t="s">
         <v>247</v>
       </c>
-      <c r="D10" s="356"/>
+      <c r="D10" s="319"/>
       <c r="E10" s="133" t="s">
         <v>111</v>
       </c>
       <c r="F10" s="134"/>
-      <c r="G10" s="329" t="str">
+      <c r="G10" s="364" t="str">
         <f>I4</f>
         <v>115/7/27</v>
       </c>
-      <c r="H10" s="317" t="s">
+      <c r="H10" s="302" t="s">
         <v>112</v>
       </c>
-      <c r="I10" s="317" t="s">
+      <c r="I10" s="302" t="s">
         <v>113</v>
       </c>
       <c r="J10" s="162"/>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1">
-      <c r="A11" s="351"/>
-      <c r="B11" s="352"/>
-      <c r="C11" s="357"/>
-      <c r="D11" s="358"/>
-      <c r="E11" s="313" t="s">
+      <c r="A11" s="314"/>
+      <c r="B11" s="315"/>
+      <c r="C11" s="320"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="326" t="s">
         <v>134</v>
       </c>
-      <c r="F11" s="314"/>
-      <c r="G11" s="330"/>
-      <c r="H11" s="318"/>
-      <c r="I11" s="318"/>
+      <c r="F11" s="327"/>
+      <c r="G11" s="365"/>
+      <c r="H11" s="303"/>
+      <c r="I11" s="303"/>
       <c r="J11" s="162"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1">
-      <c r="A12" s="351"/>
-      <c r="B12" s="352"/>
-      <c r="C12" s="357"/>
-      <c r="D12" s="358"/>
-      <c r="E12" s="313"/>
-      <c r="F12" s="314"/>
-      <c r="G12" s="330"/>
-      <c r="H12" s="318"/>
-      <c r="I12" s="318"/>
+      <c r="A12" s="314"/>
+      <c r="B12" s="315"/>
+      <c r="C12" s="320"/>
+      <c r="D12" s="321"/>
+      <c r="E12" s="326"/>
+      <c r="F12" s="327"/>
+      <c r="G12" s="365"/>
+      <c r="H12" s="303"/>
+      <c r="I12" s="303"/>
       <c r="J12" s="162"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1">
-      <c r="A13" s="353"/>
-      <c r="B13" s="354"/>
-      <c r="C13" s="359"/>
-      <c r="D13" s="360"/>
+      <c r="A13" s="316"/>
+      <c r="B13" s="317"/>
+      <c r="C13" s="322"/>
+      <c r="D13" s="323"/>
       <c r="E13" s="135" t="s">
         <v>114</v>
       </c>
       <c r="F13" s="136"/>
-      <c r="G13" s="331"/>
-      <c r="H13" s="319"/>
-      <c r="I13" s="319"/>
+      <c r="G13" s="301"/>
+      <c r="H13" s="304"/>
+      <c r="I13" s="304"/>
       <c r="J13" s="162"/>
     </row>
     <row r="14" spans="1:10" ht="18" customHeight="1">
-      <c r="A14" s="364" t="s">
+      <c r="A14" s="333" t="s">
         <v>115</v>
       </c>
-      <c r="B14" s="367" t="s">
+      <c r="B14" s="336" t="s">
         <v>116</v>
       </c>
       <c r="C14" s="133" t="s">
         <v>117</v>
       </c>
       <c r="D14" s="134"/>
-      <c r="E14" s="370" t="s">
+      <c r="E14" s="339" t="s">
         <v>243</v>
       </c>
-      <c r="F14" s="371"/>
-      <c r="G14" s="320" t="s">
+      <c r="F14" s="340"/>
+      <c r="G14" s="355" t="s">
         <v>236</v>
       </c>
-      <c r="H14" s="321"/>
-      <c r="I14" s="322"/>
+      <c r="H14" s="356"/>
+      <c r="I14" s="357"/>
       <c r="J14" s="151"/>
     </row>
     <row r="15" spans="1:10" ht="18" customHeight="1">
-      <c r="A15" s="365"/>
-      <c r="B15" s="368"/>
+      <c r="A15" s="334"/>
+      <c r="B15" s="337"/>
       <c r="C15" s="138" t="s">
         <v>118</v>
       </c>
       <c r="D15" s="139"/>
-      <c r="E15" s="372"/>
-      <c r="F15" s="373"/>
-      <c r="G15" s="323" t="s">
+      <c r="E15" s="341"/>
+      <c r="F15" s="342"/>
+      <c r="G15" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="H15" s="324"/>
-      <c r="I15" s="325"/>
+      <c r="H15" s="359"/>
+      <c r="I15" s="360"/>
       <c r="J15" s="151"/>
     </row>
     <row r="16" spans="1:10" ht="18" customHeight="1">
-      <c r="A16" s="365"/>
-      <c r="B16" s="368"/>
+      <c r="A16" s="334"/>
+      <c r="B16" s="337"/>
       <c r="C16" s="138" t="s">
         <v>119</v>
       </c>
       <c r="D16" s="139"/>
-      <c r="E16" s="372"/>
-      <c r="F16" s="373"/>
-      <c r="G16" s="323" t="s">
+      <c r="E16" s="341"/>
+      <c r="F16" s="342"/>
+      <c r="G16" s="358" t="s">
         <v>238</v>
       </c>
-      <c r="H16" s="324"/>
-      <c r="I16" s="325"/>
+      <c r="H16" s="359"/>
+      <c r="I16" s="360"/>
       <c r="J16" s="151"/>
     </row>
     <row r="17" spans="1:12" ht="18" customHeight="1">
-      <c r="A17" s="365"/>
-      <c r="B17" s="368"/>
+      <c r="A17" s="334"/>
+      <c r="B17" s="337"/>
       <c r="C17" s="138" t="s">
         <v>120</v>
       </c>
       <c r="D17" s="139"/>
-      <c r="E17" s="372"/>
-      <c r="F17" s="373"/>
-      <c r="G17" s="323" t="s">
+      <c r="E17" s="341"/>
+      <c r="F17" s="342"/>
+      <c r="G17" s="358" t="s">
         <v>239</v>
       </c>
-      <c r="H17" s="324"/>
-      <c r="I17" s="325"/>
+      <c r="H17" s="359"/>
+      <c r="I17" s="360"/>
       <c r="J17" s="151"/>
       <c r="L17" s="12"/>
     </row>
     <row r="18" spans="1:12" ht="18" customHeight="1">
-      <c r="A18" s="365"/>
-      <c r="B18" s="368"/>
+      <c r="A18" s="334"/>
+      <c r="B18" s="337"/>
       <c r="C18" s="138" t="s">
         <v>121</v>
       </c>
       <c r="D18" s="139"/>
-      <c r="E18" s="372"/>
-      <c r="F18" s="373"/>
-      <c r="G18" s="323" t="s">
+      <c r="E18" s="341"/>
+      <c r="F18" s="342"/>
+      <c r="G18" s="358" t="s">
         <v>240</v>
       </c>
-      <c r="H18" s="324"/>
-      <c r="I18" s="325"/>
+      <c r="H18" s="359"/>
+      <c r="I18" s="360"/>
       <c r="J18" s="151"/>
     </row>
     <row r="19" spans="1:12" ht="18" customHeight="1">
-      <c r="A19" s="366"/>
-      <c r="B19" s="369"/>
+      <c r="A19" s="335"/>
+      <c r="B19" s="338"/>
       <c r="C19" s="135"/>
       <c r="D19" s="136"/>
-      <c r="E19" s="374"/>
-      <c r="F19" s="375"/>
-      <c r="G19" s="326" t="s">
+      <c r="E19" s="343"/>
+      <c r="F19" s="344"/>
+      <c r="G19" s="361" t="s">
         <v>245</v>
       </c>
-      <c r="H19" s="327"/>
-      <c r="I19" s="328"/>
+      <c r="H19" s="362"/>
+      <c r="I19" s="363"/>
       <c r="J19" s="151"/>
     </row>
     <row r="20" spans="1:12" ht="18" customHeight="1">
-      <c r="A20" s="303" t="s">
+      <c r="A20" s="369" t="s">
         <v>122</v>
       </c>
-      <c r="B20" s="304"/>
-      <c r="C20" s="305" t="s">
+      <c r="B20" s="370"/>
+      <c r="C20" s="324" t="s">
         <v>123</v>
       </c>
-      <c r="D20" s="306"/>
-      <c r="E20" s="307"/>
-      <c r="F20" s="305" t="s">
+      <c r="D20" s="371"/>
+      <c r="E20" s="325"/>
+      <c r="F20" s="324" t="s">
         <v>190</v>
       </c>
-      <c r="G20" s="307"/>
-      <c r="H20" s="315" t="s">
+      <c r="G20" s="325"/>
+      <c r="H20" s="375" t="s">
         <v>189</v>
       </c>
-      <c r="I20" s="317" t="s">
+      <c r="I20" s="302" t="s">
         <v>143</v>
       </c>
       <c r="J20" s="162"/>
     </row>
     <row r="21" spans="1:12" ht="18" customHeight="1">
-      <c r="A21" s="311" t="s">
+      <c r="A21" s="373" t="s">
         <v>124</v>
       </c>
-      <c r="B21" s="312"/>
-      <c r="C21" s="308"/>
-      <c r="D21" s="309"/>
-      <c r="E21" s="310"/>
-      <c r="F21" s="308"/>
-      <c r="G21" s="310"/>
-      <c r="H21" s="316"/>
-      <c r="I21" s="319"/>
+      <c r="B21" s="374"/>
+      <c r="C21" s="328"/>
+      <c r="D21" s="372"/>
+      <c r="E21" s="329"/>
+      <c r="F21" s="328"/>
+      <c r="G21" s="329"/>
+      <c r="H21" s="376"/>
+      <c r="I21" s="304"/>
       <c r="J21" s="162"/>
     </row>
     <row r="22" spans="1:12" s="45" customFormat="1" ht="21" customHeight="1">
-      <c r="A22" s="344" t="str">
+      <c r="A22" s="307" t="str">
         <f>進口艙單印1份!B16</f>
         <v>5501</v>
       </c>
-      <c r="B22" s="345"/>
-      <c r="C22" s="346" t="str">
+      <c r="B22" s="308"/>
+      <c r="C22" s="309" t="str">
         <f>進口艙單印1份!T16</f>
         <v>EXPRESS PACKAGE</v>
       </c>
-      <c r="D22" s="347"/>
-      <c r="E22" s="348"/>
-      <c r="F22" s="342" t="str">
+      <c r="D22" s="310"/>
+      <c r="E22" s="311"/>
+      <c r="F22" s="305" t="str">
         <f>進口艙單印1份!C16&amp;進口艙單印1份!D16</f>
         <v>1599PKG</v>
       </c>
-      <c r="G22" s="343"/>
+      <c r="G22" s="306"/>
       <c r="H22" s="216">
         <f>進口艙單印1份!I16</f>
         <v>7137</v>
@@ -8591,16 +8591,16 @@
       <c r="J22" s="163"/>
     </row>
     <row r="23" spans="1:12" ht="18" customHeight="1">
-      <c r="A23" s="300" t="s">
+      <c r="A23" s="366" t="s">
         <v>125</v>
       </c>
-      <c r="B23" s="301"/>
-      <c r="C23" s="301"/>
-      <c r="D23" s="301"/>
-      <c r="E23" s="301"/>
-      <c r="F23" s="301"/>
-      <c r="G23" s="301"/>
-      <c r="H23" s="302"/>
+      <c r="B23" s="367"/>
+      <c r="C23" s="367"/>
+      <c r="D23" s="367"/>
+      <c r="E23" s="367"/>
+      <c r="F23" s="367"/>
+      <c r="G23" s="367"/>
+      <c r="H23" s="368"/>
       <c r="I23" s="159" t="s">
         <v>241</v>
       </c>
@@ -8766,6 +8766,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:E21"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="F20:G21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="I10:I13"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="C1:H2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:F5"/>
+    <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="I6:I9"/>
     <mergeCell ref="F22:G22"/>
@@ -8782,27 +8803,6 @@
     <mergeCell ref="A10:B13"/>
     <mergeCell ref="C10:D13"/>
     <mergeCell ref="H10:H13"/>
-    <mergeCell ref="C1:H2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="C4:F5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I10:I13"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:E21"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="F20:G21"/>
-    <mergeCell ref="H20:H21"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -9525,28 +9525,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="C1" s="332" t="s">
+      <c r="C1" s="346" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="332"/>
-      <c r="E1" s="332"/>
-      <c r="F1" s="332"/>
-      <c r="G1" s="332"/>
-      <c r="H1" s="332"/>
+      <c r="D1" s="346"/>
+      <c r="E1" s="346"/>
+      <c r="F1" s="346"/>
+      <c r="G1" s="346"/>
+      <c r="H1" s="346"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="C2" s="332"/>
-      <c r="D2" s="332"/>
-      <c r="E2" s="332"/>
-      <c r="F2" s="332"/>
-      <c r="G2" s="332"/>
-      <c r="H2" s="332"/>
+      <c r="C2" s="346"/>
+      <c r="D2" s="346"/>
+      <c r="E2" s="346"/>
+      <c r="F2" s="346"/>
+      <c r="G2" s="346"/>
+      <c r="H2" s="346"/>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="383" t="s">
+      <c r="A3" s="402" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="383"/>
+      <c r="B3" s="402"/>
       <c r="H3" s="125" t="str">
         <f>'准單(紅紙)-2份'!H3</f>
         <v>准單編號:料</v>
@@ -9558,340 +9558,340 @@
       <c r="J3" s="17"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
-      <c r="A4" s="305" t="s">
+      <c r="A4" s="324" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="307"/>
-      <c r="C4" s="335" t="str">
+      <c r="B4" s="325"/>
+      <c r="C4" s="349" t="str">
         <f>'准單(紅紙)-2份'!C4:F5</f>
         <v>新銳船務代理有限公司</v>
       </c>
-      <c r="D4" s="384"/>
-      <c r="E4" s="384"/>
-      <c r="F4" s="385"/>
+      <c r="D4" s="391"/>
+      <c r="E4" s="391"/>
+      <c r="F4" s="392"/>
       <c r="G4" s="191">
         <v>1312450</v>
       </c>
-      <c r="H4" s="317" t="s">
+      <c r="H4" s="302" t="s">
         <v>128</v>
       </c>
-      <c r="I4" s="341" t="str">
+      <c r="I4" s="300" t="str">
         <f>'准單(紅紙)-2份'!I4:J5</f>
         <v>115/7/27</v>
       </c>
       <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
-      <c r="A5" s="308"/>
-      <c r="B5" s="310"/>
-      <c r="C5" s="386"/>
-      <c r="D5" s="387"/>
-      <c r="E5" s="387"/>
-      <c r="F5" s="388"/>
+      <c r="A5" s="328"/>
+      <c r="B5" s="329"/>
+      <c r="C5" s="393"/>
+      <c r="D5" s="394"/>
+      <c r="E5" s="394"/>
+      <c r="F5" s="395"/>
       <c r="G5" s="215"/>
-      <c r="H5" s="319"/>
-      <c r="I5" s="331"/>
+      <c r="H5" s="304"/>
+      <c r="I5" s="301"/>
       <c r="J5" s="18"/>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
-      <c r="A6" s="349" t="s">
+      <c r="A6" s="312" t="s">
         <v>129</v>
       </c>
-      <c r="B6" s="350"/>
-      <c r="C6" s="377" t="str">
+      <c r="B6" s="313"/>
+      <c r="C6" s="396" t="str">
         <f>'准單(紅紙)-2份'!C6:D9</f>
         <v>大佑輪</v>
       </c>
-      <c r="D6" s="378"/>
-      <c r="E6" s="305" t="s">
+      <c r="D6" s="397"/>
+      <c r="E6" s="324" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="307"/>
-      <c r="G6" s="361" t="str">
+      <c r="F6" s="325"/>
+      <c r="G6" s="330" t="str">
         <f>'准單(紅紙)-2份'!G6:G9</f>
         <v>15PAHD</v>
       </c>
-      <c r="H6" s="317" t="s">
+      <c r="H6" s="302" t="s">
         <v>130</v>
       </c>
-      <c r="I6" s="317" t="s">
+      <c r="I6" s="302" t="s">
         <v>131</v>
       </c>
       <c r="J6" s="19"/>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
-      <c r="A7" s="351"/>
-      <c r="B7" s="352"/>
-      <c r="C7" s="379"/>
-      <c r="D7" s="380"/>
-      <c r="E7" s="313"/>
-      <c r="F7" s="314"/>
-      <c r="G7" s="362"/>
-      <c r="H7" s="318"/>
-      <c r="I7" s="318"/>
+      <c r="A7" s="314"/>
+      <c r="B7" s="315"/>
+      <c r="C7" s="398"/>
+      <c r="D7" s="399"/>
+      <c r="E7" s="326"/>
+      <c r="F7" s="327"/>
+      <c r="G7" s="331"/>
+      <c r="H7" s="303"/>
+      <c r="I7" s="303"/>
       <c r="J7" s="19"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1">
-      <c r="A8" s="351"/>
-      <c r="B8" s="352"/>
-      <c r="C8" s="379"/>
-      <c r="D8" s="380"/>
-      <c r="E8" s="313"/>
-      <c r="F8" s="314"/>
-      <c r="G8" s="362"/>
-      <c r="H8" s="318"/>
-      <c r="I8" s="318"/>
+      <c r="A8" s="314"/>
+      <c r="B8" s="315"/>
+      <c r="C8" s="398"/>
+      <c r="D8" s="399"/>
+      <c r="E8" s="326"/>
+      <c r="F8" s="327"/>
+      <c r="G8" s="331"/>
+      <c r="H8" s="303"/>
+      <c r="I8" s="303"/>
       <c r="J8" s="19"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
-      <c r="A9" s="353"/>
-      <c r="B9" s="354"/>
-      <c r="C9" s="381"/>
-      <c r="D9" s="382"/>
-      <c r="E9" s="308"/>
-      <c r="F9" s="310"/>
-      <c r="G9" s="363"/>
-      <c r="H9" s="319"/>
-      <c r="I9" s="319"/>
+      <c r="A9" s="316"/>
+      <c r="B9" s="317"/>
+      <c r="C9" s="400"/>
+      <c r="D9" s="401"/>
+      <c r="E9" s="328"/>
+      <c r="F9" s="329"/>
+      <c r="G9" s="332"/>
+      <c r="H9" s="304"/>
+      <c r="I9" s="304"/>
       <c r="J9" s="19"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
-      <c r="A10" s="349" t="s">
+      <c r="A10" s="312" t="s">
         <v>110</v>
       </c>
-      <c r="B10" s="350"/>
-      <c r="C10" s="305" t="str">
+      <c r="B10" s="313"/>
+      <c r="C10" s="324" t="str">
         <f>'准單(紅紙)-2份'!C10:D13</f>
         <v>KHH0638S</v>
       </c>
-      <c r="D10" s="307"/>
+      <c r="D10" s="325"/>
       <c r="E10" s="133" t="s">
         <v>111</v>
       </c>
       <c r="F10" s="134"/>
-      <c r="G10" s="341" t="str">
+      <c r="G10" s="300" t="str">
         <f>I4</f>
         <v>115/7/27</v>
       </c>
-      <c r="H10" s="317" t="s">
+      <c r="H10" s="302" t="s">
         <v>132</v>
       </c>
-      <c r="I10" s="317" t="s">
+      <c r="I10" s="302" t="s">
         <v>133</v>
       </c>
       <c r="J10" s="138"/>
       <c r="K10" s="144"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
-      <c r="A11" s="351"/>
-      <c r="B11" s="352"/>
-      <c r="C11" s="313"/>
-      <c r="D11" s="314"/>
-      <c r="E11" s="313" t="s">
+      <c r="A11" s="314"/>
+      <c r="B11" s="315"/>
+      <c r="C11" s="326"/>
+      <c r="D11" s="327"/>
+      <c r="E11" s="326" t="s">
         <v>134</v>
       </c>
-      <c r="F11" s="314"/>
-      <c r="G11" s="330"/>
-      <c r="H11" s="318"/>
-      <c r="I11" s="318"/>
+      <c r="F11" s="327"/>
+      <c r="G11" s="365"/>
+      <c r="H11" s="303"/>
+      <c r="I11" s="303"/>
       <c r="J11" s="138"/>
       <c r="K11" s="144"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
-      <c r="A12" s="351"/>
-      <c r="B12" s="352"/>
-      <c r="C12" s="313"/>
-      <c r="D12" s="314"/>
-      <c r="E12" s="313"/>
-      <c r="F12" s="314"/>
-      <c r="G12" s="330"/>
-      <c r="H12" s="318"/>
-      <c r="I12" s="318"/>
+      <c r="A12" s="314"/>
+      <c r="B12" s="315"/>
+      <c r="C12" s="326"/>
+      <c r="D12" s="327"/>
+      <c r="E12" s="326"/>
+      <c r="F12" s="327"/>
+      <c r="G12" s="365"/>
+      <c r="H12" s="303"/>
+      <c r="I12" s="303"/>
       <c r="J12" s="138"/>
       <c r="K12" s="144"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
-      <c r="A13" s="353"/>
-      <c r="B13" s="354"/>
-      <c r="C13" s="308"/>
-      <c r="D13" s="310"/>
+      <c r="A13" s="316"/>
+      <c r="B13" s="317"/>
+      <c r="C13" s="328"/>
+      <c r="D13" s="329"/>
       <c r="E13" s="135" t="s">
         <v>114</v>
       </c>
       <c r="F13" s="136"/>
-      <c r="G13" s="331"/>
-      <c r="H13" s="319"/>
-      <c r="I13" s="319"/>
+      <c r="G13" s="301"/>
+      <c r="H13" s="304"/>
+      <c r="I13" s="304"/>
       <c r="J13" s="138"/>
       <c r="K13" s="144"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1">
-      <c r="A14" s="364" t="s">
+      <c r="A14" s="333" t="s">
         <v>135</v>
       </c>
-      <c r="B14" s="367" t="s">
+      <c r="B14" s="336" t="s">
         <v>136</v>
       </c>
       <c r="C14" s="133" t="s">
         <v>137</v>
       </c>
       <c r="D14" s="134"/>
-      <c r="E14" s="370" t="s">
+      <c r="E14" s="339" t="s">
         <v>243</v>
       </c>
-      <c r="F14" s="371"/>
-      <c r="G14" s="320" t="str">
+      <c r="F14" s="340"/>
+      <c r="G14" s="355" t="str">
         <f>'准單(紅紙)-2份'!G14:I14</f>
         <v>1.將貨櫃卸存本站或內陸集散站（進口報關放行）。</v>
       </c>
-      <c r="H14" s="321"/>
-      <c r="I14" s="322"/>
+      <c r="H14" s="356"/>
+      <c r="I14" s="357"/>
       <c r="J14" s="138"/>
       <c r="K14" s="144"/>
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1">
-      <c r="A15" s="365"/>
-      <c r="B15" s="368"/>
+      <c r="A15" s="334"/>
+      <c r="B15" s="337"/>
       <c r="C15" s="138" t="s">
         <v>138</v>
       </c>
       <c r="D15" s="139"/>
-      <c r="E15" s="372"/>
-      <c r="F15" s="373"/>
-      <c r="G15" s="323" t="str">
+      <c r="E15" s="341"/>
+      <c r="F15" s="342"/>
+      <c r="G15" s="358" t="str">
         <f>'准單(紅紙)-2份'!G15:I15</f>
         <v>2.將非櫃裝貨物押運或監視進倉存放。</v>
       </c>
-      <c r="H15" s="324"/>
-      <c r="I15" s="325"/>
+      <c r="H15" s="359"/>
+      <c r="I15" s="360"/>
       <c r="J15" s="138"/>
       <c r="K15" s="144"/>
     </row>
     <row r="16" spans="1:11" ht="18" customHeight="1">
-      <c r="A16" s="365"/>
-      <c r="B16" s="368"/>
+      <c r="A16" s="334"/>
+      <c r="B16" s="337"/>
       <c r="C16" s="138" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="139"/>
-      <c r="E16" s="372"/>
-      <c r="F16" s="373"/>
-      <c r="G16" s="323" t="str">
+      <c r="E16" s="341"/>
+      <c r="F16" s="342"/>
+      <c r="G16" s="358" t="str">
         <f>'准單(紅紙)-2份'!G16:I16</f>
         <v>3.船邊免驗提貨（櫃）。4.船邊驗放。</v>
       </c>
-      <c r="H16" s="324"/>
-      <c r="I16" s="325"/>
+      <c r="H16" s="359"/>
+      <c r="I16" s="360"/>
       <c r="J16" s="160"/>
       <c r="K16" s="144"/>
     </row>
     <row r="17" spans="1:11" ht="18" customHeight="1">
-      <c r="A17" s="365"/>
-      <c r="B17" s="368"/>
+      <c r="A17" s="334"/>
+      <c r="B17" s="337"/>
       <c r="C17" s="138" t="s">
         <v>140</v>
       </c>
       <c r="D17" s="139"/>
-      <c r="E17" s="372"/>
-      <c r="F17" s="373"/>
-      <c r="G17" s="323" t="str">
+      <c r="E17" s="341"/>
+      <c r="F17" s="342"/>
+      <c r="G17" s="358" t="str">
         <f>'准單(紅紙)-2份'!G17:I17</f>
         <v>5.將轉口貨櫃或空櫃卸運入站.6.公證。7重新包裝。</v>
       </c>
-      <c r="H17" s="324"/>
-      <c r="I17" s="325"/>
+      <c r="H17" s="359"/>
+      <c r="I17" s="360"/>
       <c r="J17" s="138"/>
       <c r="K17" s="144"/>
     </row>
     <row r="18" spans="1:11" ht="18" customHeight="1">
-      <c r="A18" s="365"/>
-      <c r="B18" s="368"/>
+      <c r="A18" s="334"/>
+      <c r="B18" s="337"/>
       <c r="C18" s="138" t="s">
         <v>121</v>
       </c>
       <c r="D18" s="217"/>
-      <c r="E18" s="372"/>
-      <c r="F18" s="373"/>
-      <c r="G18" s="323" t="str">
+      <c r="E18" s="341"/>
+      <c r="F18" s="342"/>
+      <c r="G18" s="358" t="str">
         <f>'准單(紅紙)-2份'!G18:I18</f>
         <v>8.換櫃.9.轉運他關區貨櫃。</v>
       </c>
-      <c r="H18" s="324"/>
-      <c r="I18" s="325"/>
+      <c r="H18" s="359"/>
+      <c r="I18" s="360"/>
       <c r="J18" s="160"/>
       <c r="K18" s="144"/>
     </row>
     <row r="19" spans="1:11" ht="18" customHeight="1">
-      <c r="A19" s="366"/>
-      <c r="B19" s="369"/>
+      <c r="A19" s="335"/>
+      <c r="B19" s="338"/>
       <c r="C19" s="135"/>
       <c r="D19" s="136"/>
-      <c r="E19" s="374"/>
-      <c r="F19" s="375"/>
-      <c r="G19" s="326" t="str">
+      <c r="E19" s="343"/>
+      <c r="F19" s="344"/>
+      <c r="G19" s="361" t="str">
         <f>'准單(紅紙)-2份'!G19:J19</f>
         <v xml:space="preserve">10.其他:轉運至高雄港(KHH0638S ) </v>
       </c>
-      <c r="H19" s="327"/>
-      <c r="I19" s="328"/>
+      <c r="H19" s="362"/>
+      <c r="I19" s="363"/>
       <c r="J19" s="138"/>
       <c r="K19" s="144"/>
     </row>
     <row r="20" spans="1:11" ht="18" customHeight="1">
-      <c r="A20" s="303" t="s">
+      <c r="A20" s="369" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="304"/>
-      <c r="C20" s="305" t="s">
+      <c r="B20" s="370"/>
+      <c r="C20" s="324" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="306"/>
-      <c r="E20" s="307"/>
-      <c r="F20" s="305" t="s">
+      <c r="D20" s="371"/>
+      <c r="E20" s="325"/>
+      <c r="F20" s="324" t="s">
         <v>192</v>
       </c>
-      <c r="G20" s="307"/>
-      <c r="H20" s="315" t="s">
+      <c r="G20" s="325"/>
+      <c r="H20" s="375" t="s">
         <v>191</v>
       </c>
-      <c r="I20" s="317" t="s">
+      <c r="I20" s="302" t="s">
         <v>143</v>
       </c>
       <c r="J20" s="164"/>
       <c r="K20" s="144"/>
     </row>
     <row r="21" spans="1:11" ht="18" customHeight="1">
-      <c r="A21" s="311" t="s">
+      <c r="A21" s="373" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="312"/>
-      <c r="C21" s="308"/>
-      <c r="D21" s="309"/>
-      <c r="E21" s="310"/>
-      <c r="F21" s="308"/>
-      <c r="G21" s="310"/>
-      <c r="H21" s="316"/>
-      <c r="I21" s="319"/>
+      <c r="B21" s="374"/>
+      <c r="C21" s="328"/>
+      <c r="D21" s="372"/>
+      <c r="E21" s="329"/>
+      <c r="F21" s="328"/>
+      <c r="G21" s="329"/>
+      <c r="H21" s="376"/>
+      <c r="I21" s="304"/>
       <c r="J21" s="164"/>
       <c r="K21" s="144"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="21" customHeight="1">
-      <c r="A22" s="389" t="str">
+      <c r="A22" s="388" t="str">
         <f>'准單(紅紙)-2份'!A22:B22</f>
         <v>5501</v>
       </c>
-      <c r="B22" s="345"/>
-      <c r="C22" s="346" t="str">
+      <c r="B22" s="308"/>
+      <c r="C22" s="309" t="str">
         <f>'准單(紅紙)-2份'!C22:E22</f>
         <v>EXPRESS PACKAGE</v>
       </c>
-      <c r="D22" s="347"/>
-      <c r="E22" s="348"/>
-      <c r="F22" s="390" t="str">
+      <c r="D22" s="310"/>
+      <c r="E22" s="311"/>
+      <c r="F22" s="389" t="str">
         <f>'准單(紅紙)-2份'!F22:H22</f>
         <v>1599PKG</v>
       </c>
-      <c r="G22" s="391"/>
+      <c r="G22" s="390"/>
       <c r="H22" s="218">
         <f>'准單(紅紙)-2份'!H22</f>
         <v>7137</v>
@@ -9983,72 +9983,72 @@
       <c r="J28" s="11"/>
     </row>
     <row r="29" spans="1:11" ht="24" customHeight="1">
-      <c r="A29" s="392" t="s">
+      <c r="A29" s="377" t="s">
         <v>148</v>
       </c>
-      <c r="B29" s="395" t="s">
+      <c r="B29" s="380" t="s">
         <v>149</v>
       </c>
       <c r="C29" s="134"/>
-      <c r="D29" s="395" t="s">
+      <c r="D29" s="380" t="s">
         <v>150</v>
       </c>
       <c r="E29" s="137"/>
       <c r="F29" s="134"/>
-      <c r="G29" s="400" t="s">
+      <c r="G29" s="385" t="s">
         <v>254</v>
       </c>
-      <c r="H29" s="400" t="s">
+      <c r="H29" s="385" t="s">
         <v>255</v>
       </c>
       <c r="I29" s="165"/>
       <c r="J29" s="11"/>
     </row>
     <row r="30" spans="1:11" ht="24" customHeight="1">
-      <c r="A30" s="393"/>
-      <c r="B30" s="396"/>
+      <c r="A30" s="378"/>
+      <c r="B30" s="381"/>
       <c r="C30" s="139"/>
-      <c r="D30" s="398"/>
+      <c r="D30" s="383"/>
       <c r="E30" s="140"/>
       <c r="F30" s="139"/>
-      <c r="G30" s="401"/>
-      <c r="H30" s="401"/>
+      <c r="G30" s="386"/>
+      <c r="H30" s="386"/>
       <c r="I30" s="143"/>
       <c r="J30" s="11"/>
     </row>
     <row r="31" spans="1:11" ht="24" customHeight="1">
-      <c r="A31" s="393"/>
-      <c r="B31" s="396"/>
+      <c r="A31" s="378"/>
+      <c r="B31" s="381"/>
       <c r="C31" s="139"/>
-      <c r="D31" s="398"/>
+      <c r="D31" s="383"/>
       <c r="E31" s="140"/>
       <c r="F31" s="139"/>
-      <c r="G31" s="401"/>
-      <c r="H31" s="401"/>
+      <c r="G31" s="386"/>
+      <c r="H31" s="386"/>
       <c r="I31" s="143"/>
       <c r="J31" s="11"/>
     </row>
     <row r="32" spans="1:11" ht="24" customHeight="1">
-      <c r="A32" s="393"/>
-      <c r="B32" s="396"/>
+      <c r="A32" s="378"/>
+      <c r="B32" s="381"/>
       <c r="C32" s="139"/>
-      <c r="D32" s="398"/>
+      <c r="D32" s="383"/>
       <c r="E32" s="140"/>
       <c r="F32" s="139"/>
-      <c r="G32" s="401"/>
-      <c r="H32" s="401"/>
+      <c r="G32" s="386"/>
+      <c r="H32" s="386"/>
       <c r="I32" s="143"/>
       <c r="J32" s="11"/>
     </row>
     <row r="33" spans="1:10" ht="24" customHeight="1">
-      <c r="A33" s="394"/>
-      <c r="B33" s="397"/>
+      <c r="A33" s="379"/>
+      <c r="B33" s="382"/>
       <c r="C33" s="146"/>
-      <c r="D33" s="399"/>
+      <c r="D33" s="384"/>
       <c r="E33" s="21"/>
       <c r="F33" s="146"/>
-      <c r="G33" s="402"/>
-      <c r="H33" s="402"/>
+      <c r="G33" s="387"/>
+      <c r="H33" s="387"/>
       <c r="I33" s="219"/>
       <c r="J33" s="22"/>
     </row>
@@ -10114,31 +10114,6 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A29:A33"/>
-    <mergeCell ref="B29:B33"/>
-    <mergeCell ref="D29:D33"/>
-    <mergeCell ref="G29:G33"/>
-    <mergeCell ref="H29:H33"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F20:G21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="I10:I13"/>
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="C4:F5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="A6:B9"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="I6:I9"/>
     <mergeCell ref="C1:H2"/>
     <mergeCell ref="A10:B13"/>
     <mergeCell ref="C10:D13"/>
@@ -10155,6 +10130,31 @@
     <mergeCell ref="E14:F19"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="G16:I16"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:F5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="A6:B9"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="I6:I9"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="I10:I13"/>
+    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F20:G21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="A29:A33"/>
+    <mergeCell ref="B29:B33"/>
+    <mergeCell ref="D29:D33"/>
+    <mergeCell ref="G29:G33"/>
+    <mergeCell ref="H29:H33"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -10185,22 +10185,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="46.5" customHeight="1">
-      <c r="A1" s="419" t="s">
+      <c r="A1" s="413" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="419"/>
+      <c r="B1" s="413"/>
       <c r="C1" s="3"/>
       <c r="D1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="420" t="s">
+      <c r="E1" s="414" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="420"/>
-      <c r="G1" s="421" t="s">
+      <c r="F1" s="414"/>
+      <c r="G1" s="415" t="s">
         <v>186</v>
       </c>
-      <c r="H1" s="421"/>
+      <c r="H1" s="415"/>
       <c r="I1" s="8" t="s">
         <v>28</v>
       </c>
@@ -10227,16 +10227,16 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="16.5">
-      <c r="A3" s="422" t="s">
+      <c r="A3" s="416" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="422"/>
+      <c r="B3" s="416"/>
       <c r="C3" s="5"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="423" t="s">
+      <c r="E3" s="403" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="423"/>
+      <c r="F3" s="403"/>
       <c r="G3" s="3" t="str">
         <f>進口艙單印1份!D3</f>
         <v>輯薪輪</v>
@@ -10249,8 +10249,8 @@
         <v>115/7/27</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="K3" s="423"/>
-      <c r="L3" s="423"/>
+      <c r="K3" s="403"/>
+      <c r="L3" s="403"/>
     </row>
     <row r="4" spans="1:12" ht="42" customHeight="1">
       <c r="A4" s="7" t="s">
@@ -10259,14 +10259,14 @@
       <c r="B4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="428" t="s">
+      <c r="C4" s="404" t="s">
         <v>248</v>
       </c>
-      <c r="D4" s="428"/>
-      <c r="E4" s="423" t="s">
+      <c r="D4" s="404"/>
+      <c r="E4" s="403" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="423"/>
+      <c r="F4" s="403"/>
       <c r="G4" s="3" t="str">
         <f>進口艙單印1份!L3</f>
         <v>15PAHD</v>
@@ -10280,100 +10280,100 @@
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A5" s="429" t="s">
+      <c r="A5" s="405" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="429"/>
+      <c r="B5" s="405"/>
       <c r="C5" s="3" t="s">
         <v>224</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="423" t="s">
+      <c r="E5" s="403" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="423"/>
-      <c r="G5" s="430" t="s">
+      <c r="F5" s="403"/>
+      <c r="G5" s="406" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="430"/>
-      <c r="I5" s="430"/>
+      <c r="H5" s="406"/>
+      <c r="I5" s="406"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickBot="1"/>
     <row r="7" spans="1:12" ht="21" customHeight="1">
-      <c r="A7" s="407" t="s">
+      <c r="A7" s="417" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="194" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="407" t="s">
+      <c r="C7" s="417" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="192" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="424" t="s">
+      <c r="E7" s="419" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="425"/>
+      <c r="F7" s="420"/>
       <c r="G7" s="194" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="407" t="s">
+      <c r="H7" s="417" t="s">
         <v>34</v>
       </c>
       <c r="I7" s="152" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="415" t="s">
+      <c r="J7" s="409" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A8" s="408"/>
+      <c r="A8" s="418"/>
       <c r="B8" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="408"/>
+      <c r="C8" s="418"/>
       <c r="D8" s="193" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="417" t="s">
+      <c r="E8" s="411" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="418"/>
+      <c r="F8" s="412"/>
       <c r="G8" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="H8" s="408"/>
+      <c r="H8" s="418"/>
       <c r="I8" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="416"/>
+      <c r="J8" s="410"/>
     </row>
     <row r="9" spans="1:12" ht="21" customHeight="1">
-      <c r="A9" s="407">
+      <c r="A9" s="417">
         <v>1</v>
       </c>
-      <c r="B9" s="409" t="str">
+      <c r="B9" s="427" t="str">
         <f>進口艙單印1份!E16</f>
         <v>TCNU9125529</v>
       </c>
-      <c r="C9" s="411">
+      <c r="C9" s="429">
         <f>進口艙單印1份!P16</f>
         <v>200405</v>
       </c>
-      <c r="D9" s="426" t="str">
+      <c r="D9" s="421" t="str">
         <f>進口艙單印1份!B16</f>
         <v>5501</v>
       </c>
-      <c r="E9" s="407">
+      <c r="E9" s="417">
         <f>進口艙單印1份!C16</f>
         <v>1599</v>
       </c>
-      <c r="F9" s="407" t="str">
+      <c r="F9" s="417" t="str">
         <f>進口艙單印1份!D16</f>
         <v>PKG</v>
       </c>
@@ -10381,52 +10381,52 @@
         <f t="shared" ref="G9" si="0">B9</f>
         <v>TCNU9125529</v>
       </c>
-      <c r="H9" s="407" t="str">
+      <c r="H9" s="417" t="str">
         <f>進口艙單印1份!U16</f>
         <v>45G1</v>
       </c>
-      <c r="I9" s="403"/>
-      <c r="J9" s="413" t="s">
+      <c r="I9" s="423"/>
+      <c r="J9" s="407" t="s">
         <v>278</v>
       </c>
       <c r="L9" s="44"/>
     </row>
     <row r="10" spans="1:12" ht="21" customHeight="1" thickBot="1">
-      <c r="A10" s="408"/>
-      <c r="B10" s="410"/>
-      <c r="C10" s="412"/>
-      <c r="D10" s="427"/>
-      <c r="E10" s="408"/>
-      <c r="F10" s="408"/>
+      <c r="A10" s="418"/>
+      <c r="B10" s="428"/>
+      <c r="C10" s="430"/>
+      <c r="D10" s="422"/>
+      <c r="E10" s="418"/>
+      <c r="F10" s="418"/>
       <c r="G10" s="168">
         <f>進口艙單印1份!I16</f>
         <v>7137</v>
       </c>
-      <c r="H10" s="408"/>
-      <c r="I10" s="404"/>
-      <c r="J10" s="414"/>
+      <c r="H10" s="418"/>
+      <c r="I10" s="424"/>
+      <c r="J10" s="408"/>
       <c r="L10" s="44"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="406" t="s">
+      <c r="A11" s="426" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="406"/>
+      <c r="B11" s="426"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="405" t="s">
+      <c r="A12" s="425" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="405"/>
+      <c r="B12" s="425"/>
       <c r="G12" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="405" t="s">
+      <c r="A13" s="425" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="405"/>
+      <c r="B13" s="425"/>
     </row>
     <row r="14" spans="1:12" ht="12" customHeight="1">
       <c r="A14" s="1"/>
@@ -10438,12 +10438,13 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="E8:F8"/>
@@ -10460,13 +10461,12 @@
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:I5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -11449,21 +11449,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1">
-      <c r="A1" s="462" t="s">
+      <c r="A1" s="432" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="462"/>
+      <c r="B1" s="432"/>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1" thickBot="1">
-      <c r="D2" s="463" t="s">
+      <c r="D2" s="433" t="s">
         <v>277</v>
       </c>
-      <c r="E2" s="464"/>
-      <c r="F2" s="464"/>
-      <c r="G2" s="464"/>
-      <c r="H2" s="464"/>
-      <c r="I2" s="464"/>
-      <c r="J2" s="464"/>
+      <c r="E2" s="434"/>
+      <c r="F2" s="434"/>
+      <c r="G2" s="434"/>
+      <c r="H2" s="434"/>
+      <c r="I2" s="434"/>
+      <c r="J2" s="434"/>
     </row>
     <row r="3" spans="1:16" ht="12" customHeight="1" thickTop="1">
       <c r="A3" s="40">
@@ -11485,12 +11485,12 @@
       <c r="A5" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="B5" s="433" t="str">
+      <c r="B5" s="466" t="str">
         <f>'准單(紅紙)-2份'!C6</f>
         <v>大佑輪</v>
       </c>
-      <c r="C5" s="434"/>
-      <c r="D5" s="435"/>
+      <c r="C5" s="467"/>
+      <c r="D5" s="468"/>
       <c r="E5" s="27" t="s">
         <v>156</v>
       </c>
@@ -11508,12 +11508,12 @@
       <c r="I5" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="J5" s="436" t="str">
+      <c r="J5" s="458" t="str">
         <f>進口艙單印1份!O16</f>
         <v>JET-F WORLDWIDE EXPRESS CO., LTD.</v>
       </c>
-      <c r="K5" s="437"/>
-      <c r="L5" s="438"/>
+      <c r="K5" s="469"/>
+      <c r="L5" s="459"/>
       <c r="M5" s="29" t="s">
         <v>159</v>
       </c>
@@ -11561,186 +11561,186 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="12" customHeight="1" thickBot="1">
-      <c r="A7" s="439" t="s">
+      <c r="A7" s="470" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="440"/>
-      <c r="C7" s="440"/>
-      <c r="D7" s="440"/>
-      <c r="E7" s="440"/>
-      <c r="F7" s="441"/>
-      <c r="G7" s="439" t="s">
+      <c r="B7" s="471"/>
+      <c r="C7" s="471"/>
+      <c r="D7" s="471"/>
+      <c r="E7" s="471"/>
+      <c r="F7" s="472"/>
+      <c r="G7" s="470" t="s">
         <v>168</v>
       </c>
-      <c r="H7" s="440"/>
-      <c r="I7" s="440"/>
-      <c r="J7" s="440"/>
-      <c r="K7" s="440"/>
-      <c r="L7" s="440"/>
-      <c r="M7" s="440"/>
-      <c r="N7" s="441"/>
+      <c r="H7" s="471"/>
+      <c r="I7" s="471"/>
+      <c r="J7" s="471"/>
+      <c r="K7" s="471"/>
+      <c r="L7" s="471"/>
+      <c r="M7" s="471"/>
+      <c r="N7" s="472"/>
     </row>
     <row r="8" spans="1:16" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A8" s="431" t="s">
+      <c r="A8" s="437" t="s">
         <v>169</v>
       </c>
-      <c r="B8" s="442"/>
-      <c r="C8" s="432"/>
-      <c r="D8" s="431" t="s">
+      <c r="B8" s="473"/>
+      <c r="C8" s="438"/>
+      <c r="D8" s="437" t="s">
         <v>170</v>
       </c>
-      <c r="E8" s="442"/>
-      <c r="F8" s="432"/>
-      <c r="G8" s="431" t="s">
+      <c r="E8" s="473"/>
+      <c r="F8" s="438"/>
+      <c r="G8" s="437" t="s">
         <v>171</v>
       </c>
-      <c r="H8" s="432"/>
-      <c r="I8" s="431" t="s">
+      <c r="H8" s="438"/>
+      <c r="I8" s="437" t="s">
         <v>172</v>
       </c>
-      <c r="J8" s="432"/>
-      <c r="K8" s="431" t="s">
+      <c r="J8" s="438"/>
+      <c r="K8" s="437" t="s">
         <v>173</v>
       </c>
-      <c r="L8" s="432"/>
-      <c r="M8" s="431" t="s">
+      <c r="L8" s="438"/>
+      <c r="M8" s="437" t="s">
         <v>174</v>
       </c>
-      <c r="N8" s="432"/>
+      <c r="N8" s="438"/>
     </row>
     <row r="9" spans="1:16" ht="24" customHeight="1">
-      <c r="A9" s="443" t="str">
+      <c r="A9" s="439" t="str">
         <f>進口艙單印1份!E16</f>
         <v>TCNU9125529</v>
       </c>
-      <c r="B9" s="444"/>
-      <c r="C9" s="445"/>
-      <c r="D9" s="467">
+      <c r="B9" s="440"/>
+      <c r="C9" s="441"/>
+      <c r="D9" s="460">
         <f>進口艙單印1份!P16</f>
         <v>200405</v>
       </c>
-      <c r="E9" s="468"/>
-      <c r="F9" s="469"/>
-      <c r="G9" s="455"/>
-      <c r="H9" s="456"/>
-      <c r="I9" s="455"/>
-      <c r="J9" s="456"/>
-      <c r="K9" s="455"/>
-      <c r="L9" s="456"/>
-      <c r="M9" s="455"/>
-      <c r="N9" s="456"/>
+      <c r="E9" s="461"/>
+      <c r="F9" s="462"/>
+      <c r="G9" s="451"/>
+      <c r="H9" s="452"/>
+      <c r="I9" s="451"/>
+      <c r="J9" s="452"/>
+      <c r="K9" s="451"/>
+      <c r="L9" s="452"/>
+      <c r="M9" s="451"/>
+      <c r="N9" s="452"/>
       <c r="P9" s="37"/>
     </row>
     <row r="10" spans="1:16" ht="33.75" customHeight="1" thickBot="1">
-      <c r="A10" s="446"/>
-      <c r="B10" s="447"/>
-      <c r="C10" s="448"/>
-      <c r="D10" s="470" t="str">
+      <c r="A10" s="442"/>
+      <c r="B10" s="443"/>
+      <c r="C10" s="444"/>
+      <c r="D10" s="463" t="str">
         <f>'貨櫃清單-1份'!J9</f>
-        <v>ESN501</v>
-      </c>
-      <c r="E10" s="471"/>
-      <c r="F10" s="472"/>
-      <c r="G10" s="457"/>
-      <c r="H10" s="458"/>
-      <c r="I10" s="457"/>
-      <c r="J10" s="458"/>
-      <c r="K10" s="457"/>
-      <c r="L10" s="458"/>
-      <c r="M10" s="457"/>
-      <c r="N10" s="458"/>
+        <v>ESN888</v>
+      </c>
+      <c r="E10" s="464"/>
+      <c r="F10" s="465"/>
+      <c r="G10" s="453"/>
+      <c r="H10" s="454"/>
+      <c r="I10" s="453"/>
+      <c r="J10" s="454"/>
+      <c r="K10" s="453"/>
+      <c r="L10" s="454"/>
+      <c r="M10" s="453"/>
+      <c r="N10" s="454"/>
       <c r="P10" s="37"/>
     </row>
     <row r="11" spans="1:16" ht="42" customHeight="1" thickBot="1">
-      <c r="A11" s="449"/>
-      <c r="B11" s="450"/>
-      <c r="C11" s="451"/>
-      <c r="D11" s="431" t="s">
+      <c r="A11" s="445"/>
+      <c r="B11" s="446"/>
+      <c r="C11" s="447"/>
+      <c r="D11" s="437" t="s">
         <v>175</v>
       </c>
-      <c r="E11" s="432"/>
+      <c r="E11" s="438"/>
       <c r="F11" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="G11" s="431" t="s">
+      <c r="G11" s="437" t="s">
         <v>177</v>
       </c>
-      <c r="H11" s="432"/>
-      <c r="I11" s="431" t="s">
+      <c r="H11" s="438"/>
+      <c r="I11" s="437" t="s">
         <v>178</v>
       </c>
-      <c r="J11" s="432"/>
-      <c r="K11" s="431" t="s">
+      <c r="J11" s="438"/>
+      <c r="K11" s="437" t="s">
         <v>179</v>
       </c>
-      <c r="L11" s="432"/>
-      <c r="M11" s="431" t="s">
+      <c r="L11" s="438"/>
+      <c r="M11" s="437" t="s">
         <v>180</v>
       </c>
-      <c r="N11" s="432"/>
+      <c r="N11" s="438"/>
     </row>
     <row r="12" spans="1:16" ht="49.5" customHeight="1" thickBot="1">
       <c r="A12" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="431"/>
-      <c r="C12" s="432"/>
-      <c r="D12" s="436"/>
-      <c r="E12" s="438"/>
+      <c r="B12" s="437"/>
+      <c r="C12" s="438"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="459"/>
       <c r="F12" s="28"/>
-      <c r="G12" s="436"/>
-      <c r="H12" s="438"/>
-      <c r="I12" s="436"/>
-      <c r="J12" s="438"/>
-      <c r="K12" s="436"/>
-      <c r="L12" s="438"/>
-      <c r="M12" s="436"/>
-      <c r="N12" s="438"/>
+      <c r="G12" s="458"/>
+      <c r="H12" s="459"/>
+      <c r="I12" s="458"/>
+      <c r="J12" s="459"/>
+      <c r="K12" s="458"/>
+      <c r="L12" s="459"/>
+      <c r="M12" s="458"/>
+      <c r="N12" s="459"/>
     </row>
     <row r="13" spans="1:16" ht="23.25" customHeight="1">
-      <c r="A13" s="465" t="s">
+      <c r="A13" s="435" t="s">
         <v>271</v>
       </c>
-      <c r="B13" s="465"/>
-      <c r="C13" s="465"/>
-      <c r="D13" s="465"/>
-      <c r="E13" s="465"/>
-      <c r="F13" s="465"/>
+      <c r="B13" s="435"/>
+      <c r="C13" s="435"/>
+      <c r="D13" s="435"/>
+      <c r="E13" s="435"/>
+      <c r="F13" s="435"/>
     </row>
     <row r="14" spans="1:16" ht="9" customHeight="1">
-      <c r="A14" s="466" t="s">
+      <c r="A14" s="436" t="s">
         <v>272</v>
       </c>
-      <c r="B14" s="466"/>
-      <c r="C14" s="466"/>
-      <c r="D14" s="466"/>
-      <c r="E14" s="466"/>
-      <c r="F14" s="466"/>
-      <c r="G14" s="466"/>
-      <c r="H14" s="466"/>
-      <c r="I14" s="466"/>
-      <c r="J14" s="466"/>
-      <c r="K14" s="466"/>
-      <c r="L14" s="466"/>
-      <c r="M14" s="466"/>
-      <c r="N14" s="466"/>
+      <c r="B14" s="436"/>
+      <c r="C14" s="436"/>
+      <c r="D14" s="436"/>
+      <c r="E14" s="436"/>
+      <c r="F14" s="436"/>
+      <c r="G14" s="436"/>
+      <c r="H14" s="436"/>
+      <c r="I14" s="436"/>
+      <c r="J14" s="436"/>
+      <c r="K14" s="436"/>
+      <c r="L14" s="436"/>
+      <c r="M14" s="436"/>
+      <c r="N14" s="436"/>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1">
-      <c r="A15" s="462" t="s">
+      <c r="A15" s="432" t="s">
         <v>270</v>
       </c>
-      <c r="B15" s="462"/>
+      <c r="B15" s="432"/>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1" thickBot="1">
-      <c r="D16" s="463" t="s">
+      <c r="D16" s="433" t="s">
         <v>277</v>
       </c>
-      <c r="E16" s="464"/>
-      <c r="F16" s="464"/>
-      <c r="G16" s="464"/>
-      <c r="H16" s="464"/>
-      <c r="I16" s="464"/>
-      <c r="J16" s="464"/>
+      <c r="E16" s="434"/>
+      <c r="F16" s="434"/>
+      <c r="G16" s="434"/>
+      <c r="H16" s="434"/>
+      <c r="I16" s="434"/>
+      <c r="J16" s="434"/>
     </row>
     <row r="17" spans="1:14" ht="12" customHeight="1" thickTop="1">
       <c r="A17" s="40">
@@ -11762,12 +11762,12 @@
       <c r="A19" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="433" t="str">
+      <c r="B19" s="466" t="str">
         <f>B5</f>
         <v>大佑輪</v>
       </c>
-      <c r="C19" s="434"/>
-      <c r="D19" s="435"/>
+      <c r="C19" s="467"/>
+      <c r="D19" s="468"/>
       <c r="E19" s="27" t="s">
         <v>156</v>
       </c>
@@ -11785,12 +11785,12 @@
       <c r="I19" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="J19" s="436" t="str">
+      <c r="J19" s="458" t="str">
         <f>J5</f>
         <v>JET-F WORLDWIDE EXPRESS CO., LTD.</v>
       </c>
-      <c r="K19" s="437"/>
-      <c r="L19" s="438"/>
+      <c r="K19" s="469"/>
+      <c r="L19" s="459"/>
       <c r="M19" s="29" t="s">
         <v>159</v>
       </c>
@@ -11840,184 +11840,184 @@
       </c>
     </row>
     <row r="21" spans="1:14" ht="12" customHeight="1" thickBot="1">
-      <c r="A21" s="439" t="s">
+      <c r="A21" s="470" t="s">
         <v>167</v>
       </c>
-      <c r="B21" s="440"/>
-      <c r="C21" s="440"/>
-      <c r="D21" s="440"/>
-      <c r="E21" s="440"/>
-      <c r="F21" s="441"/>
-      <c r="G21" s="439" t="s">
+      <c r="B21" s="471"/>
+      <c r="C21" s="471"/>
+      <c r="D21" s="471"/>
+      <c r="E21" s="471"/>
+      <c r="F21" s="472"/>
+      <c r="G21" s="470" t="s">
         <v>168</v>
       </c>
-      <c r="H21" s="440"/>
-      <c r="I21" s="440"/>
-      <c r="J21" s="440"/>
-      <c r="K21" s="440"/>
-      <c r="L21" s="440"/>
-      <c r="M21" s="440"/>
-      <c r="N21" s="441"/>
+      <c r="H21" s="471"/>
+      <c r="I21" s="471"/>
+      <c r="J21" s="471"/>
+      <c r="K21" s="471"/>
+      <c r="L21" s="471"/>
+      <c r="M21" s="471"/>
+      <c r="N21" s="472"/>
     </row>
     <row r="22" spans="1:14" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A22" s="431" t="s">
+      <c r="A22" s="437" t="s">
         <v>169</v>
       </c>
-      <c r="B22" s="442"/>
-      <c r="C22" s="432"/>
-      <c r="D22" s="431" t="s">
+      <c r="B22" s="473"/>
+      <c r="C22" s="438"/>
+      <c r="D22" s="437" t="s">
         <v>170</v>
       </c>
-      <c r="E22" s="442"/>
-      <c r="F22" s="432"/>
-      <c r="G22" s="431" t="s">
+      <c r="E22" s="473"/>
+      <c r="F22" s="438"/>
+      <c r="G22" s="437" t="s">
         <v>171</v>
       </c>
-      <c r="H22" s="432"/>
-      <c r="I22" s="431" t="s">
+      <c r="H22" s="438"/>
+      <c r="I22" s="437" t="s">
         <v>172</v>
       </c>
-      <c r="J22" s="432"/>
-      <c r="K22" s="431" t="s">
+      <c r="J22" s="438"/>
+      <c r="K22" s="437" t="s">
         <v>173</v>
       </c>
-      <c r="L22" s="432"/>
-      <c r="M22" s="431" t="s">
+      <c r="L22" s="438"/>
+      <c r="M22" s="437" t="s">
         <v>174</v>
       </c>
-      <c r="N22" s="432"/>
+      <c r="N22" s="438"/>
     </row>
     <row r="23" spans="1:14" ht="24" customHeight="1">
-      <c r="A23" s="443" t="str">
+      <c r="A23" s="439" t="str">
         <f>A9</f>
         <v>TCNU9125529</v>
       </c>
-      <c r="B23" s="444"/>
-      <c r="C23" s="445"/>
-      <c r="D23" s="452">
+      <c r="B23" s="440"/>
+      <c r="C23" s="441"/>
+      <c r="D23" s="448">
         <f>D9</f>
         <v>200405</v>
       </c>
-      <c r="E23" s="453"/>
-      <c r="F23" s="454"/>
-      <c r="G23" s="455"/>
-      <c r="H23" s="456"/>
-      <c r="I23" s="455"/>
-      <c r="J23" s="456"/>
-      <c r="K23" s="455"/>
-      <c r="L23" s="456"/>
-      <c r="M23" s="455"/>
-      <c r="N23" s="456"/>
+      <c r="E23" s="449"/>
+      <c r="F23" s="450"/>
+      <c r="G23" s="451"/>
+      <c r="H23" s="452"/>
+      <c r="I23" s="451"/>
+      <c r="J23" s="452"/>
+      <c r="K23" s="451"/>
+      <c r="L23" s="452"/>
+      <c r="M23" s="451"/>
+      <c r="N23" s="452"/>
     </row>
     <row r="24" spans="1:14" ht="33.75" customHeight="1" thickBot="1">
-      <c r="A24" s="446"/>
-      <c r="B24" s="447"/>
-      <c r="C24" s="448"/>
-      <c r="D24" s="459" t="str">
+      <c r="A24" s="442"/>
+      <c r="B24" s="443"/>
+      <c r="C24" s="444"/>
+      <c r="D24" s="455" t="str">
         <f>D10</f>
-        <v>ESN501</v>
-      </c>
-      <c r="E24" s="460"/>
-      <c r="F24" s="461"/>
-      <c r="G24" s="457"/>
-      <c r="H24" s="458"/>
-      <c r="I24" s="457"/>
-      <c r="J24" s="458"/>
-      <c r="K24" s="457"/>
-      <c r="L24" s="458"/>
-      <c r="M24" s="457"/>
-      <c r="N24" s="458"/>
+        <v>ESN888</v>
+      </c>
+      <c r="E24" s="456"/>
+      <c r="F24" s="457"/>
+      <c r="G24" s="453"/>
+      <c r="H24" s="454"/>
+      <c r="I24" s="453"/>
+      <c r="J24" s="454"/>
+      <c r="K24" s="453"/>
+      <c r="L24" s="454"/>
+      <c r="M24" s="453"/>
+      <c r="N24" s="454"/>
     </row>
     <row r="25" spans="1:14" ht="42" customHeight="1" thickBot="1">
-      <c r="A25" s="449"/>
-      <c r="B25" s="450"/>
-      <c r="C25" s="451"/>
-      <c r="D25" s="431" t="s">
+      <c r="A25" s="445"/>
+      <c r="B25" s="446"/>
+      <c r="C25" s="447"/>
+      <c r="D25" s="437" t="s">
         <v>175</v>
       </c>
-      <c r="E25" s="432"/>
+      <c r="E25" s="438"/>
       <c r="F25" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="G25" s="431" t="s">
+      <c r="G25" s="437" t="s">
         <v>177</v>
       </c>
-      <c r="H25" s="432"/>
-      <c r="I25" s="431" t="s">
+      <c r="H25" s="438"/>
+      <c r="I25" s="437" t="s">
         <v>178</v>
       </c>
-      <c r="J25" s="432"/>
-      <c r="K25" s="431" t="s">
+      <c r="J25" s="438"/>
+      <c r="K25" s="437" t="s">
         <v>179</v>
       </c>
-      <c r="L25" s="432"/>
-      <c r="M25" s="431" t="s">
+      <c r="L25" s="438"/>
+      <c r="M25" s="437" t="s">
         <v>180</v>
       </c>
-      <c r="N25" s="432"/>
+      <c r="N25" s="438"/>
     </row>
     <row r="26" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A26" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="B26" s="431"/>
-      <c r="C26" s="432"/>
-      <c r="D26" s="431"/>
-      <c r="E26" s="432"/>
+      <c r="B26" s="437"/>
+      <c r="C26" s="438"/>
+      <c r="D26" s="437"/>
+      <c r="E26" s="438"/>
       <c r="F26" s="27"/>
-      <c r="G26" s="431"/>
-      <c r="H26" s="432"/>
-      <c r="I26" s="431"/>
-      <c r="J26" s="432"/>
-      <c r="K26" s="431"/>
-      <c r="L26" s="432"/>
-      <c r="M26" s="431"/>
-      <c r="N26" s="432"/>
+      <c r="G26" s="437"/>
+      <c r="H26" s="438"/>
+      <c r="I26" s="437"/>
+      <c r="J26" s="438"/>
+      <c r="K26" s="437"/>
+      <c r="L26" s="438"/>
+      <c r="M26" s="437"/>
+      <c r="N26" s="438"/>
     </row>
     <row r="27" spans="1:14" ht="23.25" customHeight="1">
-      <c r="A27" s="465" t="s">
+      <c r="A27" s="435" t="s">
         <v>271</v>
       </c>
-      <c r="B27" s="465"/>
-      <c r="C27" s="465"/>
-      <c r="D27" s="465"/>
-      <c r="E27" s="465"/>
-      <c r="F27" s="465"/>
+      <c r="B27" s="435"/>
+      <c r="C27" s="435"/>
+      <c r="D27" s="435"/>
+      <c r="E27" s="435"/>
+      <c r="F27" s="435"/>
     </row>
     <row r="28" spans="1:14" s="169" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="466" t="s">
+      <c r="A28" s="436" t="s">
         <v>272</v>
       </c>
-      <c r="B28" s="466"/>
-      <c r="C28" s="466"/>
-      <c r="D28" s="466"/>
-      <c r="E28" s="466"/>
-      <c r="F28" s="466"/>
-      <c r="G28" s="466"/>
-      <c r="H28" s="466"/>
-      <c r="I28" s="466"/>
-      <c r="J28" s="466"/>
-      <c r="K28" s="466"/>
-      <c r="L28" s="466"/>
-      <c r="M28" s="466"/>
-      <c r="N28" s="466"/>
+      <c r="B28" s="436"/>
+      <c r="C28" s="436"/>
+      <c r="D28" s="436"/>
+      <c r="E28" s="436"/>
+      <c r="F28" s="436"/>
+      <c r="G28" s="436"/>
+      <c r="H28" s="436"/>
+      <c r="I28" s="436"/>
+      <c r="J28" s="436"/>
+      <c r="K28" s="436"/>
+      <c r="L28" s="436"/>
+      <c r="M28" s="436"/>
+      <c r="N28" s="436"/>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
-      <c r="A29" s="473" t="s">
+      <c r="A29" s="431" t="s">
         <v>276</v>
       </c>
-      <c r="B29" s="462"/>
+      <c r="B29" s="432"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1" thickBot="1">
-      <c r="D30" s="463" t="s">
+      <c r="D30" s="433" t="s">
         <v>277</v>
       </c>
-      <c r="E30" s="464"/>
-      <c r="F30" s="464"/>
-      <c r="G30" s="464"/>
-      <c r="H30" s="464"/>
-      <c r="I30" s="464"/>
-      <c r="J30" s="464"/>
+      <c r="E30" s="434"/>
+      <c r="F30" s="434"/>
+      <c r="G30" s="434"/>
+      <c r="H30" s="434"/>
+      <c r="I30" s="434"/>
+      <c r="J30" s="434"/>
     </row>
     <row r="31" spans="1:14" ht="12" customHeight="1" thickTop="1">
       <c r="A31" s="40">
@@ -12039,12 +12039,12 @@
       <c r="A33" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="B33" s="433" t="str">
+      <c r="B33" s="466" t="str">
         <f>B5</f>
         <v>大佑輪</v>
       </c>
-      <c r="C33" s="434"/>
-      <c r="D33" s="435"/>
+      <c r="C33" s="467"/>
+      <c r="D33" s="468"/>
       <c r="E33" s="27" t="s">
         <v>156</v>
       </c>
@@ -12062,12 +12062,12 @@
       <c r="I33" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="J33" s="436" t="str">
+      <c r="J33" s="458" t="str">
         <f>J5</f>
         <v>JET-F WORLDWIDE EXPRESS CO., LTD.</v>
       </c>
-      <c r="K33" s="437"/>
-      <c r="L33" s="438"/>
+      <c r="K33" s="469"/>
+      <c r="L33" s="459"/>
       <c r="M33" s="29" t="s">
         <v>159</v>
       </c>
@@ -12117,153 +12117,232 @@
       </c>
     </row>
     <row r="35" spans="1:14" ht="12" customHeight="1" thickBot="1">
-      <c r="A35" s="439" t="s">
+      <c r="A35" s="470" t="s">
         <v>167</v>
       </c>
-      <c r="B35" s="440"/>
-      <c r="C35" s="440"/>
-      <c r="D35" s="440"/>
-      <c r="E35" s="440"/>
-      <c r="F35" s="441"/>
-      <c r="G35" s="439" t="s">
+      <c r="B35" s="471"/>
+      <c r="C35" s="471"/>
+      <c r="D35" s="471"/>
+      <c r="E35" s="471"/>
+      <c r="F35" s="472"/>
+      <c r="G35" s="470" t="s">
         <v>168</v>
       </c>
-      <c r="H35" s="440"/>
-      <c r="I35" s="440"/>
-      <c r="J35" s="440"/>
-      <c r="K35" s="440"/>
-      <c r="L35" s="440"/>
-      <c r="M35" s="440"/>
-      <c r="N35" s="441"/>
+      <c r="H35" s="471"/>
+      <c r="I35" s="471"/>
+      <c r="J35" s="471"/>
+      <c r="K35" s="471"/>
+      <c r="L35" s="471"/>
+      <c r="M35" s="471"/>
+      <c r="N35" s="472"/>
     </row>
     <row r="36" spans="1:14" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A36" s="431" t="s">
+      <c r="A36" s="437" t="s">
         <v>169</v>
       </c>
-      <c r="B36" s="442"/>
-      <c r="C36" s="432"/>
-      <c r="D36" s="431" t="s">
+      <c r="B36" s="473"/>
+      <c r="C36" s="438"/>
+      <c r="D36" s="437" t="s">
         <v>170</v>
       </c>
-      <c r="E36" s="442"/>
-      <c r="F36" s="432"/>
-      <c r="G36" s="431" t="s">
+      <c r="E36" s="473"/>
+      <c r="F36" s="438"/>
+      <c r="G36" s="437" t="s">
         <v>171</v>
       </c>
-      <c r="H36" s="432"/>
-      <c r="I36" s="431" t="s">
+      <c r="H36" s="438"/>
+      <c r="I36" s="437" t="s">
         <v>172</v>
       </c>
-      <c r="J36" s="432"/>
-      <c r="K36" s="431" t="s">
+      <c r="J36" s="438"/>
+      <c r="K36" s="437" t="s">
         <v>173</v>
       </c>
-      <c r="L36" s="432"/>
-      <c r="M36" s="431" t="s">
+      <c r="L36" s="438"/>
+      <c r="M36" s="437" t="s">
         <v>174</v>
       </c>
-      <c r="N36" s="432"/>
+      <c r="N36" s="438"/>
     </row>
     <row r="37" spans="1:14" ht="18" customHeight="1">
-      <c r="A37" s="443" t="str">
+      <c r="A37" s="439" t="str">
         <f>A9</f>
         <v>TCNU9125529</v>
       </c>
-      <c r="B37" s="444"/>
-      <c r="C37" s="445"/>
-      <c r="D37" s="452">
+      <c r="B37" s="440"/>
+      <c r="C37" s="441"/>
+      <c r="D37" s="448">
         <f>D9</f>
         <v>200405</v>
       </c>
-      <c r="E37" s="453"/>
-      <c r="F37" s="454"/>
-      <c r="G37" s="455"/>
-      <c r="H37" s="456"/>
-      <c r="I37" s="455"/>
-      <c r="J37" s="456"/>
-      <c r="K37" s="455"/>
-      <c r="L37" s="456"/>
-      <c r="M37" s="455"/>
-      <c r="N37" s="456"/>
+      <c r="E37" s="449"/>
+      <c r="F37" s="450"/>
+      <c r="G37" s="451"/>
+      <c r="H37" s="452"/>
+      <c r="I37" s="451"/>
+      <c r="J37" s="452"/>
+      <c r="K37" s="451"/>
+      <c r="L37" s="452"/>
+      <c r="M37" s="451"/>
+      <c r="N37" s="452"/>
     </row>
     <row r="38" spans="1:14" ht="33.75" customHeight="1" thickBot="1">
-      <c r="A38" s="446"/>
-      <c r="B38" s="447"/>
-      <c r="C38" s="448"/>
-      <c r="D38" s="459" t="str">
+      <c r="A38" s="442"/>
+      <c r="B38" s="443"/>
+      <c r="C38" s="444"/>
+      <c r="D38" s="455" t="str">
         <f>D10</f>
-        <v>ESN501</v>
-      </c>
-      <c r="E38" s="460"/>
-      <c r="F38" s="461"/>
-      <c r="G38" s="457"/>
-      <c r="H38" s="458"/>
-      <c r="I38" s="457"/>
-      <c r="J38" s="458"/>
-      <c r="K38" s="457"/>
-      <c r="L38" s="458"/>
-      <c r="M38" s="457"/>
-      <c r="N38" s="458"/>
+        <v>ESN888</v>
+      </c>
+      <c r="E38" s="456"/>
+      <c r="F38" s="457"/>
+      <c r="G38" s="453"/>
+      <c r="H38" s="454"/>
+      <c r="I38" s="453"/>
+      <c r="J38" s="454"/>
+      <c r="K38" s="453"/>
+      <c r="L38" s="454"/>
+      <c r="M38" s="453"/>
+      <c r="N38" s="454"/>
     </row>
     <row r="39" spans="1:14" ht="42" customHeight="1" thickBot="1">
-      <c r="A39" s="449"/>
-      <c r="B39" s="450"/>
-      <c r="C39" s="451"/>
-      <c r="D39" s="431" t="s">
+      <c r="A39" s="445"/>
+      <c r="B39" s="446"/>
+      <c r="C39" s="447"/>
+      <c r="D39" s="437" t="s">
         <v>175</v>
       </c>
-      <c r="E39" s="432"/>
+      <c r="E39" s="438"/>
       <c r="F39" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="G39" s="431" t="s">
+      <c r="G39" s="437" t="s">
         <v>177</v>
       </c>
-      <c r="H39" s="432"/>
-      <c r="I39" s="431" t="s">
+      <c r="H39" s="438"/>
+      <c r="I39" s="437" t="s">
         <v>178</v>
       </c>
-      <c r="J39" s="432"/>
-      <c r="K39" s="431" t="s">
+      <c r="J39" s="438"/>
+      <c r="K39" s="437" t="s">
         <v>179</v>
       </c>
-      <c r="L39" s="432"/>
-      <c r="M39" s="431" t="s">
+      <c r="L39" s="438"/>
+      <c r="M39" s="437" t="s">
         <v>180</v>
       </c>
-      <c r="N39" s="432"/>
+      <c r="N39" s="438"/>
     </row>
     <row r="40" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A40" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="B40" s="431"/>
-      <c r="C40" s="432"/>
-      <c r="D40" s="431"/>
-      <c r="E40" s="432"/>
+      <c r="B40" s="437"/>
+      <c r="C40" s="438"/>
+      <c r="D40" s="437"/>
+      <c r="E40" s="438"/>
       <c r="F40" s="27"/>
-      <c r="G40" s="431"/>
-      <c r="H40" s="432"/>
-      <c r="I40" s="431"/>
-      <c r="J40" s="432"/>
-      <c r="K40" s="431"/>
-      <c r="L40" s="432"/>
-      <c r="M40" s="431"/>
-      <c r="N40" s="432"/>
+      <c r="G40" s="437"/>
+      <c r="H40" s="438"/>
+      <c r="I40" s="437"/>
+      <c r="J40" s="438"/>
+      <c r="K40" s="437"/>
+      <c r="L40" s="438"/>
+      <c r="M40" s="437"/>
+      <c r="N40" s="438"/>
     </row>
     <row r="41" spans="1:14" ht="23.25" customHeight="1">
-      <c r="A41" s="465" t="s">
+      <c r="A41" s="435" t="s">
         <v>271</v>
       </c>
-      <c r="B41" s="465"/>
-      <c r="C41" s="465"/>
-      <c r="D41" s="465"/>
-      <c r="E41" s="465"/>
-      <c r="F41" s="465"/>
+      <c r="B41" s="435"/>
+      <c r="C41" s="435"/>
+      <c r="D41" s="435"/>
+      <c r="E41" s="435"/>
+      <c r="F41" s="435"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="95">
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:N7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="G21:N21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="A23:C25"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:H24"/>
+    <mergeCell ref="I23:J24"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="M23:N24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="G35:N35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D16:J16"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:N14"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A9:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="M9:N10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="D30:J30"/>
     <mergeCell ref="A27:F27"/>
@@ -12280,85 +12359,6 @@
     <mergeCell ref="D39:E39"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="D40:E40"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D16:J16"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:N14"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A9:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="M9:N10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="G35:N35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="A23:C25"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:H24"/>
-    <mergeCell ref="I23:J24"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="M23:N24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="G21:N21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:N7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B6DD13-875B-48F6-8C98-DEEB1682275F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABA64EC-9448-43FB-B597-C4636ACE447A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="618" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="618" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="建船資料檔" sheetId="78" r:id="rId1"/>
@@ -1516,7 +1516,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>ESN888</t>
+    <t>ESN501</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3279,6 +3279,219 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="46" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="46" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="46" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="46" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="54" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="54" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3291,42 +3504,6 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3336,198 +3513,132 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="46" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="46" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="54" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="54" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="46" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="46" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="19" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3585,24 +3696,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3651,98 +3744,50 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3777,54 +3822,81 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="60" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="61" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3834,206 +3906,134 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="61" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="60" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6511,32 +6511,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="30.75" customHeight="1">
-      <c r="A1" s="262" t="s">
+      <c r="A1" s="267" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="263"/>
-      <c r="C1" s="264"/>
-      <c r="D1" s="251" t="s">
+      <c r="B1" s="268"/>
+      <c r="C1" s="269"/>
+      <c r="D1" s="273" t="s">
         <v>193</v>
       </c>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251" t="s">
+      <c r="E1" s="273"/>
+      <c r="F1" s="273" t="s">
         <v>194</v>
       </c>
-      <c r="G1" s="251"/>
-      <c r="H1" s="234" t="s">
+      <c r="G1" s="273"/>
+      <c r="H1" s="253" t="s">
         <v>195</v>
       </c>
-      <c r="I1" s="235"/>
-      <c r="J1" s="251" t="s">
+      <c r="I1" s="254"/>
+      <c r="J1" s="273" t="s">
         <v>196</v>
       </c>
-      <c r="K1" s="251"/>
-      <c r="L1" s="234" t="s">
+      <c r="K1" s="273"/>
+      <c r="L1" s="253" t="s">
         <v>197</v>
       </c>
-      <c r="M1" s="252"/>
-      <c r="N1" s="235"/>
+      <c r="M1" s="279"/>
+      <c r="N1" s="254"/>
       <c r="O1" s="186"/>
       <c r="P1" s="186"/>
       <c r="Q1" s="131"/>
@@ -6546,30 +6546,30 @@
       <c r="U1" s="180"/>
     </row>
     <row r="2" spans="1:27" ht="17.25" customHeight="1">
-      <c r="A2" s="265"/>
-      <c r="B2" s="266"/>
-      <c r="C2" s="267"/>
-      <c r="D2" s="231" t="s">
+      <c r="A2" s="270"/>
+      <c r="B2" s="271"/>
+      <c r="C2" s="272"/>
+      <c r="D2" s="249" t="s">
         <v>198</v>
       </c>
-      <c r="E2" s="233"/>
-      <c r="F2" s="253" t="s">
+      <c r="E2" s="250"/>
+      <c r="F2" s="280" t="s">
         <v>199</v>
       </c>
-      <c r="G2" s="254"/>
-      <c r="H2" s="228" t="s">
+      <c r="G2" s="281"/>
+      <c r="H2" s="247" t="s">
         <v>200</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="228" t="s">
+      <c r="I2" s="248"/>
+      <c r="J2" s="247" t="s">
         <v>201</v>
       </c>
-      <c r="K2" s="230"/>
-      <c r="L2" s="228" t="s">
+      <c r="K2" s="248"/>
+      <c r="L2" s="247" t="s">
         <v>202</v>
       </c>
-      <c r="M2" s="229"/>
-      <c r="N2" s="230"/>
+      <c r="M2" s="275"/>
+      <c r="N2" s="248"/>
       <c r="O2" s="130"/>
       <c r="P2" s="129"/>
       <c r="Q2" s="128"/>
@@ -6582,32 +6582,32 @@
       <c r="A3" s="74"/>
       <c r="B3" s="75"/>
       <c r="C3" s="76"/>
-      <c r="D3" s="273" t="str">
+      <c r="D3" s="231" t="str">
         <f>建船資料檔!B6</f>
         <v>輯薪輪</v>
       </c>
-      <c r="E3" s="274"/>
-      <c r="F3" s="268">
+      <c r="E3" s="232"/>
+      <c r="F3" s="233">
         <f>建船資料檔!B7</f>
         <v>260727</v>
       </c>
-      <c r="G3" s="269"/>
-      <c r="H3" s="294" t="str">
+      <c r="G3" s="234"/>
+      <c r="H3" s="235" t="str">
         <f>建船資料檔!B8</f>
         <v xml:space="preserve">BP3379 </v>
       </c>
-      <c r="I3" s="295"/>
-      <c r="J3" s="292" t="str">
+      <c r="I3" s="236"/>
+      <c r="J3" s="225" t="str">
         <f>建船資料檔!B9</f>
         <v>姜大炎</v>
       </c>
-      <c r="K3" s="293"/>
-      <c r="L3" s="289" t="str">
+      <c r="K3" s="226"/>
+      <c r="L3" s="222" t="str">
         <f>建船資料檔!B10</f>
         <v>15PAHD</v>
       </c>
-      <c r="M3" s="290"/>
-      <c r="N3" s="291"/>
+      <c r="M3" s="223"/>
+      <c r="N3" s="224"/>
       <c r="O3" s="186"/>
       <c r="P3" s="186"/>
       <c r="Q3" s="186"/>
@@ -6623,32 +6623,32 @@
       <c r="AA3" s="78"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="270" t="s">
+      <c r="A4" s="276" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="271"/>
-      <c r="C4" s="272"/>
-      <c r="D4" s="234" t="s">
+      <c r="B4" s="277"/>
+      <c r="C4" s="278"/>
+      <c r="D4" s="253" t="s">
         <v>203</v>
       </c>
-      <c r="E4" s="235"/>
-      <c r="F4" s="234" t="s">
+      <c r="E4" s="254"/>
+      <c r="F4" s="253" t="s">
         <v>204</v>
       </c>
-      <c r="G4" s="235"/>
-      <c r="H4" s="234" t="s">
+      <c r="G4" s="254"/>
+      <c r="H4" s="253" t="s">
         <v>205</v>
       </c>
-      <c r="I4" s="235"/>
-      <c r="J4" s="234" t="s">
+      <c r="I4" s="254"/>
+      <c r="J4" s="253" t="s">
         <v>206</v>
       </c>
-      <c r="K4" s="235"/>
-      <c r="L4" s="234" t="s">
+      <c r="K4" s="254"/>
+      <c r="L4" s="253" t="s">
         <v>207</v>
       </c>
-      <c r="M4" s="252"/>
-      <c r="N4" s="235"/>
+      <c r="M4" s="279"/>
+      <c r="N4" s="254"/>
       <c r="O4" s="148"/>
       <c r="P4" s="154"/>
       <c r="Q4" s="179"/>
@@ -6664,32 +6664,32 @@
       <c r="AA4" s="78"/>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="231" t="s">
+      <c r="A5" s="249" t="s">
         <v>273</v>
       </c>
-      <c r="B5" s="232"/>
-      <c r="C5" s="233"/>
-      <c r="D5" s="228" t="s">
+      <c r="B5" s="274"/>
+      <c r="C5" s="250"/>
+      <c r="D5" s="247" t="s">
         <v>208</v>
       </c>
-      <c r="E5" s="230"/>
-      <c r="F5" s="228" t="s">
+      <c r="E5" s="248"/>
+      <c r="F5" s="247" t="s">
         <v>209</v>
       </c>
-      <c r="G5" s="230"/>
-      <c r="H5" s="228" t="s">
+      <c r="G5" s="248"/>
+      <c r="H5" s="247" t="s">
         <v>210</v>
       </c>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228" t="s">
+      <c r="I5" s="248"/>
+      <c r="J5" s="247" t="s">
         <v>211</v>
       </c>
-      <c r="K5" s="230"/>
-      <c r="L5" s="228" t="s">
+      <c r="K5" s="248"/>
+      <c r="L5" s="247" t="s">
         <v>212</v>
       </c>
-      <c r="M5" s="229"/>
-      <c r="N5" s="230"/>
+      <c r="M5" s="275"/>
+      <c r="N5" s="248"/>
       <c r="O5" s="148"/>
       <c r="P5" s="154"/>
       <c r="Q5" s="147"/>
@@ -6705,34 +6705,34 @@
       <c r="AA5" s="78"/>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="228" t="s">
+      <c r="A6" s="247" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="229"/>
-      <c r="C6" s="230"/>
-      <c r="D6" s="268" t="s">
+      <c r="B6" s="275"/>
+      <c r="C6" s="248"/>
+      <c r="D6" s="233" t="s">
         <v>188</v>
       </c>
-      <c r="E6" s="269"/>
-      <c r="F6" s="273" t="str">
+      <c r="E6" s="234"/>
+      <c r="F6" s="231" t="str">
         <f>建船資料檔!B11</f>
         <v>1486/445</v>
       </c>
-      <c r="G6" s="274"/>
-      <c r="H6" s="268" t="s">
+      <c r="G6" s="232"/>
+      <c r="H6" s="233" t="s">
         <v>213</v>
       </c>
-      <c r="I6" s="269"/>
-      <c r="J6" s="241" t="str">
+      <c r="I6" s="234"/>
+      <c r="J6" s="240" t="str">
         <f>建船資料檔!B12</f>
         <v>115/7/27</v>
       </c>
       <c r="K6" s="242"/>
-      <c r="L6" s="241" t="str">
+      <c r="L6" s="240" t="str">
         <f>J6</f>
         <v>115/7/27</v>
       </c>
-      <c r="M6" s="299"/>
+      <c r="M6" s="241"/>
       <c r="N6" s="242"/>
       <c r="O6" s="189"/>
       <c r="P6" s="189"/>
@@ -6744,36 +6744,36 @@
       <c r="V6" s="186"/>
       <c r="W6" s="177"/>
       <c r="X6" s="77"/>
-      <c r="Y6" s="222"/>
-      <c r="Z6" s="222"/>
+      <c r="Y6" s="293"/>
+      <c r="Z6" s="293"/>
       <c r="AA6" s="78"/>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="231" t="s">
+      <c r="A7" s="249" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="232"/>
-      <c r="C7" s="233"/>
-      <c r="D7" s="234" t="s">
+      <c r="B7" s="274"/>
+      <c r="C7" s="250"/>
+      <c r="D7" s="253" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="235"/>
-      <c r="F7" s="234" t="s">
+      <c r="E7" s="254"/>
+      <c r="F7" s="253" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="235"/>
-      <c r="H7" s="234" t="s">
+      <c r="G7" s="254"/>
+      <c r="H7" s="253" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="235"/>
-      <c r="J7" s="234" t="s">
+      <c r="I7" s="254"/>
+      <c r="J7" s="253" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="235"/>
-      <c r="L7" s="234" t="s">
+      <c r="K7" s="254"/>
+      <c r="L7" s="253" t="s">
         <v>43</v>
       </c>
-      <c r="M7" s="235"/>
+      <c r="M7" s="254"/>
       <c r="N7" s="190" t="s">
         <v>44</v>
       </c>
@@ -6792,29 +6792,29 @@
       <c r="AA7" s="78"/>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="228" t="s">
+      <c r="A8" s="247" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="229"/>
-      <c r="C8" s="230"/>
-      <c r="D8" s="228" t="s">
+      <c r="B8" s="275"/>
+      <c r="C8" s="248"/>
+      <c r="D8" s="247" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="230"/>
-      <c r="F8" s="228" t="s">
+      <c r="E8" s="248"/>
+      <c r="F8" s="247" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="230"/>
-      <c r="H8" s="231"/>
-      <c r="I8" s="233"/>
-      <c r="J8" s="228" t="s">
+      <c r="G8" s="248"/>
+      <c r="H8" s="249"/>
+      <c r="I8" s="250"/>
+      <c r="J8" s="247" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="230"/>
-      <c r="L8" s="231" t="s">
+      <c r="K8" s="248"/>
+      <c r="L8" s="249" t="s">
         <v>49</v>
       </c>
-      <c r="M8" s="233"/>
+      <c r="M8" s="250"/>
       <c r="N8" s="197" t="s">
         <v>50</v>
       </c>
@@ -6828,29 +6828,29 @@
       <c r="V8" s="186"/>
       <c r="W8" s="177"/>
       <c r="X8" s="77"/>
-      <c r="Y8" s="222"/>
-      <c r="Z8" s="222"/>
+      <c r="Y8" s="293"/>
+      <c r="Z8" s="293"/>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="296" t="s">
+      <c r="A9" s="237" t="s">
         <v>152</v>
       </c>
-      <c r="B9" s="297"/>
-      <c r="C9" s="298"/>
-      <c r="D9" s="273" t="s">
+      <c r="B9" s="238"/>
+      <c r="C9" s="239"/>
+      <c r="D9" s="231" t="s">
         <v>225</v>
       </c>
-      <c r="E9" s="274"/>
-      <c r="F9" s="241"/>
+      <c r="E9" s="232"/>
+      <c r="F9" s="240"/>
       <c r="G9" s="242"/>
-      <c r="H9" s="285"/>
-      <c r="I9" s="269"/>
-      <c r="J9" s="268"/>
-      <c r="K9" s="269"/>
-      <c r="L9" s="268" t="s">
+      <c r="H9" s="263"/>
+      <c r="I9" s="234"/>
+      <c r="J9" s="233"/>
+      <c r="K9" s="234"/>
+      <c r="L9" s="233" t="s">
         <v>51</v>
       </c>
-      <c r="M9" s="269"/>
+      <c r="M9" s="234"/>
       <c r="N9" s="198"/>
       <c r="O9" s="189"/>
       <c r="P9" s="189"/>
@@ -6868,29 +6868,29 @@
       <c r="B10" s="170" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="260" t="s">
+      <c r="C10" s="245" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="261"/>
+      <c r="D10" s="246"/>
       <c r="E10" s="203" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="226" t="s">
+      <c r="F10" s="243" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="227"/>
+      <c r="G10" s="244"/>
       <c r="H10" s="170" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="260" t="s">
+      <c r="I10" s="245" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="261"/>
-      <c r="K10" s="277" t="s">
+      <c r="J10" s="246"/>
+      <c r="K10" s="255" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="278"/>
-      <c r="M10" s="279"/>
+      <c r="L10" s="256"/>
+      <c r="M10" s="257"/>
       <c r="N10" s="171" t="s">
         <v>59</v>
       </c>
@@ -6909,29 +6909,29 @@
       <c r="B11" s="173" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="236" t="s">
+      <c r="C11" s="227" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="237"/>
+      <c r="D11" s="228"/>
       <c r="E11" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="283" t="s">
+      <c r="F11" s="229" t="s">
         <v>64</v>
       </c>
-      <c r="G11" s="284"/>
+      <c r="G11" s="230"/>
       <c r="H11" s="173" t="s">
         <v>65</v>
       </c>
-      <c r="I11" s="236" t="s">
+      <c r="I11" s="227" t="s">
         <v>66</v>
       </c>
-      <c r="J11" s="237"/>
-      <c r="K11" s="286" t="s">
+      <c r="J11" s="228"/>
+      <c r="K11" s="264" t="s">
         <v>67</v>
       </c>
-      <c r="L11" s="287"/>
-      <c r="M11" s="288"/>
+      <c r="L11" s="265"/>
+      <c r="M11" s="266"/>
       <c r="N11" s="174" t="s">
         <v>68</v>
       </c>
@@ -6949,29 +6949,29 @@
       <c r="B12" s="172" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="236" t="s">
+      <c r="C12" s="227" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="237"/>
+      <c r="D12" s="228"/>
       <c r="E12" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="226" t="s">
+      <c r="F12" s="243" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="227"/>
+      <c r="G12" s="244"/>
       <c r="H12" s="173" t="s">
         <v>74</v>
       </c>
-      <c r="I12" s="255" t="s">
+      <c r="I12" s="258" t="s">
         <v>75</v>
       </c>
-      <c r="J12" s="256"/>
-      <c r="K12" s="280" t="s">
+      <c r="J12" s="259"/>
+      <c r="K12" s="260" t="s">
         <v>76</v>
       </c>
-      <c r="L12" s="281"/>
-      <c r="M12" s="282"/>
+      <c r="L12" s="261"/>
+      <c r="M12" s="262"/>
       <c r="N12" s="175" t="s">
         <v>226</v>
       </c>
@@ -6989,25 +6989,25 @@
       <c r="B13" s="173" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="236" t="s">
+      <c r="C13" s="227" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="237"/>
+      <c r="D13" s="228"/>
       <c r="E13" s="204"/>
-      <c r="F13" s="283" t="s">
+      <c r="F13" s="229" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="284"/>
+      <c r="G13" s="230"/>
       <c r="H13" s="173" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="255" t="s">
+      <c r="I13" s="258" t="s">
         <v>81</v>
       </c>
-      <c r="J13" s="256"/>
-      <c r="K13" s="257"/>
-      <c r="L13" s="258"/>
-      <c r="M13" s="259"/>
+      <c r="J13" s="259"/>
+      <c r="K13" s="282"/>
+      <c r="L13" s="283"/>
+      <c r="M13" s="284"/>
       <c r="N13" s="173" t="s">
         <v>82</v>
       </c>
@@ -7019,22 +7019,22 @@
       <c r="B14" s="173" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="236" t="s">
+      <c r="C14" s="227" t="s">
         <v>84</v>
       </c>
-      <c r="D14" s="237"/>
+      <c r="D14" s="228"/>
       <c r="E14" s="84"/>
-      <c r="F14" s="226" t="s">
+      <c r="F14" s="243" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="227"/>
+      <c r="G14" s="244"/>
       <c r="H14" s="173" t="s">
         <v>86</v>
       </c>
-      <c r="I14" s="255" t="s">
+      <c r="I14" s="258" t="s">
         <v>87</v>
       </c>
-      <c r="J14" s="256"/>
+      <c r="J14" s="259"/>
       <c r="K14" s="88"/>
       <c r="L14" s="89"/>
       <c r="M14" s="87"/>
@@ -7050,15 +7050,15 @@
       <c r="B15" s="199" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="224" t="s">
+      <c r="C15" s="295" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="225"/>
+      <c r="D15" s="296"/>
       <c r="E15" s="90"/>
-      <c r="F15" s="226" t="s">
+      <c r="F15" s="243" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="227"/>
+      <c r="G15" s="244"/>
       <c r="H15" s="90"/>
       <c r="I15" s="200"/>
       <c r="J15" s="202"/>
@@ -7089,11 +7089,11 @@
       <c r="E16" s="210" t="s">
         <v>263</v>
       </c>
-      <c r="F16" s="275" t="str">
+      <c r="F16" s="251" t="str">
         <f>T16&amp;"  "&amp;E16&amp;"/"&amp;U16&amp;"/"&amp;V16&amp;"/"&amp;P16</f>
         <v>EXPRESS PACKAGE  TCNU9125529/45G1/2/200405</v>
       </c>
-      <c r="G16" s="276"/>
+      <c r="G16" s="252"/>
       <c r="H16" s="127" t="s">
         <v>265</v>
       </c>
@@ -7103,11 +7103,11 @@
       <c r="J16" s="96" t="s">
         <v>235</v>
       </c>
-      <c r="K16" s="238" t="s">
+      <c r="K16" s="297" t="s">
         <v>266</v>
       </c>
-      <c r="L16" s="239"/>
-      <c r="M16" s="240"/>
+      <c r="L16" s="298"/>
+      <c r="M16" s="299"/>
       <c r="N16" s="149" t="s">
         <v>95</v>
       </c>
@@ -7149,64 +7149,102 @@
         <v>94</v>
       </c>
       <c r="E17" s="213"/>
-      <c r="F17" s="244"/>
-      <c r="G17" s="245"/>
+      <c r="F17" s="286"/>
+      <c r="G17" s="287"/>
       <c r="H17" s="212"/>
-      <c r="I17" s="246">
+      <c r="I17" s="288">
         <f>SUM(I16:J16)</f>
         <v>7137</v>
       </c>
-      <c r="J17" s="247"/>
-      <c r="K17" s="248"/>
-      <c r="L17" s="249"/>
-      <c r="M17" s="250"/>
+      <c r="J17" s="289"/>
+      <c r="K17" s="290"/>
+      <c r="L17" s="291"/>
+      <c r="M17" s="292"/>
       <c r="N17" s="211"/>
       <c r="T17" s="73"/>
       <c r="U17" s="184"/>
       <c r="V17" s="184"/>
     </row>
     <row r="18" spans="1:22">
-      <c r="A18" s="223" t="s">
+      <c r="A18" s="294" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="223"/>
-      <c r="H18" s="223"/>
-      <c r="I18" s="223"/>
-      <c r="J18" s="223"/>
-      <c r="K18" s="223"/>
+      <c r="B18" s="294"/>
+      <c r="H18" s="294"/>
+      <c r="I18" s="294"/>
+      <c r="J18" s="294"/>
+      <c r="K18" s="294"/>
     </row>
     <row r="19" spans="1:22">
-      <c r="A19" s="243" t="s">
+      <c r="A19" s="285" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="243"/>
-      <c r="H19" s="243" t="s">
+      <c r="B19" s="285"/>
+      <c r="H19" s="285" t="s">
         <v>99</v>
       </c>
-      <c r="I19" s="243"/>
-      <c r="J19" s="243"/>
-      <c r="K19" s="243"/>
+      <c r="I19" s="285"/>
+      <c r="J19" s="285"/>
+      <c r="K19" s="285"/>
     </row>
     <row r="21" spans="1:22">
       <c r="G21" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="Y8:Z8"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="J7:K7"/>
@@ -7223,59 +7261,21 @@
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="Y8:Z8"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="E3" s="106" t="str">
         <f>'貨櫃清單-1份'!J9</f>
-        <v>ESN888</v>
+        <v>ESN501</v>
       </c>
       <c r="F3" s="119" t="s">
         <v>249</v>
@@ -8235,28 +8235,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="C1" s="346" t="s">
+      <c r="C1" s="332" t="s">
         <v>100</v>
       </c>
-      <c r="D1" s="346"/>
-      <c r="E1" s="346"/>
-      <c r="F1" s="346"/>
-      <c r="G1" s="346"/>
-      <c r="H1" s="346"/>
+      <c r="D1" s="332"/>
+      <c r="E1" s="332"/>
+      <c r="F1" s="332"/>
+      <c r="G1" s="332"/>
+      <c r="H1" s="332"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="C2" s="346"/>
-      <c r="D2" s="346"/>
-      <c r="E2" s="346"/>
-      <c r="F2" s="346"/>
-      <c r="G2" s="346"/>
-      <c r="H2" s="346"/>
+      <c r="C2" s="332"/>
+      <c r="D2" s="332"/>
+      <c r="E2" s="332"/>
+      <c r="F2" s="332"/>
+      <c r="G2" s="332"/>
+      <c r="H2" s="332"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="347" t="s">
+      <c r="A3" s="333" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="348"/>
+      <c r="B3" s="334"/>
       <c r="H3" s="124" t="s">
         <v>251</v>
       </c>
@@ -8266,320 +8266,320 @@
       <c r="J3" s="142"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1">
-      <c r="A4" s="324" t="s">
+      <c r="A4" s="305" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="325"/>
-      <c r="C4" s="349" t="s">
+      <c r="B4" s="307"/>
+      <c r="C4" s="335" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="350"/>
-      <c r="E4" s="350"/>
-      <c r="F4" s="351"/>
+      <c r="D4" s="336"/>
+      <c r="E4" s="336"/>
+      <c r="F4" s="337"/>
       <c r="G4" s="191">
         <v>1312450</v>
       </c>
-      <c r="H4" s="302" t="s">
+      <c r="H4" s="317" t="s">
         <v>104</v>
       </c>
-      <c r="I4" s="300" t="str">
+      <c r="I4" s="341" t="str">
         <f>建船資料檔!B13</f>
         <v>115/7/27</v>
       </c>
       <c r="J4" s="161"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="328"/>
-      <c r="B5" s="329"/>
-      <c r="C5" s="352"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="353"/>
-      <c r="F5" s="354"/>
+      <c r="A5" s="308"/>
+      <c r="B5" s="310"/>
+      <c r="C5" s="338"/>
+      <c r="D5" s="339"/>
+      <c r="E5" s="339"/>
+      <c r="F5" s="340"/>
       <c r="G5" s="215"/>
-      <c r="H5" s="304"/>
-      <c r="I5" s="301"/>
+      <c r="H5" s="319"/>
+      <c r="I5" s="331"/>
       <c r="J5" s="161"/>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1">
-      <c r="A6" s="312" t="s">
+      <c r="A6" s="349" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="313"/>
-      <c r="C6" s="318" t="s">
+      <c r="B6" s="350"/>
+      <c r="C6" s="355" t="s">
         <v>264</v>
       </c>
-      <c r="D6" s="319"/>
-      <c r="E6" s="324" t="s">
+      <c r="D6" s="356"/>
+      <c r="E6" s="305" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="325"/>
-      <c r="G6" s="330" t="str">
+      <c r="F6" s="307"/>
+      <c r="G6" s="361" t="str">
         <f>進口艙單印1份!L3</f>
         <v>15PAHD</v>
       </c>
-      <c r="H6" s="302" t="s">
+      <c r="H6" s="317" t="s">
         <v>107</v>
       </c>
-      <c r="I6" s="302" t="s">
+      <c r="I6" s="317" t="s">
         <v>108</v>
       </c>
       <c r="J6" s="162"/>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1">
-      <c r="A7" s="314"/>
-      <c r="B7" s="315"/>
-      <c r="C7" s="320"/>
-      <c r="D7" s="321"/>
-      <c r="E7" s="326"/>
-      <c r="F7" s="327"/>
-      <c r="G7" s="331"/>
-      <c r="H7" s="303"/>
-      <c r="I7" s="303"/>
+      <c r="A7" s="351"/>
+      <c r="B7" s="352"/>
+      <c r="C7" s="357"/>
+      <c r="D7" s="358"/>
+      <c r="E7" s="313"/>
+      <c r="F7" s="314"/>
+      <c r="G7" s="362"/>
+      <c r="H7" s="318"/>
+      <c r="I7" s="318"/>
       <c r="J7" s="162"/>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1">
-      <c r="A8" s="314"/>
-      <c r="B8" s="315"/>
-      <c r="C8" s="320"/>
-      <c r="D8" s="321"/>
-      <c r="E8" s="326"/>
-      <c r="F8" s="327"/>
-      <c r="G8" s="331"/>
-      <c r="H8" s="303"/>
-      <c r="I8" s="303"/>
+      <c r="A8" s="351"/>
+      <c r="B8" s="352"/>
+      <c r="C8" s="357"/>
+      <c r="D8" s="358"/>
+      <c r="E8" s="313"/>
+      <c r="F8" s="314"/>
+      <c r="G8" s="362"/>
+      <c r="H8" s="318"/>
+      <c r="I8" s="318"/>
       <c r="J8" s="162"/>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1">
-      <c r="A9" s="316"/>
-      <c r="B9" s="317"/>
-      <c r="C9" s="322"/>
-      <c r="D9" s="323"/>
-      <c r="E9" s="328"/>
-      <c r="F9" s="329"/>
-      <c r="G9" s="332"/>
-      <c r="H9" s="304"/>
-      <c r="I9" s="304"/>
+      <c r="A9" s="353"/>
+      <c r="B9" s="354"/>
+      <c r="C9" s="359"/>
+      <c r="D9" s="360"/>
+      <c r="E9" s="308"/>
+      <c r="F9" s="310"/>
+      <c r="G9" s="363"/>
+      <c r="H9" s="319"/>
+      <c r="I9" s="319"/>
       <c r="J9" s="162"/>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1">
-      <c r="A10" s="312" t="s">
+      <c r="A10" s="349" t="s">
         <v>110</v>
       </c>
-      <c r="B10" s="313"/>
-      <c r="C10" s="345" t="s">
+      <c r="B10" s="350"/>
+      <c r="C10" s="376" t="s">
         <v>247</v>
       </c>
-      <c r="D10" s="319"/>
+      <c r="D10" s="356"/>
       <c r="E10" s="133" t="s">
         <v>111</v>
       </c>
       <c r="F10" s="134"/>
-      <c r="G10" s="364" t="str">
+      <c r="G10" s="329" t="str">
         <f>I4</f>
         <v>115/7/27</v>
       </c>
-      <c r="H10" s="302" t="s">
+      <c r="H10" s="317" t="s">
         <v>112</v>
       </c>
-      <c r="I10" s="302" t="s">
+      <c r="I10" s="317" t="s">
         <v>113</v>
       </c>
       <c r="J10" s="162"/>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1">
-      <c r="A11" s="314"/>
-      <c r="B11" s="315"/>
-      <c r="C11" s="320"/>
-      <c r="D11" s="321"/>
-      <c r="E11" s="326" t="s">
+      <c r="A11" s="351"/>
+      <c r="B11" s="352"/>
+      <c r="C11" s="357"/>
+      <c r="D11" s="358"/>
+      <c r="E11" s="313" t="s">
         <v>134</v>
       </c>
-      <c r="F11" s="327"/>
-      <c r="G11" s="365"/>
-      <c r="H11" s="303"/>
-      <c r="I11" s="303"/>
+      <c r="F11" s="314"/>
+      <c r="G11" s="330"/>
+      <c r="H11" s="318"/>
+      <c r="I11" s="318"/>
       <c r="J11" s="162"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1">
-      <c r="A12" s="314"/>
-      <c r="B12" s="315"/>
-      <c r="C12" s="320"/>
-      <c r="D12" s="321"/>
-      <c r="E12" s="326"/>
-      <c r="F12" s="327"/>
-      <c r="G12" s="365"/>
-      <c r="H12" s="303"/>
-      <c r="I12" s="303"/>
+      <c r="A12" s="351"/>
+      <c r="B12" s="352"/>
+      <c r="C12" s="357"/>
+      <c r="D12" s="358"/>
+      <c r="E12" s="313"/>
+      <c r="F12" s="314"/>
+      <c r="G12" s="330"/>
+      <c r="H12" s="318"/>
+      <c r="I12" s="318"/>
       <c r="J12" s="162"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1">
-      <c r="A13" s="316"/>
-      <c r="B13" s="317"/>
-      <c r="C13" s="322"/>
-      <c r="D13" s="323"/>
+      <c r="A13" s="353"/>
+      <c r="B13" s="354"/>
+      <c r="C13" s="359"/>
+      <c r="D13" s="360"/>
       <c r="E13" s="135" t="s">
         <v>114</v>
       </c>
       <c r="F13" s="136"/>
-      <c r="G13" s="301"/>
-      <c r="H13" s="304"/>
-      <c r="I13" s="304"/>
+      <c r="G13" s="331"/>
+      <c r="H13" s="319"/>
+      <c r="I13" s="319"/>
       <c r="J13" s="162"/>
     </row>
     <row r="14" spans="1:10" ht="18" customHeight="1">
-      <c r="A14" s="333" t="s">
+      <c r="A14" s="364" t="s">
         <v>115</v>
       </c>
-      <c r="B14" s="336" t="s">
+      <c r="B14" s="367" t="s">
         <v>116</v>
       </c>
       <c r="C14" s="133" t="s">
         <v>117</v>
       </c>
       <c r="D14" s="134"/>
-      <c r="E14" s="339" t="s">
+      <c r="E14" s="370" t="s">
         <v>243</v>
       </c>
-      <c r="F14" s="340"/>
-      <c r="G14" s="355" t="s">
+      <c r="F14" s="371"/>
+      <c r="G14" s="320" t="s">
         <v>236</v>
       </c>
-      <c r="H14" s="356"/>
-      <c r="I14" s="357"/>
+      <c r="H14" s="321"/>
+      <c r="I14" s="322"/>
       <c r="J14" s="151"/>
     </row>
     <row r="15" spans="1:10" ht="18" customHeight="1">
-      <c r="A15" s="334"/>
-      <c r="B15" s="337"/>
+      <c r="A15" s="365"/>
+      <c r="B15" s="368"/>
       <c r="C15" s="138" t="s">
         <v>118</v>
       </c>
       <c r="D15" s="139"/>
-      <c r="E15" s="341"/>
-      <c r="F15" s="342"/>
-      <c r="G15" s="358" t="s">
+      <c r="E15" s="372"/>
+      <c r="F15" s="373"/>
+      <c r="G15" s="323" t="s">
         <v>237</v>
       </c>
-      <c r="H15" s="359"/>
-      <c r="I15" s="360"/>
+      <c r="H15" s="324"/>
+      <c r="I15" s="325"/>
       <c r="J15" s="151"/>
     </row>
     <row r="16" spans="1:10" ht="18" customHeight="1">
-      <c r="A16" s="334"/>
-      <c r="B16" s="337"/>
+      <c r="A16" s="365"/>
+      <c r="B16" s="368"/>
       <c r="C16" s="138" t="s">
         <v>119</v>
       </c>
       <c r="D16" s="139"/>
-      <c r="E16" s="341"/>
-      <c r="F16" s="342"/>
-      <c r="G16" s="358" t="s">
+      <c r="E16" s="372"/>
+      <c r="F16" s="373"/>
+      <c r="G16" s="323" t="s">
         <v>238</v>
       </c>
-      <c r="H16" s="359"/>
-      <c r="I16" s="360"/>
+      <c r="H16" s="324"/>
+      <c r="I16" s="325"/>
       <c r="J16" s="151"/>
     </row>
     <row r="17" spans="1:12" ht="18" customHeight="1">
-      <c r="A17" s="334"/>
-      <c r="B17" s="337"/>
+      <c r="A17" s="365"/>
+      <c r="B17" s="368"/>
       <c r="C17" s="138" t="s">
         <v>120</v>
       </c>
       <c r="D17" s="139"/>
-      <c r="E17" s="341"/>
-      <c r="F17" s="342"/>
-      <c r="G17" s="358" t="s">
+      <c r="E17" s="372"/>
+      <c r="F17" s="373"/>
+      <c r="G17" s="323" t="s">
         <v>239</v>
       </c>
-      <c r="H17" s="359"/>
-      <c r="I17" s="360"/>
+      <c r="H17" s="324"/>
+      <c r="I17" s="325"/>
       <c r="J17" s="151"/>
       <c r="L17" s="12"/>
     </row>
     <row r="18" spans="1:12" ht="18" customHeight="1">
-      <c r="A18" s="334"/>
-      <c r="B18" s="337"/>
+      <c r="A18" s="365"/>
+      <c r="B18" s="368"/>
       <c r="C18" s="138" t="s">
         <v>121</v>
       </c>
       <c r="D18" s="139"/>
-      <c r="E18" s="341"/>
-      <c r="F18" s="342"/>
-      <c r="G18" s="358" t="s">
+      <c r="E18" s="372"/>
+      <c r="F18" s="373"/>
+      <c r="G18" s="323" t="s">
         <v>240</v>
       </c>
-      <c r="H18" s="359"/>
-      <c r="I18" s="360"/>
+      <c r="H18" s="324"/>
+      <c r="I18" s="325"/>
       <c r="J18" s="151"/>
     </row>
     <row r="19" spans="1:12" ht="18" customHeight="1">
-      <c r="A19" s="335"/>
-      <c r="B19" s="338"/>
+      <c r="A19" s="366"/>
+      <c r="B19" s="369"/>
       <c r="C19" s="135"/>
       <c r="D19" s="136"/>
-      <c r="E19" s="343"/>
-      <c r="F19" s="344"/>
-      <c r="G19" s="361" t="s">
+      <c r="E19" s="374"/>
+      <c r="F19" s="375"/>
+      <c r="G19" s="326" t="s">
         <v>245</v>
       </c>
-      <c r="H19" s="362"/>
-      <c r="I19" s="363"/>
+      <c r="H19" s="327"/>
+      <c r="I19" s="328"/>
       <c r="J19" s="151"/>
     </row>
     <row r="20" spans="1:12" ht="18" customHeight="1">
-      <c r="A20" s="369" t="s">
+      <c r="A20" s="303" t="s">
         <v>122</v>
       </c>
-      <c r="B20" s="370"/>
-      <c r="C20" s="324" t="s">
+      <c r="B20" s="304"/>
+      <c r="C20" s="305" t="s">
         <v>123</v>
       </c>
-      <c r="D20" s="371"/>
-      <c r="E20" s="325"/>
-      <c r="F20" s="324" t="s">
+      <c r="D20" s="306"/>
+      <c r="E20" s="307"/>
+      <c r="F20" s="305" t="s">
         <v>190</v>
       </c>
-      <c r="G20" s="325"/>
-      <c r="H20" s="375" t="s">
+      <c r="G20" s="307"/>
+      <c r="H20" s="315" t="s">
         <v>189</v>
       </c>
-      <c r="I20" s="302" t="s">
+      <c r="I20" s="317" t="s">
         <v>143</v>
       </c>
       <c r="J20" s="162"/>
     </row>
     <row r="21" spans="1:12" ht="18" customHeight="1">
-      <c r="A21" s="373" t="s">
+      <c r="A21" s="311" t="s">
         <v>124</v>
       </c>
-      <c r="B21" s="374"/>
-      <c r="C21" s="328"/>
-      <c r="D21" s="372"/>
-      <c r="E21" s="329"/>
-      <c r="F21" s="328"/>
-      <c r="G21" s="329"/>
-      <c r="H21" s="376"/>
-      <c r="I21" s="304"/>
+      <c r="B21" s="312"/>
+      <c r="C21" s="308"/>
+      <c r="D21" s="309"/>
+      <c r="E21" s="310"/>
+      <c r="F21" s="308"/>
+      <c r="G21" s="310"/>
+      <c r="H21" s="316"/>
+      <c r="I21" s="319"/>
       <c r="J21" s="162"/>
     </row>
     <row r="22" spans="1:12" s="45" customFormat="1" ht="21" customHeight="1">
-      <c r="A22" s="307" t="str">
+      <c r="A22" s="344" t="str">
         <f>進口艙單印1份!B16</f>
         <v>5501</v>
       </c>
-      <c r="B22" s="308"/>
-      <c r="C22" s="309" t="str">
+      <c r="B22" s="345"/>
+      <c r="C22" s="346" t="str">
         <f>進口艙單印1份!T16</f>
         <v>EXPRESS PACKAGE</v>
       </c>
-      <c r="D22" s="310"/>
-      <c r="E22" s="311"/>
-      <c r="F22" s="305" t="str">
+      <c r="D22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="342" t="str">
         <f>進口艙單印1份!C16&amp;進口艙單印1份!D16</f>
         <v>1599PKG</v>
       </c>
-      <c r="G22" s="306"/>
+      <c r="G22" s="343"/>
       <c r="H22" s="216">
         <f>進口艙單印1份!I16</f>
         <v>7137</v>
@@ -8591,16 +8591,16 @@
       <c r="J22" s="163"/>
     </row>
     <row r="23" spans="1:12" ht="18" customHeight="1">
-      <c r="A23" s="366" t="s">
+      <c r="A23" s="300" t="s">
         <v>125</v>
       </c>
-      <c r="B23" s="367"/>
-      <c r="C23" s="367"/>
-      <c r="D23" s="367"/>
-      <c r="E23" s="367"/>
-      <c r="F23" s="367"/>
-      <c r="G23" s="367"/>
-      <c r="H23" s="368"/>
+      <c r="B23" s="301"/>
+      <c r="C23" s="301"/>
+      <c r="D23" s="301"/>
+      <c r="E23" s="301"/>
+      <c r="F23" s="301"/>
+      <c r="G23" s="301"/>
+      <c r="H23" s="302"/>
       <c r="I23" s="159" t="s">
         <v>241</v>
       </c>
@@ -8766,27 +8766,6 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:E21"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="F20:G21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="I10:I13"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="C1:H2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="C4:F5"/>
-    <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="I6:I9"/>
     <mergeCell ref="F22:G22"/>
@@ -8803,6 +8782,27 @@
     <mergeCell ref="A10:B13"/>
     <mergeCell ref="C10:D13"/>
     <mergeCell ref="H10:H13"/>
+    <mergeCell ref="C1:H2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:F5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I10:I13"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:E21"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="F20:G21"/>
+    <mergeCell ref="H20:H21"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -9525,28 +9525,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="C1" s="346" t="s">
+      <c r="C1" s="332" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="346"/>
-      <c r="E1" s="346"/>
-      <c r="F1" s="346"/>
-      <c r="G1" s="346"/>
-      <c r="H1" s="346"/>
+      <c r="D1" s="332"/>
+      <c r="E1" s="332"/>
+      <c r="F1" s="332"/>
+      <c r="G1" s="332"/>
+      <c r="H1" s="332"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="C2" s="346"/>
-      <c r="D2" s="346"/>
-      <c r="E2" s="346"/>
-      <c r="F2" s="346"/>
-      <c r="G2" s="346"/>
-      <c r="H2" s="346"/>
+      <c r="C2" s="332"/>
+      <c r="D2" s="332"/>
+      <c r="E2" s="332"/>
+      <c r="F2" s="332"/>
+      <c r="G2" s="332"/>
+      <c r="H2" s="332"/>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="402" t="s">
+      <c r="A3" s="383" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="402"/>
+      <c r="B3" s="383"/>
       <c r="H3" s="125" t="str">
         <f>'准單(紅紙)-2份'!H3</f>
         <v>准單編號:料</v>
@@ -9558,340 +9558,340 @@
       <c r="J3" s="17"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
-      <c r="A4" s="324" t="s">
+      <c r="A4" s="305" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="325"/>
-      <c r="C4" s="349" t="str">
+      <c r="B4" s="307"/>
+      <c r="C4" s="335" t="str">
         <f>'准單(紅紙)-2份'!C4:F5</f>
         <v>新銳船務代理有限公司</v>
       </c>
-      <c r="D4" s="391"/>
-      <c r="E4" s="391"/>
-      <c r="F4" s="392"/>
+      <c r="D4" s="384"/>
+      <c r="E4" s="384"/>
+      <c r="F4" s="385"/>
       <c r="G4" s="191">
         <v>1312450</v>
       </c>
-      <c r="H4" s="302" t="s">
+      <c r="H4" s="317" t="s">
         <v>128</v>
       </c>
-      <c r="I4" s="300" t="str">
+      <c r="I4" s="341" t="str">
         <f>'准單(紅紙)-2份'!I4:J5</f>
         <v>115/7/27</v>
       </c>
       <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
-      <c r="A5" s="328"/>
-      <c r="B5" s="329"/>
-      <c r="C5" s="393"/>
-      <c r="D5" s="394"/>
-      <c r="E5" s="394"/>
-      <c r="F5" s="395"/>
+      <c r="A5" s="308"/>
+      <c r="B5" s="310"/>
+      <c r="C5" s="386"/>
+      <c r="D5" s="387"/>
+      <c r="E5" s="387"/>
+      <c r="F5" s="388"/>
       <c r="G5" s="215"/>
-      <c r="H5" s="304"/>
-      <c r="I5" s="301"/>
+      <c r="H5" s="319"/>
+      <c r="I5" s="331"/>
       <c r="J5" s="18"/>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
-      <c r="A6" s="312" t="s">
+      <c r="A6" s="349" t="s">
         <v>129</v>
       </c>
-      <c r="B6" s="313"/>
-      <c r="C6" s="396" t="str">
+      <c r="B6" s="350"/>
+      <c r="C6" s="377" t="str">
         <f>'准單(紅紙)-2份'!C6:D9</f>
         <v>大佑輪</v>
       </c>
-      <c r="D6" s="397"/>
-      <c r="E6" s="324" t="s">
+      <c r="D6" s="378"/>
+      <c r="E6" s="305" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="325"/>
-      <c r="G6" s="330" t="str">
+      <c r="F6" s="307"/>
+      <c r="G6" s="361" t="str">
         <f>'准單(紅紙)-2份'!G6:G9</f>
         <v>15PAHD</v>
       </c>
-      <c r="H6" s="302" t="s">
+      <c r="H6" s="317" t="s">
         <v>130</v>
       </c>
-      <c r="I6" s="302" t="s">
+      <c r="I6" s="317" t="s">
         <v>131</v>
       </c>
       <c r="J6" s="19"/>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
-      <c r="A7" s="314"/>
-      <c r="B7" s="315"/>
-      <c r="C7" s="398"/>
-      <c r="D7" s="399"/>
-      <c r="E7" s="326"/>
-      <c r="F7" s="327"/>
-      <c r="G7" s="331"/>
-      <c r="H7" s="303"/>
-      <c r="I7" s="303"/>
+      <c r="A7" s="351"/>
+      <c r="B7" s="352"/>
+      <c r="C7" s="379"/>
+      <c r="D7" s="380"/>
+      <c r="E7" s="313"/>
+      <c r="F7" s="314"/>
+      <c r="G7" s="362"/>
+      <c r="H7" s="318"/>
+      <c r="I7" s="318"/>
       <c r="J7" s="19"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1">
-      <c r="A8" s="314"/>
-      <c r="B8" s="315"/>
-      <c r="C8" s="398"/>
-      <c r="D8" s="399"/>
-      <c r="E8" s="326"/>
-      <c r="F8" s="327"/>
-      <c r="G8" s="331"/>
-      <c r="H8" s="303"/>
-      <c r="I8" s="303"/>
+      <c r="A8" s="351"/>
+      <c r="B8" s="352"/>
+      <c r="C8" s="379"/>
+      <c r="D8" s="380"/>
+      <c r="E8" s="313"/>
+      <c r="F8" s="314"/>
+      <c r="G8" s="362"/>
+      <c r="H8" s="318"/>
+      <c r="I8" s="318"/>
       <c r="J8" s="19"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
-      <c r="A9" s="316"/>
-      <c r="B9" s="317"/>
-      <c r="C9" s="400"/>
-      <c r="D9" s="401"/>
-      <c r="E9" s="328"/>
-      <c r="F9" s="329"/>
-      <c r="G9" s="332"/>
-      <c r="H9" s="304"/>
-      <c r="I9" s="304"/>
+      <c r="A9" s="353"/>
+      <c r="B9" s="354"/>
+      <c r="C9" s="381"/>
+      <c r="D9" s="382"/>
+      <c r="E9" s="308"/>
+      <c r="F9" s="310"/>
+      <c r="G9" s="363"/>
+      <c r="H9" s="319"/>
+      <c r="I9" s="319"/>
       <c r="J9" s="19"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
-      <c r="A10" s="312" t="s">
+      <c r="A10" s="349" t="s">
         <v>110</v>
       </c>
-      <c r="B10" s="313"/>
-      <c r="C10" s="324" t="str">
+      <c r="B10" s="350"/>
+      <c r="C10" s="305" t="str">
         <f>'准單(紅紙)-2份'!C10:D13</f>
         <v>KHH0638S</v>
       </c>
-      <c r="D10" s="325"/>
+      <c r="D10" s="307"/>
       <c r="E10" s="133" t="s">
         <v>111</v>
       </c>
       <c r="F10" s="134"/>
-      <c r="G10" s="300" t="str">
+      <c r="G10" s="341" t="str">
         <f>I4</f>
         <v>115/7/27</v>
       </c>
-      <c r="H10" s="302" t="s">
+      <c r="H10" s="317" t="s">
         <v>132</v>
       </c>
-      <c r="I10" s="302" t="s">
+      <c r="I10" s="317" t="s">
         <v>133</v>
       </c>
       <c r="J10" s="138"/>
       <c r="K10" s="144"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
-      <c r="A11" s="314"/>
-      <c r="B11" s="315"/>
-      <c r="C11" s="326"/>
-      <c r="D11" s="327"/>
-      <c r="E11" s="326" t="s">
+      <c r="A11" s="351"/>
+      <c r="B11" s="352"/>
+      <c r="C11" s="313"/>
+      <c r="D11" s="314"/>
+      <c r="E11" s="313" t="s">
         <v>134</v>
       </c>
-      <c r="F11" s="327"/>
-      <c r="G11" s="365"/>
-      <c r="H11" s="303"/>
-      <c r="I11" s="303"/>
+      <c r="F11" s="314"/>
+      <c r="G11" s="330"/>
+      <c r="H11" s="318"/>
+      <c r="I11" s="318"/>
       <c r="J11" s="138"/>
       <c r="K11" s="144"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
-      <c r="A12" s="314"/>
-      <c r="B12" s="315"/>
-      <c r="C12" s="326"/>
-      <c r="D12" s="327"/>
-      <c r="E12" s="326"/>
-      <c r="F12" s="327"/>
-      <c r="G12" s="365"/>
-      <c r="H12" s="303"/>
-      <c r="I12" s="303"/>
+      <c r="A12" s="351"/>
+      <c r="B12" s="352"/>
+      <c r="C12" s="313"/>
+      <c r="D12" s="314"/>
+      <c r="E12" s="313"/>
+      <c r="F12" s="314"/>
+      <c r="G12" s="330"/>
+      <c r="H12" s="318"/>
+      <c r="I12" s="318"/>
       <c r="J12" s="138"/>
       <c r="K12" s="144"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
-      <c r="A13" s="316"/>
-      <c r="B13" s="317"/>
-      <c r="C13" s="328"/>
-      <c r="D13" s="329"/>
+      <c r="A13" s="353"/>
+      <c r="B13" s="354"/>
+      <c r="C13" s="308"/>
+      <c r="D13" s="310"/>
       <c r="E13" s="135" t="s">
         <v>114</v>
       </c>
       <c r="F13" s="136"/>
-      <c r="G13" s="301"/>
-      <c r="H13" s="304"/>
-      <c r="I13" s="304"/>
+      <c r="G13" s="331"/>
+      <c r="H13" s="319"/>
+      <c r="I13" s="319"/>
       <c r="J13" s="138"/>
       <c r="K13" s="144"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1">
-      <c r="A14" s="333" t="s">
+      <c r="A14" s="364" t="s">
         <v>135</v>
       </c>
-      <c r="B14" s="336" t="s">
+      <c r="B14" s="367" t="s">
         <v>136</v>
       </c>
       <c r="C14" s="133" t="s">
         <v>137</v>
       </c>
       <c r="D14" s="134"/>
-      <c r="E14" s="339" t="s">
+      <c r="E14" s="370" t="s">
         <v>243</v>
       </c>
-      <c r="F14" s="340"/>
-      <c r="G14" s="355" t="str">
+      <c r="F14" s="371"/>
+      <c r="G14" s="320" t="str">
         <f>'准單(紅紙)-2份'!G14:I14</f>
         <v>1.將貨櫃卸存本站或內陸集散站（進口報關放行）。</v>
       </c>
-      <c r="H14" s="356"/>
-      <c r="I14" s="357"/>
+      <c r="H14" s="321"/>
+      <c r="I14" s="322"/>
       <c r="J14" s="138"/>
       <c r="K14" s="144"/>
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1">
-      <c r="A15" s="334"/>
-      <c r="B15" s="337"/>
+      <c r="A15" s="365"/>
+      <c r="B15" s="368"/>
       <c r="C15" s="138" t="s">
         <v>138</v>
       </c>
       <c r="D15" s="139"/>
-      <c r="E15" s="341"/>
-      <c r="F15" s="342"/>
-      <c r="G15" s="358" t="str">
+      <c r="E15" s="372"/>
+      <c r="F15" s="373"/>
+      <c r="G15" s="323" t="str">
         <f>'准單(紅紙)-2份'!G15:I15</f>
         <v>2.將非櫃裝貨物押運或監視進倉存放。</v>
       </c>
-      <c r="H15" s="359"/>
-      <c r="I15" s="360"/>
+      <c r="H15" s="324"/>
+      <c r="I15" s="325"/>
       <c r="J15" s="138"/>
       <c r="K15" s="144"/>
     </row>
     <row r="16" spans="1:11" ht="18" customHeight="1">
-      <c r="A16" s="334"/>
-      <c r="B16" s="337"/>
+      <c r="A16" s="365"/>
+      <c r="B16" s="368"/>
       <c r="C16" s="138" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="139"/>
-      <c r="E16" s="341"/>
-      <c r="F16" s="342"/>
-      <c r="G16" s="358" t="str">
+      <c r="E16" s="372"/>
+      <c r="F16" s="373"/>
+      <c r="G16" s="323" t="str">
         <f>'准單(紅紙)-2份'!G16:I16</f>
         <v>3.船邊免驗提貨（櫃）。4.船邊驗放。</v>
       </c>
-      <c r="H16" s="359"/>
-      <c r="I16" s="360"/>
+      <c r="H16" s="324"/>
+      <c r="I16" s="325"/>
       <c r="J16" s="160"/>
       <c r="K16" s="144"/>
     </row>
     <row r="17" spans="1:11" ht="18" customHeight="1">
-      <c r="A17" s="334"/>
-      <c r="B17" s="337"/>
+      <c r="A17" s="365"/>
+      <c r="B17" s="368"/>
       <c r="C17" s="138" t="s">
         <v>140</v>
       </c>
       <c r="D17" s="139"/>
-      <c r="E17" s="341"/>
-      <c r="F17" s="342"/>
-      <c r="G17" s="358" t="str">
+      <c r="E17" s="372"/>
+      <c r="F17" s="373"/>
+      <c r="G17" s="323" t="str">
         <f>'准單(紅紙)-2份'!G17:I17</f>
         <v>5.將轉口貨櫃或空櫃卸運入站.6.公證。7重新包裝。</v>
       </c>
-      <c r="H17" s="359"/>
-      <c r="I17" s="360"/>
+      <c r="H17" s="324"/>
+      <c r="I17" s="325"/>
       <c r="J17" s="138"/>
       <c r="K17" s="144"/>
     </row>
     <row r="18" spans="1:11" ht="18" customHeight="1">
-      <c r="A18" s="334"/>
-      <c r="B18" s="337"/>
+      <c r="A18" s="365"/>
+      <c r="B18" s="368"/>
       <c r="C18" s="138" t="s">
         <v>121</v>
       </c>
       <c r="D18" s="217"/>
-      <c r="E18" s="341"/>
-      <c r="F18" s="342"/>
-      <c r="G18" s="358" t="str">
+      <c r="E18" s="372"/>
+      <c r="F18" s="373"/>
+      <c r="G18" s="323" t="str">
         <f>'准單(紅紙)-2份'!G18:I18</f>
         <v>8.換櫃.9.轉運他關區貨櫃。</v>
       </c>
-      <c r="H18" s="359"/>
-      <c r="I18" s="360"/>
+      <c r="H18" s="324"/>
+      <c r="I18" s="325"/>
       <c r="J18" s="160"/>
       <c r="K18" s="144"/>
     </row>
     <row r="19" spans="1:11" ht="18" customHeight="1">
-      <c r="A19" s="335"/>
-      <c r="B19" s="338"/>
+      <c r="A19" s="366"/>
+      <c r="B19" s="369"/>
       <c r="C19" s="135"/>
       <c r="D19" s="136"/>
-      <c r="E19" s="343"/>
-      <c r="F19" s="344"/>
-      <c r="G19" s="361" t="str">
+      <c r="E19" s="374"/>
+      <c r="F19" s="375"/>
+      <c r="G19" s="326" t="str">
         <f>'准單(紅紙)-2份'!G19:J19</f>
         <v xml:space="preserve">10.其他:轉運至高雄港(KHH0638S ) </v>
       </c>
-      <c r="H19" s="362"/>
-      <c r="I19" s="363"/>
+      <c r="H19" s="327"/>
+      <c r="I19" s="328"/>
       <c r="J19" s="138"/>
       <c r="K19" s="144"/>
     </row>
     <row r="20" spans="1:11" ht="18" customHeight="1">
-      <c r="A20" s="369" t="s">
+      <c r="A20" s="303" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="370"/>
-      <c r="C20" s="324" t="s">
+      <c r="B20" s="304"/>
+      <c r="C20" s="305" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="371"/>
-      <c r="E20" s="325"/>
-      <c r="F20" s="324" t="s">
+      <c r="D20" s="306"/>
+      <c r="E20" s="307"/>
+      <c r="F20" s="305" t="s">
         <v>192</v>
       </c>
-      <c r="G20" s="325"/>
-      <c r="H20" s="375" t="s">
+      <c r="G20" s="307"/>
+      <c r="H20" s="315" t="s">
         <v>191</v>
       </c>
-      <c r="I20" s="302" t="s">
+      <c r="I20" s="317" t="s">
         <v>143</v>
       </c>
       <c r="J20" s="164"/>
       <c r="K20" s="144"/>
     </row>
     <row r="21" spans="1:11" ht="18" customHeight="1">
-      <c r="A21" s="373" t="s">
+      <c r="A21" s="311" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="374"/>
-      <c r="C21" s="328"/>
-      <c r="D21" s="372"/>
-      <c r="E21" s="329"/>
-      <c r="F21" s="328"/>
-      <c r="G21" s="329"/>
-      <c r="H21" s="376"/>
-      <c r="I21" s="304"/>
+      <c r="B21" s="312"/>
+      <c r="C21" s="308"/>
+      <c r="D21" s="309"/>
+      <c r="E21" s="310"/>
+      <c r="F21" s="308"/>
+      <c r="G21" s="310"/>
+      <c r="H21" s="316"/>
+      <c r="I21" s="319"/>
       <c r="J21" s="164"/>
       <c r="K21" s="144"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="21" customHeight="1">
-      <c r="A22" s="388" t="str">
+      <c r="A22" s="389" t="str">
         <f>'准單(紅紙)-2份'!A22:B22</f>
         <v>5501</v>
       </c>
-      <c r="B22" s="308"/>
-      <c r="C22" s="309" t="str">
+      <c r="B22" s="345"/>
+      <c r="C22" s="346" t="str">
         <f>'准單(紅紙)-2份'!C22:E22</f>
         <v>EXPRESS PACKAGE</v>
       </c>
-      <c r="D22" s="310"/>
-      <c r="E22" s="311"/>
-      <c r="F22" s="389" t="str">
+      <c r="D22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="390" t="str">
         <f>'准單(紅紙)-2份'!F22:H22</f>
         <v>1599PKG</v>
       </c>
-      <c r="G22" s="390"/>
+      <c r="G22" s="391"/>
       <c r="H22" s="218">
         <f>'准單(紅紙)-2份'!H22</f>
         <v>7137</v>
@@ -9983,72 +9983,72 @@
       <c r="J28" s="11"/>
     </row>
     <row r="29" spans="1:11" ht="24" customHeight="1">
-      <c r="A29" s="377" t="s">
+      <c r="A29" s="392" t="s">
         <v>148</v>
       </c>
-      <c r="B29" s="380" t="s">
+      <c r="B29" s="395" t="s">
         <v>149</v>
       </c>
       <c r="C29" s="134"/>
-      <c r="D29" s="380" t="s">
+      <c r="D29" s="395" t="s">
         <v>150</v>
       </c>
       <c r="E29" s="137"/>
       <c r="F29" s="134"/>
-      <c r="G29" s="385" t="s">
+      <c r="G29" s="400" t="s">
         <v>254</v>
       </c>
-      <c r="H29" s="385" t="s">
+      <c r="H29" s="400" t="s">
         <v>255</v>
       </c>
       <c r="I29" s="165"/>
       <c r="J29" s="11"/>
     </row>
     <row r="30" spans="1:11" ht="24" customHeight="1">
-      <c r="A30" s="378"/>
-      <c r="B30" s="381"/>
+      <c r="A30" s="393"/>
+      <c r="B30" s="396"/>
       <c r="C30" s="139"/>
-      <c r="D30" s="383"/>
+      <c r="D30" s="398"/>
       <c r="E30" s="140"/>
       <c r="F30" s="139"/>
-      <c r="G30" s="386"/>
-      <c r="H30" s="386"/>
+      <c r="G30" s="401"/>
+      <c r="H30" s="401"/>
       <c r="I30" s="143"/>
       <c r="J30" s="11"/>
     </row>
     <row r="31" spans="1:11" ht="24" customHeight="1">
-      <c r="A31" s="378"/>
-      <c r="B31" s="381"/>
+      <c r="A31" s="393"/>
+      <c r="B31" s="396"/>
       <c r="C31" s="139"/>
-      <c r="D31" s="383"/>
+      <c r="D31" s="398"/>
       <c r="E31" s="140"/>
       <c r="F31" s="139"/>
-      <c r="G31" s="386"/>
-      <c r="H31" s="386"/>
+      <c r="G31" s="401"/>
+      <c r="H31" s="401"/>
       <c r="I31" s="143"/>
       <c r="J31" s="11"/>
     </row>
     <row r="32" spans="1:11" ht="24" customHeight="1">
-      <c r="A32" s="378"/>
-      <c r="B32" s="381"/>
+      <c r="A32" s="393"/>
+      <c r="B32" s="396"/>
       <c r="C32" s="139"/>
-      <c r="D32" s="383"/>
+      <c r="D32" s="398"/>
       <c r="E32" s="140"/>
       <c r="F32" s="139"/>
-      <c r="G32" s="386"/>
-      <c r="H32" s="386"/>
+      <c r="G32" s="401"/>
+      <c r="H32" s="401"/>
       <c r="I32" s="143"/>
       <c r="J32" s="11"/>
     </row>
     <row r="33" spans="1:10" ht="24" customHeight="1">
-      <c r="A33" s="379"/>
-      <c r="B33" s="382"/>
+      <c r="A33" s="394"/>
+      <c r="B33" s="397"/>
       <c r="C33" s="146"/>
-      <c r="D33" s="384"/>
+      <c r="D33" s="399"/>
       <c r="E33" s="21"/>
       <c r="F33" s="146"/>
-      <c r="G33" s="387"/>
-      <c r="H33" s="387"/>
+      <c r="G33" s="402"/>
+      <c r="H33" s="402"/>
       <c r="I33" s="219"/>
       <c r="J33" s="22"/>
     </row>
@@ -10114,6 +10114,31 @@
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="A29:A33"/>
+    <mergeCell ref="B29:B33"/>
+    <mergeCell ref="D29:D33"/>
+    <mergeCell ref="G29:G33"/>
+    <mergeCell ref="H29:H33"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F20:G21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="I10:I13"/>
+    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:F5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="A6:B9"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="I6:I9"/>
     <mergeCell ref="C1:H2"/>
     <mergeCell ref="A10:B13"/>
     <mergeCell ref="C10:D13"/>
@@ -10130,31 +10155,6 @@
     <mergeCell ref="E14:F19"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="G16:I16"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="C4:F5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="A6:B9"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="I6:I9"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="I10:I13"/>
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F20:G21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="A29:A33"/>
-    <mergeCell ref="B29:B33"/>
-    <mergeCell ref="D29:D33"/>
-    <mergeCell ref="G29:G33"/>
-    <mergeCell ref="H29:H33"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -10185,22 +10185,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="46.5" customHeight="1">
-      <c r="A1" s="413" t="s">
+      <c r="A1" s="419" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="413"/>
+      <c r="B1" s="419"/>
       <c r="C1" s="3"/>
       <c r="D1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="414" t="s">
+      <c r="E1" s="420" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="414"/>
-      <c r="G1" s="415" t="s">
+      <c r="F1" s="420"/>
+      <c r="G1" s="421" t="s">
         <v>186</v>
       </c>
-      <c r="H1" s="415"/>
+      <c r="H1" s="421"/>
       <c r="I1" s="8" t="s">
         <v>28</v>
       </c>
@@ -10227,16 +10227,16 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="16.5">
-      <c r="A3" s="416" t="s">
+      <c r="A3" s="422" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="416"/>
+      <c r="B3" s="422"/>
       <c r="C3" s="5"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="403" t="s">
+      <c r="E3" s="423" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="403"/>
+      <c r="F3" s="423"/>
       <c r="G3" s="3" t="str">
         <f>進口艙單印1份!D3</f>
         <v>輯薪輪</v>
@@ -10249,8 +10249,8 @@
         <v>115/7/27</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="K3" s="403"/>
-      <c r="L3" s="403"/>
+      <c r="K3" s="423"/>
+      <c r="L3" s="423"/>
     </row>
     <row r="4" spans="1:12" ht="42" customHeight="1">
       <c r="A4" s="7" t="s">
@@ -10259,14 +10259,14 @@
       <c r="B4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="404" t="s">
+      <c r="C4" s="428" t="s">
         <v>248</v>
       </c>
-      <c r="D4" s="404"/>
-      <c r="E4" s="403" t="s">
+      <c r="D4" s="428"/>
+      <c r="E4" s="423" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="403"/>
+      <c r="F4" s="423"/>
       <c r="G4" s="3" t="str">
         <f>進口艙單印1份!L3</f>
         <v>15PAHD</v>
@@ -10280,100 +10280,100 @@
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A5" s="405" t="s">
+      <c r="A5" s="429" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="405"/>
+      <c r="B5" s="429"/>
       <c r="C5" s="3" t="s">
         <v>224</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="403" t="s">
+      <c r="E5" s="423" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="403"/>
-      <c r="G5" s="406" t="s">
+      <c r="F5" s="423"/>
+      <c r="G5" s="430" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="406"/>
-      <c r="I5" s="406"/>
+      <c r="H5" s="430"/>
+      <c r="I5" s="430"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickBot="1"/>
     <row r="7" spans="1:12" ht="21" customHeight="1">
-      <c r="A7" s="417" t="s">
+      <c r="A7" s="407" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="194" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="417" t="s">
+      <c r="C7" s="407" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="192" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="419" t="s">
+      <c r="E7" s="424" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="420"/>
+      <c r="F7" s="425"/>
       <c r="G7" s="194" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="417" t="s">
+      <c r="H7" s="407" t="s">
         <v>34</v>
       </c>
       <c r="I7" s="152" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="409" t="s">
+      <c r="J7" s="415" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A8" s="418"/>
+      <c r="A8" s="408"/>
       <c r="B8" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="418"/>
+      <c r="C8" s="408"/>
       <c r="D8" s="193" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="411" t="s">
+      <c r="E8" s="417" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="412"/>
+      <c r="F8" s="418"/>
       <c r="G8" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="H8" s="418"/>
+      <c r="H8" s="408"/>
       <c r="I8" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="410"/>
+      <c r="J8" s="416"/>
     </row>
     <row r="9" spans="1:12" ht="21" customHeight="1">
-      <c r="A9" s="417">
+      <c r="A9" s="407">
         <v>1</v>
       </c>
-      <c r="B9" s="427" t="str">
+      <c r="B9" s="409" t="str">
         <f>進口艙單印1份!E16</f>
         <v>TCNU9125529</v>
       </c>
-      <c r="C9" s="429">
+      <c r="C9" s="411">
         <f>進口艙單印1份!P16</f>
         <v>200405</v>
       </c>
-      <c r="D9" s="421" t="str">
+      <c r="D9" s="426" t="str">
         <f>進口艙單印1份!B16</f>
         <v>5501</v>
       </c>
-      <c r="E9" s="417">
+      <c r="E9" s="407">
         <f>進口艙單印1份!C16</f>
         <v>1599</v>
       </c>
-      <c r="F9" s="417" t="str">
+      <c r="F9" s="407" t="str">
         <f>進口艙單印1份!D16</f>
         <v>PKG</v>
       </c>
@@ -10381,52 +10381,52 @@
         <f t="shared" ref="G9" si="0">B9</f>
         <v>TCNU9125529</v>
       </c>
-      <c r="H9" s="417" t="str">
+      <c r="H9" s="407" t="str">
         <f>進口艙單印1份!U16</f>
         <v>45G1</v>
       </c>
-      <c r="I9" s="423"/>
-      <c r="J9" s="407" t="s">
+      <c r="I9" s="403"/>
+      <c r="J9" s="413" t="s">
         <v>278</v>
       </c>
       <c r="L9" s="44"/>
     </row>
     <row r="10" spans="1:12" ht="21" customHeight="1" thickBot="1">
-      <c r="A10" s="418"/>
-      <c r="B10" s="428"/>
-      <c r="C10" s="430"/>
-      <c r="D10" s="422"/>
-      <c r="E10" s="418"/>
-      <c r="F10" s="418"/>
+      <c r="A10" s="408"/>
+      <c r="B10" s="410"/>
+      <c r="C10" s="412"/>
+      <c r="D10" s="427"/>
+      <c r="E10" s="408"/>
+      <c r="F10" s="408"/>
       <c r="G10" s="168">
         <f>進口艙單印1份!I16</f>
         <v>7137</v>
       </c>
-      <c r="H10" s="418"/>
-      <c r="I10" s="424"/>
-      <c r="J10" s="408"/>
+      <c r="H10" s="408"/>
+      <c r="I10" s="404"/>
+      <c r="J10" s="414"/>
       <c r="L10" s="44"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="426" t="s">
+      <c r="A11" s="406" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="426"/>
+      <c r="B11" s="406"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="425" t="s">
+      <c r="A12" s="405" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="425"/>
+      <c r="B12" s="405"/>
       <c r="G12" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="425" t="s">
+      <c r="A13" s="405" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="425"/>
+      <c r="B13" s="405"/>
     </row>
     <row r="14" spans="1:12" ht="12" customHeight="1">
       <c r="A14" s="1"/>
@@ -10438,13 +10438,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="E8:F8"/>
@@ -10461,12 +10460,13 @@
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="H9:H10"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -11449,21 +11449,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1">
-      <c r="A1" s="432" t="s">
+      <c r="A1" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="432"/>
+      <c r="B1" s="462"/>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1" thickBot="1">
-      <c r="D2" s="433" t="s">
+      <c r="D2" s="463" t="s">
         <v>277</v>
       </c>
-      <c r="E2" s="434"/>
-      <c r="F2" s="434"/>
-      <c r="G2" s="434"/>
-      <c r="H2" s="434"/>
-      <c r="I2" s="434"/>
-      <c r="J2" s="434"/>
+      <c r="E2" s="464"/>
+      <c r="F2" s="464"/>
+      <c r="G2" s="464"/>
+      <c r="H2" s="464"/>
+      <c r="I2" s="464"/>
+      <c r="J2" s="464"/>
     </row>
     <row r="3" spans="1:16" ht="12" customHeight="1" thickTop="1">
       <c r="A3" s="40">
@@ -11485,12 +11485,12 @@
       <c r="A5" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="B5" s="466" t="str">
+      <c r="B5" s="433" t="str">
         <f>'准單(紅紙)-2份'!C6</f>
         <v>大佑輪</v>
       </c>
-      <c r="C5" s="467"/>
-      <c r="D5" s="468"/>
+      <c r="C5" s="434"/>
+      <c r="D5" s="435"/>
       <c r="E5" s="27" t="s">
         <v>156</v>
       </c>
@@ -11508,12 +11508,12 @@
       <c r="I5" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="J5" s="458" t="str">
+      <c r="J5" s="436" t="str">
         <f>進口艙單印1份!O16</f>
         <v>JET-F WORLDWIDE EXPRESS CO., LTD.</v>
       </c>
-      <c r="K5" s="469"/>
-      <c r="L5" s="459"/>
+      <c r="K5" s="437"/>
+      <c r="L5" s="438"/>
       <c r="M5" s="29" t="s">
         <v>159</v>
       </c>
@@ -11561,186 +11561,186 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="12" customHeight="1" thickBot="1">
-      <c r="A7" s="470" t="s">
+      <c r="A7" s="439" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="471"/>
-      <c r="C7" s="471"/>
-      <c r="D7" s="471"/>
-      <c r="E7" s="471"/>
-      <c r="F7" s="472"/>
-      <c r="G7" s="470" t="s">
+      <c r="B7" s="440"/>
+      <c r="C7" s="440"/>
+      <c r="D7" s="440"/>
+      <c r="E7" s="440"/>
+      <c r="F7" s="441"/>
+      <c r="G7" s="439" t="s">
         <v>168</v>
       </c>
-      <c r="H7" s="471"/>
-      <c r="I7" s="471"/>
-      <c r="J7" s="471"/>
-      <c r="K7" s="471"/>
-      <c r="L7" s="471"/>
-      <c r="M7" s="471"/>
-      <c r="N7" s="472"/>
+      <c r="H7" s="440"/>
+      <c r="I7" s="440"/>
+      <c r="J7" s="440"/>
+      <c r="K7" s="440"/>
+      <c r="L7" s="440"/>
+      <c r="M7" s="440"/>
+      <c r="N7" s="441"/>
     </row>
     <row r="8" spans="1:16" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A8" s="437" t="s">
+      <c r="A8" s="431" t="s">
         <v>169</v>
       </c>
-      <c r="B8" s="473"/>
-      <c r="C8" s="438"/>
-      <c r="D8" s="437" t="s">
+      <c r="B8" s="442"/>
+      <c r="C8" s="432"/>
+      <c r="D8" s="431" t="s">
         <v>170</v>
       </c>
-      <c r="E8" s="473"/>
-      <c r="F8" s="438"/>
-      <c r="G8" s="437" t="s">
+      <c r="E8" s="442"/>
+      <c r="F8" s="432"/>
+      <c r="G8" s="431" t="s">
         <v>171</v>
       </c>
-      <c r="H8" s="438"/>
-      <c r="I8" s="437" t="s">
+      <c r="H8" s="432"/>
+      <c r="I8" s="431" t="s">
         <v>172</v>
       </c>
-      <c r="J8" s="438"/>
-      <c r="K8" s="437" t="s">
+      <c r="J8" s="432"/>
+      <c r="K8" s="431" t="s">
         <v>173</v>
       </c>
-      <c r="L8" s="438"/>
-      <c r="M8" s="437" t="s">
+      <c r="L8" s="432"/>
+      <c r="M8" s="431" t="s">
         <v>174</v>
       </c>
-      <c r="N8" s="438"/>
+      <c r="N8" s="432"/>
     </row>
     <row r="9" spans="1:16" ht="24" customHeight="1">
-      <c r="A9" s="439" t="str">
+      <c r="A9" s="443" t="str">
         <f>進口艙單印1份!E16</f>
         <v>TCNU9125529</v>
       </c>
-      <c r="B9" s="440"/>
-      <c r="C9" s="441"/>
-      <c r="D9" s="460">
+      <c r="B9" s="444"/>
+      <c r="C9" s="445"/>
+      <c r="D9" s="467">
         <f>進口艙單印1份!P16</f>
         <v>200405</v>
       </c>
-      <c r="E9" s="461"/>
-      <c r="F9" s="462"/>
-      <c r="G9" s="451"/>
-      <c r="H9" s="452"/>
-      <c r="I9" s="451"/>
-      <c r="J9" s="452"/>
-      <c r="K9" s="451"/>
-      <c r="L9" s="452"/>
-      <c r="M9" s="451"/>
-      <c r="N9" s="452"/>
+      <c r="E9" s="468"/>
+      <c r="F9" s="469"/>
+      <c r="G9" s="455"/>
+      <c r="H9" s="456"/>
+      <c r="I9" s="455"/>
+      <c r="J9" s="456"/>
+      <c r="K9" s="455"/>
+      <c r="L9" s="456"/>
+      <c r="M9" s="455"/>
+      <c r="N9" s="456"/>
       <c r="P9" s="37"/>
     </row>
     <row r="10" spans="1:16" ht="33.75" customHeight="1" thickBot="1">
-      <c r="A10" s="442"/>
-      <c r="B10" s="443"/>
-      <c r="C10" s="444"/>
-      <c r="D10" s="463" t="str">
+      <c r="A10" s="446"/>
+      <c r="B10" s="447"/>
+      <c r="C10" s="448"/>
+      <c r="D10" s="470" t="str">
         <f>'貨櫃清單-1份'!J9</f>
-        <v>ESN888</v>
-      </c>
-      <c r="E10" s="464"/>
-      <c r="F10" s="465"/>
-      <c r="G10" s="453"/>
-      <c r="H10" s="454"/>
-      <c r="I10" s="453"/>
-      <c r="J10" s="454"/>
-      <c r="K10" s="453"/>
-      <c r="L10" s="454"/>
-      <c r="M10" s="453"/>
-      <c r="N10" s="454"/>
+        <v>ESN501</v>
+      </c>
+      <c r="E10" s="471"/>
+      <c r="F10" s="472"/>
+      <c r="G10" s="457"/>
+      <c r="H10" s="458"/>
+      <c r="I10" s="457"/>
+      <c r="J10" s="458"/>
+      <c r="K10" s="457"/>
+      <c r="L10" s="458"/>
+      <c r="M10" s="457"/>
+      <c r="N10" s="458"/>
       <c r="P10" s="37"/>
     </row>
     <row r="11" spans="1:16" ht="42" customHeight="1" thickBot="1">
-      <c r="A11" s="445"/>
-      <c r="B11" s="446"/>
-      <c r="C11" s="447"/>
-      <c r="D11" s="437" t="s">
+      <c r="A11" s="449"/>
+      <c r="B11" s="450"/>
+      <c r="C11" s="451"/>
+      <c r="D11" s="431" t="s">
         <v>175</v>
       </c>
-      <c r="E11" s="438"/>
+      <c r="E11" s="432"/>
       <c r="F11" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="G11" s="437" t="s">
+      <c r="G11" s="431" t="s">
         <v>177</v>
       </c>
-      <c r="H11" s="438"/>
-      <c r="I11" s="437" t="s">
+      <c r="H11" s="432"/>
+      <c r="I11" s="431" t="s">
         <v>178</v>
       </c>
-      <c r="J11" s="438"/>
-      <c r="K11" s="437" t="s">
+      <c r="J11" s="432"/>
+      <c r="K11" s="431" t="s">
         <v>179</v>
       </c>
-      <c r="L11" s="438"/>
-      <c r="M11" s="437" t="s">
+      <c r="L11" s="432"/>
+      <c r="M11" s="431" t="s">
         <v>180</v>
       </c>
-      <c r="N11" s="438"/>
+      <c r="N11" s="432"/>
     </row>
     <row r="12" spans="1:16" ht="49.5" customHeight="1" thickBot="1">
       <c r="A12" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="437"/>
-      <c r="C12" s="438"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="459"/>
+      <c r="B12" s="431"/>
+      <c r="C12" s="432"/>
+      <c r="D12" s="436"/>
+      <c r="E12" s="438"/>
       <c r="F12" s="28"/>
-      <c r="G12" s="458"/>
-      <c r="H12" s="459"/>
-      <c r="I12" s="458"/>
-      <c r="J12" s="459"/>
-      <c r="K12" s="458"/>
-      <c r="L12" s="459"/>
-      <c r="M12" s="458"/>
-      <c r="N12" s="459"/>
+      <c r="G12" s="436"/>
+      <c r="H12" s="438"/>
+      <c r="I12" s="436"/>
+      <c r="J12" s="438"/>
+      <c r="K12" s="436"/>
+      <c r="L12" s="438"/>
+      <c r="M12" s="436"/>
+      <c r="N12" s="438"/>
     </row>
     <row r="13" spans="1:16" ht="23.25" customHeight="1">
-      <c r="A13" s="435" t="s">
+      <c r="A13" s="465" t="s">
         <v>271</v>
       </c>
-      <c r="B13" s="435"/>
-      <c r="C13" s="435"/>
-      <c r="D13" s="435"/>
-      <c r="E13" s="435"/>
-      <c r="F13" s="435"/>
+      <c r="B13" s="465"/>
+      <c r="C13" s="465"/>
+      <c r="D13" s="465"/>
+      <c r="E13" s="465"/>
+      <c r="F13" s="465"/>
     </row>
     <row r="14" spans="1:16" ht="9" customHeight="1">
-      <c r="A14" s="436" t="s">
+      <c r="A14" s="466" t="s">
         <v>272</v>
       </c>
-      <c r="B14" s="436"/>
-      <c r="C14" s="436"/>
-      <c r="D14" s="436"/>
-      <c r="E14" s="436"/>
-      <c r="F14" s="436"/>
-      <c r="G14" s="436"/>
-      <c r="H14" s="436"/>
-      <c r="I14" s="436"/>
-      <c r="J14" s="436"/>
-      <c r="K14" s="436"/>
-      <c r="L14" s="436"/>
-      <c r="M14" s="436"/>
-      <c r="N14" s="436"/>
+      <c r="B14" s="466"/>
+      <c r="C14" s="466"/>
+      <c r="D14" s="466"/>
+      <c r="E14" s="466"/>
+      <c r="F14" s="466"/>
+      <c r="G14" s="466"/>
+      <c r="H14" s="466"/>
+      <c r="I14" s="466"/>
+      <c r="J14" s="466"/>
+      <c r="K14" s="466"/>
+      <c r="L14" s="466"/>
+      <c r="M14" s="466"/>
+      <c r="N14" s="466"/>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1">
-      <c r="A15" s="432" t="s">
+      <c r="A15" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="B15" s="432"/>
+      <c r="B15" s="462"/>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1" thickBot="1">
-      <c r="D16" s="433" t="s">
+      <c r="D16" s="463" t="s">
         <v>277</v>
       </c>
-      <c r="E16" s="434"/>
-      <c r="F16" s="434"/>
-      <c r="G16" s="434"/>
-      <c r="H16" s="434"/>
-      <c r="I16" s="434"/>
-      <c r="J16" s="434"/>
+      <c r="E16" s="464"/>
+      <c r="F16" s="464"/>
+      <c r="G16" s="464"/>
+      <c r="H16" s="464"/>
+      <c r="I16" s="464"/>
+      <c r="J16" s="464"/>
     </row>
     <row r="17" spans="1:14" ht="12" customHeight="1" thickTop="1">
       <c r="A17" s="40">
@@ -11762,12 +11762,12 @@
       <c r="A19" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="466" t="str">
+      <c r="B19" s="433" t="str">
         <f>B5</f>
         <v>大佑輪</v>
       </c>
-      <c r="C19" s="467"/>
-      <c r="D19" s="468"/>
+      <c r="C19" s="434"/>
+      <c r="D19" s="435"/>
       <c r="E19" s="27" t="s">
         <v>156</v>
       </c>
@@ -11785,12 +11785,12 @@
       <c r="I19" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="J19" s="458" t="str">
+      <c r="J19" s="436" t="str">
         <f>J5</f>
         <v>JET-F WORLDWIDE EXPRESS CO., LTD.</v>
       </c>
-      <c r="K19" s="469"/>
-      <c r="L19" s="459"/>
+      <c r="K19" s="437"/>
+      <c r="L19" s="438"/>
       <c r="M19" s="29" t="s">
         <v>159</v>
       </c>
@@ -11840,184 +11840,184 @@
       </c>
     </row>
     <row r="21" spans="1:14" ht="12" customHeight="1" thickBot="1">
-      <c r="A21" s="470" t="s">
+      <c r="A21" s="439" t="s">
         <v>167</v>
       </c>
-      <c r="B21" s="471"/>
-      <c r="C21" s="471"/>
-      <c r="D21" s="471"/>
-      <c r="E21" s="471"/>
-      <c r="F21" s="472"/>
-      <c r="G21" s="470" t="s">
+      <c r="B21" s="440"/>
+      <c r="C21" s="440"/>
+      <c r="D21" s="440"/>
+      <c r="E21" s="440"/>
+      <c r="F21" s="441"/>
+      <c r="G21" s="439" t="s">
         <v>168</v>
       </c>
-      <c r="H21" s="471"/>
-      <c r="I21" s="471"/>
-      <c r="J21" s="471"/>
-      <c r="K21" s="471"/>
-      <c r="L21" s="471"/>
-      <c r="M21" s="471"/>
-      <c r="N21" s="472"/>
+      <c r="H21" s="440"/>
+      <c r="I21" s="440"/>
+      <c r="J21" s="440"/>
+      <c r="K21" s="440"/>
+      <c r="L21" s="440"/>
+      <c r="M21" s="440"/>
+      <c r="N21" s="441"/>
     </row>
     <row r="22" spans="1:14" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A22" s="437" t="s">
+      <c r="A22" s="431" t="s">
         <v>169</v>
       </c>
-      <c r="B22" s="473"/>
-      <c r="C22" s="438"/>
-      <c r="D22" s="437" t="s">
+      <c r="B22" s="442"/>
+      <c r="C22" s="432"/>
+      <c r="D22" s="431" t="s">
         <v>170</v>
       </c>
-      <c r="E22" s="473"/>
-      <c r="F22" s="438"/>
-      <c r="G22" s="437" t="s">
+      <c r="E22" s="442"/>
+      <c r="F22" s="432"/>
+      <c r="G22" s="431" t="s">
         <v>171</v>
       </c>
-      <c r="H22" s="438"/>
-      <c r="I22" s="437" t="s">
+      <c r="H22" s="432"/>
+      <c r="I22" s="431" t="s">
         <v>172</v>
       </c>
-      <c r="J22" s="438"/>
-      <c r="K22" s="437" t="s">
+      <c r="J22" s="432"/>
+      <c r="K22" s="431" t="s">
         <v>173</v>
       </c>
-      <c r="L22" s="438"/>
-      <c r="M22" s="437" t="s">
+      <c r="L22" s="432"/>
+      <c r="M22" s="431" t="s">
         <v>174</v>
       </c>
-      <c r="N22" s="438"/>
+      <c r="N22" s="432"/>
     </row>
     <row r="23" spans="1:14" ht="24" customHeight="1">
-      <c r="A23" s="439" t="str">
+      <c r="A23" s="443" t="str">
         <f>A9</f>
         <v>TCNU9125529</v>
       </c>
-      <c r="B23" s="440"/>
-      <c r="C23" s="441"/>
-      <c r="D23" s="448">
+      <c r="B23" s="444"/>
+      <c r="C23" s="445"/>
+      <c r="D23" s="452">
         <f>D9</f>
         <v>200405</v>
       </c>
-      <c r="E23" s="449"/>
-      <c r="F23" s="450"/>
-      <c r="G23" s="451"/>
-      <c r="H23" s="452"/>
-      <c r="I23" s="451"/>
-      <c r="J23" s="452"/>
-      <c r="K23" s="451"/>
-      <c r="L23" s="452"/>
-      <c r="M23" s="451"/>
-      <c r="N23" s="452"/>
+      <c r="E23" s="453"/>
+      <c r="F23" s="454"/>
+      <c r="G23" s="455"/>
+      <c r="H23" s="456"/>
+      <c r="I23" s="455"/>
+      <c r="J23" s="456"/>
+      <c r="K23" s="455"/>
+      <c r="L23" s="456"/>
+      <c r="M23" s="455"/>
+      <c r="N23" s="456"/>
     </row>
     <row r="24" spans="1:14" ht="33.75" customHeight="1" thickBot="1">
-      <c r="A24" s="442"/>
-      <c r="B24" s="443"/>
-      <c r="C24" s="444"/>
-      <c r="D24" s="455" t="str">
+      <c r="A24" s="446"/>
+      <c r="B24" s="447"/>
+      <c r="C24" s="448"/>
+      <c r="D24" s="459" t="str">
         <f>D10</f>
-        <v>ESN888</v>
-      </c>
-      <c r="E24" s="456"/>
-      <c r="F24" s="457"/>
-      <c r="G24" s="453"/>
-      <c r="H24" s="454"/>
-      <c r="I24" s="453"/>
-      <c r="J24" s="454"/>
-      <c r="K24" s="453"/>
-      <c r="L24" s="454"/>
-      <c r="M24" s="453"/>
-      <c r="N24" s="454"/>
+        <v>ESN501</v>
+      </c>
+      <c r="E24" s="460"/>
+      <c r="F24" s="461"/>
+      <c r="G24" s="457"/>
+      <c r="H24" s="458"/>
+      <c r="I24" s="457"/>
+      <c r="J24" s="458"/>
+      <c r="K24" s="457"/>
+      <c r="L24" s="458"/>
+      <c r="M24" s="457"/>
+      <c r="N24" s="458"/>
     </row>
     <row r="25" spans="1:14" ht="42" customHeight="1" thickBot="1">
-      <c r="A25" s="445"/>
-      <c r="B25" s="446"/>
-      <c r="C25" s="447"/>
-      <c r="D25" s="437" t="s">
+      <c r="A25" s="449"/>
+      <c r="B25" s="450"/>
+      <c r="C25" s="451"/>
+      <c r="D25" s="431" t="s">
         <v>175</v>
       </c>
-      <c r="E25" s="438"/>
+      <c r="E25" s="432"/>
       <c r="F25" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="G25" s="437" t="s">
+      <c r="G25" s="431" t="s">
         <v>177</v>
       </c>
-      <c r="H25" s="438"/>
-      <c r="I25" s="437" t="s">
+      <c r="H25" s="432"/>
+      <c r="I25" s="431" t="s">
         <v>178</v>
       </c>
-      <c r="J25" s="438"/>
-      <c r="K25" s="437" t="s">
+      <c r="J25" s="432"/>
+      <c r="K25" s="431" t="s">
         <v>179</v>
       </c>
-      <c r="L25" s="438"/>
-      <c r="M25" s="437" t="s">
+      <c r="L25" s="432"/>
+      <c r="M25" s="431" t="s">
         <v>180</v>
       </c>
-      <c r="N25" s="438"/>
+      <c r="N25" s="432"/>
     </row>
     <row r="26" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A26" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="B26" s="437"/>
-      <c r="C26" s="438"/>
-      <c r="D26" s="437"/>
-      <c r="E26" s="438"/>
+      <c r="B26" s="431"/>
+      <c r="C26" s="432"/>
+      <c r="D26" s="431"/>
+      <c r="E26" s="432"/>
       <c r="F26" s="27"/>
-      <c r="G26" s="437"/>
-      <c r="H26" s="438"/>
-      <c r="I26" s="437"/>
-      <c r="J26" s="438"/>
-      <c r="K26" s="437"/>
-      <c r="L26" s="438"/>
-      <c r="M26" s="437"/>
-      <c r="N26" s="438"/>
+      <c r="G26" s="431"/>
+      <c r="H26" s="432"/>
+      <c r="I26" s="431"/>
+      <c r="J26" s="432"/>
+      <c r="K26" s="431"/>
+      <c r="L26" s="432"/>
+      <c r="M26" s="431"/>
+      <c r="N26" s="432"/>
     </row>
     <row r="27" spans="1:14" ht="23.25" customHeight="1">
-      <c r="A27" s="435" t="s">
+      <c r="A27" s="465" t="s">
         <v>271</v>
       </c>
-      <c r="B27" s="435"/>
-      <c r="C27" s="435"/>
-      <c r="D27" s="435"/>
-      <c r="E27" s="435"/>
-      <c r="F27" s="435"/>
+      <c r="B27" s="465"/>
+      <c r="C27" s="465"/>
+      <c r="D27" s="465"/>
+      <c r="E27" s="465"/>
+      <c r="F27" s="465"/>
     </row>
     <row r="28" spans="1:14" s="169" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="436" t="s">
+      <c r="A28" s="466" t="s">
         <v>272</v>
       </c>
-      <c r="B28" s="436"/>
-      <c r="C28" s="436"/>
-      <c r="D28" s="436"/>
-      <c r="E28" s="436"/>
-      <c r="F28" s="436"/>
-      <c r="G28" s="436"/>
-      <c r="H28" s="436"/>
-      <c r="I28" s="436"/>
-      <c r="J28" s="436"/>
-      <c r="K28" s="436"/>
-      <c r="L28" s="436"/>
-      <c r="M28" s="436"/>
-      <c r="N28" s="436"/>
+      <c r="B28" s="466"/>
+      <c r="C28" s="466"/>
+      <c r="D28" s="466"/>
+      <c r="E28" s="466"/>
+      <c r="F28" s="466"/>
+      <c r="G28" s="466"/>
+      <c r="H28" s="466"/>
+      <c r="I28" s="466"/>
+      <c r="J28" s="466"/>
+      <c r="K28" s="466"/>
+      <c r="L28" s="466"/>
+      <c r="M28" s="466"/>
+      <c r="N28" s="466"/>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
-      <c r="A29" s="431" t="s">
+      <c r="A29" s="473" t="s">
         <v>276</v>
       </c>
-      <c r="B29" s="432"/>
+      <c r="B29" s="462"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1" thickBot="1">
-      <c r="D30" s="433" t="s">
+      <c r="D30" s="463" t="s">
         <v>277</v>
       </c>
-      <c r="E30" s="434"/>
-      <c r="F30" s="434"/>
-      <c r="G30" s="434"/>
-      <c r="H30" s="434"/>
-      <c r="I30" s="434"/>
-      <c r="J30" s="434"/>
+      <c r="E30" s="464"/>
+      <c r="F30" s="464"/>
+      <c r="G30" s="464"/>
+      <c r="H30" s="464"/>
+      <c r="I30" s="464"/>
+      <c r="J30" s="464"/>
     </row>
     <row r="31" spans="1:14" ht="12" customHeight="1" thickTop="1">
       <c r="A31" s="40">
@@ -12039,12 +12039,12 @@
       <c r="A33" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="B33" s="466" t="str">
+      <c r="B33" s="433" t="str">
         <f>B5</f>
         <v>大佑輪</v>
       </c>
-      <c r="C33" s="467"/>
-      <c r="D33" s="468"/>
+      <c r="C33" s="434"/>
+      <c r="D33" s="435"/>
       <c r="E33" s="27" t="s">
         <v>156</v>
       </c>
@@ -12062,12 +12062,12 @@
       <c r="I33" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="J33" s="458" t="str">
+      <c r="J33" s="436" t="str">
         <f>J5</f>
         <v>JET-F WORLDWIDE EXPRESS CO., LTD.</v>
       </c>
-      <c r="K33" s="469"/>
-      <c r="L33" s="459"/>
+      <c r="K33" s="437"/>
+      <c r="L33" s="438"/>
       <c r="M33" s="29" t="s">
         <v>159</v>
       </c>
@@ -12117,184 +12117,201 @@
       </c>
     </row>
     <row r="35" spans="1:14" ht="12" customHeight="1" thickBot="1">
-      <c r="A35" s="470" t="s">
+      <c r="A35" s="439" t="s">
         <v>167</v>
       </c>
-      <c r="B35" s="471"/>
-      <c r="C35" s="471"/>
-      <c r="D35" s="471"/>
-      <c r="E35" s="471"/>
-      <c r="F35" s="472"/>
-      <c r="G35" s="470" t="s">
+      <c r="B35" s="440"/>
+      <c r="C35" s="440"/>
+      <c r="D35" s="440"/>
+      <c r="E35" s="440"/>
+      <c r="F35" s="441"/>
+      <c r="G35" s="439" t="s">
         <v>168</v>
       </c>
-      <c r="H35" s="471"/>
-      <c r="I35" s="471"/>
-      <c r="J35" s="471"/>
-      <c r="K35" s="471"/>
-      <c r="L35" s="471"/>
-      <c r="M35" s="471"/>
-      <c r="N35" s="472"/>
+      <c r="H35" s="440"/>
+      <c r="I35" s="440"/>
+      <c r="J35" s="440"/>
+      <c r="K35" s="440"/>
+      <c r="L35" s="440"/>
+      <c r="M35" s="440"/>
+      <c r="N35" s="441"/>
     </row>
     <row r="36" spans="1:14" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A36" s="437" t="s">
+      <c r="A36" s="431" t="s">
         <v>169</v>
       </c>
-      <c r="B36" s="473"/>
-      <c r="C36" s="438"/>
-      <c r="D36" s="437" t="s">
+      <c r="B36" s="442"/>
+      <c r="C36" s="432"/>
+      <c r="D36" s="431" t="s">
         <v>170</v>
       </c>
-      <c r="E36" s="473"/>
-      <c r="F36" s="438"/>
-      <c r="G36" s="437" t="s">
+      <c r="E36" s="442"/>
+      <c r="F36" s="432"/>
+      <c r="G36" s="431" t="s">
         <v>171</v>
       </c>
-      <c r="H36" s="438"/>
-      <c r="I36" s="437" t="s">
+      <c r="H36" s="432"/>
+      <c r="I36" s="431" t="s">
         <v>172</v>
       </c>
-      <c r="J36" s="438"/>
-      <c r="K36" s="437" t="s">
+      <c r="J36" s="432"/>
+      <c r="K36" s="431" t="s">
         <v>173</v>
       </c>
-      <c r="L36" s="438"/>
-      <c r="M36" s="437" t="s">
+      <c r="L36" s="432"/>
+      <c r="M36" s="431" t="s">
         <v>174</v>
       </c>
-      <c r="N36" s="438"/>
+      <c r="N36" s="432"/>
     </row>
     <row r="37" spans="1:14" ht="18" customHeight="1">
-      <c r="A37" s="439" t="str">
+      <c r="A37" s="443" t="str">
         <f>A9</f>
         <v>TCNU9125529</v>
       </c>
-      <c r="B37" s="440"/>
-      <c r="C37" s="441"/>
-      <c r="D37" s="448">
+      <c r="B37" s="444"/>
+      <c r="C37" s="445"/>
+      <c r="D37" s="452">
         <f>D9</f>
         <v>200405</v>
       </c>
-      <c r="E37" s="449"/>
-      <c r="F37" s="450"/>
-      <c r="G37" s="451"/>
-      <c r="H37" s="452"/>
-      <c r="I37" s="451"/>
-      <c r="J37" s="452"/>
-      <c r="K37" s="451"/>
-      <c r="L37" s="452"/>
-      <c r="M37" s="451"/>
-      <c r="N37" s="452"/>
+      <c r="E37" s="453"/>
+      <c r="F37" s="454"/>
+      <c r="G37" s="455"/>
+      <c r="H37" s="456"/>
+      <c r="I37" s="455"/>
+      <c r="J37" s="456"/>
+      <c r="K37" s="455"/>
+      <c r="L37" s="456"/>
+      <c r="M37" s="455"/>
+      <c r="N37" s="456"/>
     </row>
     <row r="38" spans="1:14" ht="33.75" customHeight="1" thickBot="1">
-      <c r="A38" s="442"/>
-      <c r="B38" s="443"/>
-      <c r="C38" s="444"/>
-      <c r="D38" s="455" t="str">
+      <c r="A38" s="446"/>
+      <c r="B38" s="447"/>
+      <c r="C38" s="448"/>
+      <c r="D38" s="459" t="str">
         <f>D10</f>
-        <v>ESN888</v>
-      </c>
-      <c r="E38" s="456"/>
-      <c r="F38" s="457"/>
-      <c r="G38" s="453"/>
-      <c r="H38" s="454"/>
-      <c r="I38" s="453"/>
-      <c r="J38" s="454"/>
-      <c r="K38" s="453"/>
-      <c r="L38" s="454"/>
-      <c r="M38" s="453"/>
-      <c r="N38" s="454"/>
+        <v>ESN501</v>
+      </c>
+      <c r="E38" s="460"/>
+      <c r="F38" s="461"/>
+      <c r="G38" s="457"/>
+      <c r="H38" s="458"/>
+      <c r="I38" s="457"/>
+      <c r="J38" s="458"/>
+      <c r="K38" s="457"/>
+      <c r="L38" s="458"/>
+      <c r="M38" s="457"/>
+      <c r="N38" s="458"/>
     </row>
     <row r="39" spans="1:14" ht="42" customHeight="1" thickBot="1">
-      <c r="A39" s="445"/>
-      <c r="B39" s="446"/>
-      <c r="C39" s="447"/>
-      <c r="D39" s="437" t="s">
+      <c r="A39" s="449"/>
+      <c r="B39" s="450"/>
+      <c r="C39" s="451"/>
+      <c r="D39" s="431" t="s">
         <v>175</v>
       </c>
-      <c r="E39" s="438"/>
+      <c r="E39" s="432"/>
       <c r="F39" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="G39" s="437" t="s">
+      <c r="G39" s="431" t="s">
         <v>177</v>
       </c>
-      <c r="H39" s="438"/>
-      <c r="I39" s="437" t="s">
+      <c r="H39" s="432"/>
+      <c r="I39" s="431" t="s">
         <v>178</v>
       </c>
-      <c r="J39" s="438"/>
-      <c r="K39" s="437" t="s">
+      <c r="J39" s="432"/>
+      <c r="K39" s="431" t="s">
         <v>179</v>
       </c>
-      <c r="L39" s="438"/>
-      <c r="M39" s="437" t="s">
+      <c r="L39" s="432"/>
+      <c r="M39" s="431" t="s">
         <v>180</v>
       </c>
-      <c r="N39" s="438"/>
+      <c r="N39" s="432"/>
     </row>
     <row r="40" spans="1:14" ht="49.5" customHeight="1" thickBot="1">
       <c r="A40" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="B40" s="437"/>
-      <c r="C40" s="438"/>
-      <c r="D40" s="437"/>
-      <c r="E40" s="438"/>
+      <c r="B40" s="431"/>
+      <c r="C40" s="432"/>
+      <c r="D40" s="431"/>
+      <c r="E40" s="432"/>
       <c r="F40" s="27"/>
-      <c r="G40" s="437"/>
-      <c r="H40" s="438"/>
-      <c r="I40" s="437"/>
-      <c r="J40" s="438"/>
-      <c r="K40" s="437"/>
-      <c r="L40" s="438"/>
-      <c r="M40" s="437"/>
-      <c r="N40" s="438"/>
+      <c r="G40" s="431"/>
+      <c r="H40" s="432"/>
+      <c r="I40" s="431"/>
+      <c r="J40" s="432"/>
+      <c r="K40" s="431"/>
+      <c r="L40" s="432"/>
+      <c r="M40" s="431"/>
+      <c r="N40" s="432"/>
     </row>
     <row r="41" spans="1:14" ht="23.25" customHeight="1">
-      <c r="A41" s="435" t="s">
+      <c r="A41" s="465" t="s">
         <v>271</v>
       </c>
-      <c r="B41" s="435"/>
-      <c r="C41" s="435"/>
-      <c r="D41" s="435"/>
-      <c r="E41" s="435"/>
-      <c r="F41" s="435"/>
+      <c r="B41" s="465"/>
+      <c r="C41" s="465"/>
+      <c r="D41" s="465"/>
+      <c r="E41" s="465"/>
+      <c r="F41" s="465"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="95">
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:N7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="G21:N21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D30:J30"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="A37:C39"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="G37:H38"/>
+    <mergeCell ref="I37:J38"/>
+    <mergeCell ref="K37:L38"/>
+    <mergeCell ref="M37:N38"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D16:J16"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:N14"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A9:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="M9:N10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="G35:N35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="M36:N36"/>
     <mergeCell ref="M39:N39"/>
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="A23:C25"/>
@@ -12311,54 +12328,37 @@
     <mergeCell ref="I26:J26"/>
     <mergeCell ref="K26:L26"/>
     <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="G35:N35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D16:J16"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:N14"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A9:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="M9:N10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D30:J30"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A28:N28"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="A37:C39"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="G37:H38"/>
-    <mergeCell ref="I37:J38"/>
-    <mergeCell ref="K37:L38"/>
-    <mergeCell ref="M37:N38"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="G21:N21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:N7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
